--- a/indicadores/GR-EPRIV-INF_out.xlsx
+++ b/indicadores/GR-EPRIV-INF_out.xlsx
@@ -8,13 +8,14 @@
   <sheets>
     <sheet name="Portada" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Data" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Correlograma" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Referencias" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Correlograma" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="190">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -58,7 +59,7 @@
     <t xml:space="preserve">niv</t>
   </si>
   <si>
-    <t xml:space="preserve">(1 0 2)(0 0 1)</t>
+    <t xml:space="preserve">(4 0 0)</t>
   </si>
   <si>
     <t xml:space="preserve">Código</t>
@@ -106,13 +107,13 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">17/11/2025</t>
+    <t xml:space="preserve">07/05/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">pcohan</t>
+    <t xml:space="preserve">vcorvalan</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>
@@ -494,6 +495,63 @@
   </si>
   <si>
     <t xml:space="preserve">2030T4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Referencias de las series incluidas en la hoja Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a_original | serie de datos brutos transformados, se importa directo desde base de datos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a_original_fct_normal | serie original con 4 forecasts obtenidos del mejor modelo ARIMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a_original_fct_optimista | serie original con 4 forecasts, intervalo y límite optimista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a_original_fct_pesimista | serie original con 4 forecasts, intervalo y límite pesimista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b_d16 | salida D16 del X13-ARIMA-SEATS con los factores estacionales de la serie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c_c17 | salida C17 del X13-ARIMA-SEATS con pesos del irregular</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d_d12 | salida D12 del X13-ARIMA-SEATS con el componente tendencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d_hp_1600 | tendencia HP de largo plazo con un lambda de 1.600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d_hp_200 | suavizado con filtro HP usando lambda de 200, sirve para determinar PG automáticos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e_ajustada | serie ajustada por estacionalidad usando el mejor modelo (LOG o NIV según el caso)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">f_filtrada | serie ajustada por estacionalidad y corregida por irregularidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">g_final | serie f_filtrada con o sin suavizado 2x2 según el caso (es la vieja española)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">g_final_fct_normal | a_original_fct ajustada por D16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gg_final_tctl | tasas de cambio trimestral logarítmicas de la serie g_final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gg_var_interanual | variaciones interanuales de g_final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gg_final_var_trimestral | variaciones trimestrales de g_final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">h_irregular | g_final/d_d12 componente irregular</t>
+  </si>
+  <si>
+    <t xml:space="preserve">i_dt | g_final/d_hp_1600 desvíos respecto de la tendencia</t>
   </si>
   <si>
     <t xml:space="preserve">Coeficientes de correlación de TCTL del ICA-SFE y serie específica</t>
@@ -1060,7 +1118,7 @@
       <c r="B9"/>
       <c r="C9"/>
       <c r="D9" t="n">
-        <v>0.322680640744442</v>
+        <v>-0.234116698817283</v>
       </c>
       <c r="E9"/>
       <c r="F9"/>
@@ -1076,7 +1134,7 @@
       <c r="B10"/>
       <c r="C10"/>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E10"/>
       <c r="F10"/>
@@ -1118,7 +1176,7 @@
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13" t="n">
-        <v>0.0525636251869252</v>
+        <v>0.0395045978888794</v>
       </c>
       <c r="E13"/>
       <c r="F13"/>
@@ -1188,7 +1246,7 @@
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18" t="n">
-        <v>0.442268742372217</v>
+        <v>0.661942796338858</v>
       </c>
       <c r="E18"/>
       <c r="F18"/>
@@ -1218,7 +1276,7 @@
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20" t="n">
-        <v>0.299746885161285</v>
+        <v>0.455952867215112</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -1478,40 +1536,40 @@
         <v>184.844</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>-3.24669134247289</v>
+        <v>-3.7457939628279</v>
       </c>
       <c r="G2" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H2" s="8" t="n">
-        <v>190.287290258006</v>
+        <v>191.045083655607</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>187.628445971511</v>
+        <v>187.656366159075</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>188.501624608426</v>
+        <v>188.233046615371</v>
       </c>
       <c r="K2" s="11" t="n">
-        <v>188.090691342473</v>
+        <v>188.589793962828</v>
       </c>
       <c r="L2" s="12" t="n">
-        <v>188.090691342473</v>
+        <v>188.589793962828</v>
       </c>
       <c r="M2" s="13" t="n">
-        <v>189.338238249839</v>
+        <v>189.879483082141</v>
       </c>
       <c r="N2" s="14" t="n">
-        <v>189.338238249839</v>
+        <v>189.879483082141</v>
       </c>
       <c r="O2" s="15"/>
       <c r="P2" s="16"/>
       <c r="Q2" s="17"/>
       <c r="R2" s="18" t="n">
-        <v>0.995012530753469</v>
+        <v>0.993898819319701</v>
       </c>
       <c r="S2" s="19" t="n">
-        <v>1.0091126495744</v>
+        <v>1.01184674396382</v>
       </c>
     </row>
     <row r="3">
@@ -1531,44 +1589,44 @@
         <v>187.087</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>-4.7463320645699</v>
+        <v>-5.37186132076815</v>
       </c>
       <c r="G3" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>188.859760094257</v>
+        <v>189.12463927302</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>187.054338969707</v>
+        <v>187.202043372929</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>187.841474651279</v>
+        <v>187.672267121634</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>191.83333206457</v>
+        <v>192.458861320768</v>
       </c>
       <c r="L3" s="12" t="n">
-        <v>191.83333206457</v>
+        <v>192.458861320768</v>
       </c>
       <c r="M3" s="13" t="n">
-        <v>188.841773101594</v>
+        <v>189.114990042871</v>
       </c>
       <c r="N3" s="14" t="n">
-        <v>188.841773101594</v>
+        <v>189.114990042871</v>
       </c>
       <c r="O3" s="15" t="n">
-        <v>-0.00262555089397585</v>
+        <v>-0.00403432836295332</v>
       </c>
       <c r="P3" s="16"/>
       <c r="Q3" s="17" t="n">
-        <v>-0.00262210714979527</v>
+        <v>-0.00402620139291177</v>
       </c>
       <c r="R3" s="18" t="n">
-        <v>0.999904760057653</v>
+        <v>0.999948979518552</v>
       </c>
       <c r="S3" s="19" t="n">
-        <v>1.00955569457374</v>
+        <v>1.01021862067035</v>
       </c>
     </row>
     <row r="4">
@@ -1588,44 +1646,44 @@
         <v>186.517</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>2.90726306523667</v>
+        <v>3.56455643288175</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>186.133543901287</v>
+        <v>185.698939889549</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>186.48052087126</v>
+        <v>186.748303979161</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>187.179270027801</v>
+        <v>187.113271364633</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>183.609736934763</v>
+        <v>182.952443567118</v>
       </c>
       <c r="L4" s="12" t="n">
-        <v>183.609736934763</v>
+        <v>182.952443567118</v>
       </c>
       <c r="M4" s="13" t="n">
-        <v>185.908992656167</v>
+        <v>185.593680776486</v>
       </c>
       <c r="N4" s="14" t="n">
-        <v>185.908992656167</v>
+        <v>185.593680776486</v>
       </c>
       <c r="O4" s="15" t="n">
-        <v>-0.0156522178940932</v>
+        <v>-0.0187954707447947</v>
       </c>
       <c r="P4" s="16"/>
       <c r="Q4" s="17" t="n">
-        <v>-0.0155303585496882</v>
+        <v>-0.0186199373491588</v>
       </c>
       <c r="R4" s="18" t="n">
-        <v>0.998793601408897</v>
+        <v>0.999433173322766</v>
       </c>
       <c r="S4" s="19" t="n">
-        <v>0.996935185442307</v>
+        <v>0.993817222549963</v>
       </c>
     </row>
     <row r="5">
@@ -1645,44 +1703,44 @@
         <v>189.606</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>5.02283530942705</v>
+        <v>5.59502534906231</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>182.583173737183</v>
+        <v>182.156230495883</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>185.910267450211</v>
+        <v>186.299016881364</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>186.53291535873</v>
+        <v>186.581776052103</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>184.583164690573</v>
+        <v>184.010974650938</v>
       </c>
       <c r="L5" s="12" t="n">
-        <v>184.583164690573</v>
+        <v>184.010974650938</v>
       </c>
       <c r="M5" s="13" t="n">
-        <v>183.580273281766</v>
+        <v>183.286154297388</v>
       </c>
       <c r="N5" s="14" t="n">
-        <v>183.580273281766</v>
+        <v>183.286154297388</v>
       </c>
       <c r="O5" s="15" t="n">
-        <v>-0.0126052387637858</v>
+        <v>-0.0125111559873121</v>
       </c>
       <c r="P5" s="16"/>
       <c r="Q5" s="17" t="n">
-        <v>-0.0125261255043672</v>
+        <v>-0.0124332168500758</v>
       </c>
       <c r="R5" s="18" t="n">
-        <v>1.0054610702847</v>
+        <v>1.00620304778172</v>
       </c>
       <c r="S5" s="19" t="n">
-        <v>0.987467103348292</v>
+        <v>0.983827812758159</v>
       </c>
     </row>
     <row r="6">
@@ -1702,46 +1760,46 @@
         <v>178.421</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>-3.12402681115382</v>
+        <v>-3.74922432055751</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>183.893986982656</v>
+        <v>184.387060489615</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>185.34506024064</v>
+        <v>185.855678570377</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>185.902467599338</v>
+        <v>186.082693752789</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>181.545026811154</v>
+        <v>182.170224320558</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>181.545026811154</v>
+        <v>182.170224320558</v>
       </c>
       <c r="M6" s="13" t="n">
-        <v>184.049481280107</v>
+        <v>184.394308646302</v>
       </c>
       <c r="N6" s="14" t="n">
-        <v>184.049481280107</v>
+        <v>184.394308646302</v>
       </c>
       <c r="O6" s="15" t="n">
-        <v>0.00255261304229026</v>
+        <v>0.00602783022744576</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>-0.0279328519089376</v>
+        <v>-0.028887662567876</v>
       </c>
       <c r="Q6" s="17" t="n">
-        <v>0.00255587373279886</v>
+        <v>0.00604603415441773</v>
       </c>
       <c r="R6" s="18" t="n">
-        <v>1.00084556488226</v>
+        <v>1.00003930946492</v>
       </c>
       <c r="S6" s="19" t="n">
-        <v>0.993009908336097</v>
+        <v>0.992137071434586</v>
       </c>
     </row>
     <row r="7">
@@ -1761,46 +1819,46 @@
         <v>183.734</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>-4.79070680754619</v>
+        <v>-5.49181129315402</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>186.710825131959</v>
+        <v>187.149141164796</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>184.785551337405</v>
+        <v>185.418355510642</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>185.278234951555</v>
+        <v>185.608083028429</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>188.524706807546</v>
+        <v>189.225811293154</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>188.524706807546</v>
+        <v>189.225811293154</v>
       </c>
       <c r="M7" s="13" t="n">
-        <v>186.538857046527</v>
+        <v>186.851000960686</v>
       </c>
       <c r="N7" s="14" t="n">
-        <v>186.538857046527</v>
+        <v>186.851000960686</v>
       </c>
       <c r="O7" s="15" t="n">
-        <v>0.0134349247001566</v>
+        <v>0.0132350664730482</v>
       </c>
       <c r="P7" s="16" t="n">
-        <v>-0.012194950392827</v>
+        <v>-0.0119714946005699</v>
       </c>
       <c r="Q7" s="17" t="n">
-        <v>0.0135255788231823</v>
+        <v>0.0133230376383049</v>
       </c>
       <c r="R7" s="18" t="n">
-        <v>0.999078960283578</v>
+        <v>0.99840693789854</v>
       </c>
       <c r="S7" s="19" t="n">
-        <v>1.00948832685473</v>
+        <v>1.00772655676995</v>
       </c>
     </row>
     <row r="8">
@@ -1820,46 +1878,46 @@
         <v>190.427</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>2.86601224013994</v>
+        <v>3.64484306412342</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>187.57083853147</v>
+        <v>187.040522442146</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>184.230017814467</v>
+        <v>184.984810757698</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>184.628738413371</v>
+        <v>185.130440093603</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>187.56098775986</v>
+        <v>186.782156935877</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>187.56098775986</v>
+        <v>186.782156935877</v>
       </c>
       <c r="M8" s="13" t="n">
-        <v>187.260668997654</v>
+        <v>186.879019286987</v>
       </c>
       <c r="N8" s="14" t="n">
-        <v>187.260668997654</v>
+        <v>186.879019286987</v>
       </c>
       <c r="O8" s="15" t="n">
-        <v>0.00386203190750449</v>
+        <v>0.000149938858728021</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>0.0072706345302298</v>
+        <v>0.00692555104852732</v>
       </c>
       <c r="Q8" s="17" t="n">
-        <v>0.00386949916256296</v>
+        <v>0.000149950100120533</v>
       </c>
       <c r="R8" s="18" t="n">
-        <v>0.998346387230314</v>
+        <v>0.999136533874852</v>
       </c>
       <c r="S8" s="19" t="n">
-        <v>1.01645036579348</v>
+        <v>1.01023980575233</v>
       </c>
     </row>
     <row r="9">
@@ -1879,46 +1937,46 @@
         <v>190.167</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>4.77100633665196</v>
+        <v>5.44104801695833</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>186.920488168293</v>
+        <v>186.438705092461</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>183.679073717958</v>
+        <v>184.555187026943</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>183.938731342055</v>
+        <v>184.640349804213</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>185.395993663348</v>
+        <v>184.725951983042</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>185.395993663348</v>
+        <v>184.725951983042</v>
       </c>
       <c r="M9" s="13" t="n">
-        <v>186.747666368044</v>
+        <v>186.414813984482</v>
       </c>
       <c r="N9" s="14" t="n">
-        <v>186.747666368044</v>
+        <v>186.414813984482</v>
       </c>
       <c r="O9" s="15" t="n">
-        <v>-0.00274327015105502</v>
+        <v>-0.00248707854462953</v>
       </c>
       <c r="P9" s="16" t="n">
-        <v>0.0172534501101715</v>
+        <v>0.0170698092231116</v>
       </c>
       <c r="Q9" s="17" t="n">
-        <v>-0.00273951082389656</v>
+        <v>-0.00248398832718799</v>
       </c>
       <c r="R9" s="18" t="n">
-        <v>0.999075426124005</v>
+        <v>0.999871855428479</v>
       </c>
       <c r="S9" s="19" t="n">
-        <v>1.01670627245648</v>
+        <v>1.01007626492377</v>
       </c>
     </row>
     <row r="10">
@@ -1938,46 +1996,46 @@
         <v>186.12</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>-2.51769038562137</v>
+        <v>-3.30519503596801</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>186.349583045762</v>
+        <v>186.951327015127</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>183.135414950225</v>
+        <v>184.130750375142</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>183.20762834161</v>
+        <v>184.136655600372</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>188.637690385621</v>
+        <v>189.425195035968</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>188.637690385621</v>
+        <v>189.425195035968</v>
       </c>
       <c r="M10" s="13" t="n">
-        <v>186.450813742765</v>
+        <v>186.874540148524</v>
       </c>
       <c r="N10" s="14" t="n">
-        <v>186.450813742765</v>
+        <v>186.874540148524</v>
       </c>
       <c r="O10" s="15" t="n">
-        <v>-0.0015908568962994</v>
+        <v>0.00246311013897403</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>0.0130472112496942</v>
+        <v>0.0134506944407888</v>
       </c>
       <c r="Q10" s="17" t="n">
-        <v>-0.0015895921542306</v>
+        <v>0.00246614608686535</v>
       </c>
       <c r="R10" s="18" t="n">
-        <v>1.00054323006979</v>
+        <v>0.99958926813824</v>
       </c>
       <c r="S10" s="19" t="n">
-        <v>1.01810353717461</v>
+        <v>1.01490131207195</v>
       </c>
     </row>
     <row r="11">
@@ -1997,46 +2055,46 @@
         <v>178.072</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>-5.05988053646869</v>
+        <v>-5.84981853911663</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>185.536198457329</v>
+        <v>186.039983098494</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>182.602810488582</v>
+        <v>183.712873587154</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>182.442130327645</v>
+        <v>183.618628933087</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>183.131880536469</v>
+        <v>183.921818539117</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>183.131880536469</v>
+        <v>183.921818539117</v>
       </c>
       <c r="M11" s="13" t="n">
-        <v>185.196915250819</v>
+        <v>185.554578357555</v>
       </c>
       <c r="N11" s="14" t="n">
-        <v>185.196915250819</v>
+        <v>185.554578357555</v>
       </c>
       <c r="O11" s="15" t="n">
-        <v>-0.00674780525708092</v>
+        <v>-0.00708842167405468</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>-0.007193899528251</v>
+        <v>-0.00693826951135113</v>
       </c>
       <c r="Q11" s="17" t="n">
-        <v>-0.00672508994074827</v>
+        <v>-0.00706335806857328</v>
       </c>
       <c r="R11" s="18" t="n">
-        <v>0.998171336864014</v>
+        <v>0.99739085796045</v>
       </c>
       <c r="S11" s="19" t="n">
-        <v>1.01420626963679</v>
+        <v>1.01002490862202</v>
       </c>
     </row>
     <row r="12">
@@ -2056,46 +2114,46 @@
         <v>188.752</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>2.86579045528241</v>
+        <v>3.80251868398283</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>184.168669504377</v>
+        <v>183.519786251726</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>182.088468232489</v>
+        <v>183.306238475753</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>181.676088525988</v>
+        <v>183.111983950545</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>185.886209544718</v>
+        <v>184.949481316017</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>185.886209544718</v>
+        <v>184.949481316017</v>
       </c>
       <c r="M12" s="13" t="n">
-        <v>184.017025552393</v>
+        <v>183.553809840552</v>
       </c>
       <c r="N12" s="14" t="n">
-        <v>184.017025552393</v>
+        <v>183.553809840552</v>
       </c>
       <c r="O12" s="15" t="n">
-        <v>-0.00639138225590651</v>
+        <v>-0.0108411955785957</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>-0.0173215414781044</v>
+        <v>-0.017793380225998</v>
       </c>
       <c r="Q12" s="17" t="n">
-        <v>-0.00637100081730824</v>
+        <v>-0.0107826416071877</v>
       </c>
       <c r="R12" s="18" t="n">
-        <v>0.999176602880436</v>
+        <v>1.00018539466246</v>
       </c>
       <c r="S12" s="19" t="n">
-        <v>1.0105913204643</v>
+        <v>1.00135058886625</v>
       </c>
     </row>
     <row r="13">
@@ -2115,46 +2173,46 @@
         <v>185.205</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>4.04119741633125</v>
+        <v>4.81054180894204</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>181.991371936165</v>
+        <v>181.323192470001</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>181.599926750186</v>
+        <v>182.915657444306</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>180.946802913513</v>
+        <v>182.64395074896</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>181.163802583669</v>
+        <v>180.394458191058</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>181.163802583669</v>
+        <v>180.394458191058</v>
       </c>
       <c r="M13" s="13" t="n">
-        <v>181.208214783923</v>
+        <v>180.838126712014</v>
       </c>
       <c r="N13" s="14" t="n">
-        <v>181.208214783923</v>
+        <v>180.838126712014</v>
       </c>
       <c r="O13" s="15" t="n">
-        <v>-0.0153815554710087</v>
+        <v>-0.0149055625871792</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>-0.0296627620138709</v>
+        <v>-0.0299154726669539</v>
       </c>
       <c r="Q13" s="17" t="n">
-        <v>-0.0152638635476156</v>
+        <v>-0.0147950245810606</v>
       </c>
       <c r="R13" s="18" t="n">
-        <v>0.99569673471929</v>
+        <v>0.997324855406639</v>
       </c>
       <c r="S13" s="19" t="n">
-        <v>0.997842994910448</v>
+        <v>0.988642138342233</v>
       </c>
     </row>
     <row r="14">
@@ -2174,46 +2232,46 @@
         <v>175.164</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>-1.45504442363811</v>
+        <v>-2.45010914992275</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>175.044760353566</v>
+        <v>175.529823485402</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>181.147098198233</v>
+        <v>182.546969922956</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>180.312624072184</v>
+        <v>182.250946911375</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>176.619044423638</v>
+        <v>177.614109149923</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>176.619044423638</v>
+        <v>177.614109149923</v>
       </c>
       <c r="M14" s="13" t="n">
-        <v>175.759376211545</v>
+        <v>176.773369154893</v>
       </c>
       <c r="N14" s="14" t="n">
-        <v>175.759376211545</v>
+        <v>176.773369154893</v>
       </c>
       <c r="O14" s="15" t="n">
-        <v>-0.030530849055574</v>
+        <v>-0.0227337916522047</v>
       </c>
       <c r="P14" s="16" t="n">
-        <v>-0.0573418657532396</v>
+        <v>-0.054053221940251</v>
       </c>
       <c r="Q14" s="17" t="n">
-        <v>-0.0300694898345293</v>
+        <v>-0.0224773261647087</v>
       </c>
       <c r="R14" s="18" t="n">
-        <v>1.00408247499974</v>
+        <v>1.00708452640582</v>
       </c>
       <c r="S14" s="19" t="n">
-        <v>0.970257751626845</v>
+        <v>0.968371971495884</v>
       </c>
     </row>
     <row r="15">
@@ -2233,46 +2291,46 @@
         <v>163.593</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>-5.04261341523485</v>
+        <v>-5.77601345271781</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>1</v>
+        <v>0.640970274043334</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>171.20254253726</v>
+        <v>175.223087708967</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>180.739622155587</v>
+        <v>182.204439592314</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>179.832987582321</v>
+        <v>181.958142558045</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>168.635613415235</v>
+        <v>169.369013452718</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>168.635613415235</v>
+        <v>171.470800128669</v>
       </c>
       <c r="M15" s="13" t="n">
-        <v>172.231927219849</v>
+        <v>176.288665726119</v>
       </c>
       <c r="N15" s="14" t="n">
-        <v>172.231927219849</v>
+        <v>176.288665726119</v>
       </c>
       <c r="O15" s="15" t="n">
-        <v>-0.020273896389298</v>
+        <v>-0.00274571426775113</v>
       </c>
       <c r="P15" s="16" t="n">
-        <v>-0.0700065009906431</v>
+        <v>-0.0499363190790195</v>
       </c>
       <c r="Q15" s="17" t="n">
-        <v>-0.0200697628071388</v>
+        <v>-0.00274194824192986</v>
       </c>
       <c r="R15" s="18" t="n">
-        <v>1.00601267170062</v>
+        <v>1.00608126492396</v>
       </c>
       <c r="S15" s="19" t="n">
-        <v>0.952928445715047</v>
+        <v>0.967532218866718</v>
       </c>
     </row>
     <row r="16">
@@ -2280,58 +2338,58 @@
         <v>66</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>177.4885</v>
+        <v>188.0315</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>177.4885</v>
+        <v>188.0315</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>177.4885</v>
+        <v>188.0315</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>177.4885</v>
+        <v>188.0315</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>2.45106237471354</v>
+        <v>3.43254650278531</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>174.104812450431</v>
+        <v>182.554630611875</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>180.384308167595</v>
+        <v>181.889247095007</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>179.548861125997</v>
+        <v>181.767523620415</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>175.037437625286</v>
+        <v>184.598953497215</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>175.037437625286</v>
+        <v>184.598953497215</v>
       </c>
       <c r="M16" s="13" t="n">
-        <v>173.904700972579</v>
+        <v>182.007431600444</v>
       </c>
       <c r="N16" s="14" t="n">
-        <v>173.904700972579</v>
+        <v>182.007431600444</v>
       </c>
       <c r="O16" s="15" t="n">
-        <v>0.00966547102613919</v>
+        <v>0.0319247215741744</v>
       </c>
       <c r="P16" s="16" t="n">
-        <v>-0.0549532009305004</v>
+        <v>-0.00842465891310784</v>
       </c>
       <c r="Q16" s="17" t="n">
-        <v>0.0097123325490962</v>
+        <v>0.0324397819381648</v>
       </c>
       <c r="R16" s="18" t="n">
-        <v>0.998850626383986</v>
+        <v>0.997002546527597</v>
       </c>
       <c r="S16" s="19" t="n">
-        <v>0.9640788754807</v>
+        <v>1.00064976081503</v>
       </c>
     </row>
     <row r="17">
@@ -2351,46 +2409,46 @@
         <v>191.384</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>3.27245960366804</v>
+        <v>4.02298072132175</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>176.90831522451</v>
+        <v>184.965930524754</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>180.080400774142</v>
+        <v>181.595864548996</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>179.445225514452</v>
+        <v>181.628639317785</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>188.111540396332</v>
+        <v>187.361019278678</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>176.90831522451</v>
+        <v>187.361019278678</v>
       </c>
       <c r="M17" s="13" t="n">
-        <v>176.002894729787</v>
+        <v>184.150945115933</v>
       </c>
       <c r="N17" s="14" t="n">
-        <v>176.002894729787</v>
+        <v>184.150945115933</v>
       </c>
       <c r="O17" s="15" t="n">
-        <v>0.0119929886165888</v>
+        <v>0.0117082559809636</v>
       </c>
       <c r="P17" s="16" t="n">
-        <v>-0.0287256295766917</v>
+        <v>0.0183192475179483</v>
       </c>
       <c r="Q17" s="17" t="n">
-        <v>0.0120651928640971</v>
+        <v>0.0117770658958305</v>
       </c>
       <c r="R17" s="18" t="n">
-        <v>0.994881978873779</v>
+        <v>0.995593862034438</v>
       </c>
       <c r="S17" s="19" t="n">
-        <v>0.977357302478078</v>
+        <v>1.01407014732017</v>
       </c>
     </row>
     <row r="18">
@@ -2410,46 +2468,46 @@
         <v>174.593</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>-0.564510844840615</v>
+        <v>-1.60218334144013</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>1</v>
+        <v>0.793374754069144</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>178.123183911264</v>
+        <v>181.458843465946</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>179.823802721023</v>
+        <v>181.320457638744</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>179.48450444142</v>
+        <v>181.505196018839</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>175.157510844841</v>
+        <v>176.19518334144</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>175.157510844841</v>
+        <v>177.282788409163</v>
       </c>
       <c r="M18" s="13" t="n">
-        <v>177.871787362456</v>
+        <v>181.711700036735</v>
       </c>
       <c r="N18" s="14" t="n">
-        <v>177.871787362456</v>
+        <v>181.711700036735</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>0.0105625528067211</v>
+        <v>-0.0133344098076615</v>
       </c>
       <c r="P18" s="16" t="n">
-        <v>0.0120187679112425</v>
+        <v>0.0279359436630708</v>
       </c>
       <c r="Q18" s="17" t="n">
-        <v>0.0106185334936608</v>
+        <v>-0.0132459004088324</v>
       </c>
       <c r="R18" s="18" t="n">
-        <v>0.998588636564385</v>
+        <v>1.00139346512939</v>
       </c>
       <c r="S18" s="19" t="n">
-        <v>0.98914484440308</v>
+        <v>1.0021577399654</v>
       </c>
     </row>
     <row r="19">
@@ -2469,46 +2527,46 @@
         <v>179.795</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>-4.4688125356338</v>
+        <v>-5.12520404993815</v>
       </c>
       <c r="G19" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>182.505779718618</v>
+        <v>182.633528941698</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>179.608434200565</v>
+        <v>181.062795270422</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>179.616437049189</v>
+        <v>181.389561992063</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>184.263812535634</v>
+        <v>184.920204049938</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>184.263812535634</v>
+        <v>184.920204049938</v>
       </c>
       <c r="M19" s="13" t="n">
-        <v>182.281375335588</v>
+        <v>182.892410256826</v>
       </c>
       <c r="N19" s="14" t="n">
-        <v>182.281375335588</v>
+        <v>182.892410256826</v>
       </c>
       <c r="O19" s="15" t="n">
-        <v>0.0244885165102402</v>
+        <v>0.00647669246768384</v>
       </c>
       <c r="P19" s="16" t="n">
-        <v>0.0583483461978078</v>
+        <v>0.0374598361358458</v>
       </c>
       <c r="Q19" s="17" t="n">
-        <v>0.0247908228647082</v>
+        <v>0.00649771159398105</v>
       </c>
       <c r="R19" s="18" t="n">
-        <v>0.998770425882534</v>
+        <v>1.00141749062523</v>
       </c>
       <c r="S19" s="19" t="n">
-        <v>1.01488204686445</v>
+        <v>1.01010486435754</v>
       </c>
     </row>
     <row r="20">
@@ -2528,46 +2586,46 @@
         <v>187.311</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>1.87063457375634</v>
+        <v>2.86455548173446</v>
       </c>
       <c r="G20" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>185.02382472878</v>
+        <v>184.285005439437</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>179.425298972672</v>
+        <v>180.820122806929</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>179.76912751206</v>
+        <v>181.252993467898</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>185.440365426244</v>
+        <v>184.446444518266</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>185.440365426244</v>
+        <v>184.446444518266</v>
       </c>
       <c r="M20" s="13" t="n">
-        <v>184.301647684098</v>
+        <v>183.811990129797</v>
       </c>
       <c r="N20" s="14" t="n">
-        <v>184.301647684098</v>
+        <v>183.811990129797</v>
       </c>
       <c r="O20" s="15" t="n">
-        <v>0.0110222933160433</v>
+        <v>0.00501538459641807</v>
       </c>
       <c r="P20" s="16" t="n">
-        <v>0.0597853114572087</v>
+        <v>0.00991475190592306</v>
       </c>
       <c r="Q20" s="17" t="n">
-        <v>0.0110832625921904</v>
+        <v>0.00502798269036631</v>
       </c>
       <c r="R20" s="18" t="n">
-        <v>0.996096842956626</v>
+        <v>0.997433240384847</v>
       </c>
       <c r="S20" s="19" t="n">
-        <v>1.0271775983618</v>
+        <v>1.01654609717339</v>
       </c>
     </row>
     <row r="21">
@@ -2587,46 +2645,46 @@
         <v>184.615</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>2.55295265172959</v>
+        <v>3.18013256728208</v>
       </c>
       <c r="G21" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>183.749669467348</v>
+        <v>183.216519286244</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>179.268310408708</v>
+        <v>180.592096491655</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>179.893916881769</v>
+        <v>181.084399887072</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>182.06204734827</v>
+        <v>181.434867432718</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>182.06204734827</v>
+        <v>181.434867432718</v>
       </c>
       <c r="M21" s="13" t="n">
-        <v>182.56661271267</v>
+        <v>182.011977347966</v>
       </c>
       <c r="N21" s="14" t="n">
-        <v>182.56661271267</v>
+        <v>182.011977347966</v>
       </c>
       <c r="O21" s="15" t="n">
-        <v>-0.00945869727309422</v>
+        <v>-0.00984094793438337</v>
       </c>
       <c r="P21" s="16" t="n">
-        <v>0.0372932388013292</v>
+        <v>-0.0116152961725012</v>
       </c>
       <c r="Q21" s="17" t="n">
-        <v>-0.00941410450329727</v>
+        <v>-0.00979268425612445</v>
       </c>
       <c r="R21" s="18" t="n">
-        <v>0.993561584311376</v>
+        <v>0.993425582240233</v>
       </c>
       <c r="S21" s="19" t="n">
-        <v>1.0183986913049</v>
+        <v>1.00786236432211</v>
       </c>
     </row>
     <row r="22">
@@ -2646,46 +2704,46 @@
         <v>194.435</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>-0.552877365806882</v>
+        <v>-1.70012671810568</v>
       </c>
       <c r="G22" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>180.701990727895</v>
+        <v>180.731730008162</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>179.135141296572</v>
+        <v>180.380639019058</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>179.970502399623</v>
+        <v>180.888657945566</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>194.987877365807</v>
+        <v>196.135126718106</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>180.701990727895</v>
+        <v>180.731730008162</v>
       </c>
       <c r="M22" s="13" t="n">
-        <v>179.350428970637</v>
+        <v>179.149365610857</v>
       </c>
       <c r="N22" s="14" t="n">
-        <v>179.350428970637</v>
+        <v>179.149365610857</v>
       </c>
       <c r="O22" s="15" t="n">
-        <v>-0.0177735118084187</v>
+        <v>-0.0158525918769694</v>
       </c>
       <c r="P22" s="16" t="n">
-        <v>0.00831296311858698</v>
+        <v>-0.0141010976473182</v>
       </c>
       <c r="Q22" s="17" t="n">
-        <v>-0.0176164945728283</v>
+        <v>-0.0157276008909896</v>
       </c>
       <c r="R22" s="18" t="n">
-        <v>0.992520493261789</v>
+        <v>0.991244678523061</v>
       </c>
       <c r="S22" s="19" t="n">
-        <v>1.00120181708908</v>
+        <v>0.993174026797465</v>
       </c>
     </row>
     <row r="23">
@@ -2705,46 +2763,46 @@
         <v>169.467</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>-2.90584661098574</v>
+        <v>-3.03843236605636</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>0.629757516597631</v>
+        <v>0.686477414889831</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>176.593973406436</v>
+        <v>176.312821961007</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>179.025210509746</v>
+        <v>180.188199815432</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>179.989421959259</v>
+        <v>180.672396677089</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>172.372846610986</v>
+        <v>172.505432366056</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>173.93568707849</v>
+        <v>173.699134994387</v>
       </c>
       <c r="M23" s="13" t="n">
-        <v>176.353951773111</v>
+        <v>176.072264117088</v>
       </c>
       <c r="N23" s="14" t="n">
-        <v>176.353951773111</v>
+        <v>176.072264117088</v>
       </c>
       <c r="O23" s="15" t="n">
-        <v>-0.016848530658163</v>
+        <v>-0.0173254002958146</v>
       </c>
       <c r="P23" s="16" t="n">
-        <v>-0.0325179879269865</v>
+        <v>-0.037290482038925</v>
       </c>
       <c r="Q23" s="17" t="n">
-        <v>-0.0167073879595642</v>
+        <v>-0.0171761785662863</v>
       </c>
       <c r="R23" s="18" t="n">
-        <v>0.998640827720815</v>
+        <v>0.998635619115824</v>
       </c>
       <c r="S23" s="19" t="n">
-        <v>0.985078868339106</v>
+        <v>0.977157573567196</v>
       </c>
     </row>
     <row r="24">
@@ -2764,46 +2822,46 @@
         <v>178.154</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>1.31155779243093</v>
+        <v>1.99494352858279</v>
       </c>
       <c r="G24" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>176.760873769303</v>
+        <v>176.128507731704</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>178.938916202611</v>
+        <v>180.017447738942</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>179.944870895958</v>
+        <v>180.441460475662</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>176.842442207569</v>
+        <v>176.159056471417</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>176.842442207569</v>
+        <v>176.159056471417</v>
       </c>
       <c r="M24" s="13" t="n">
-        <v>178.192176061554</v>
+        <v>177.716457089867</v>
       </c>
       <c r="N24" s="14" t="n">
-        <v>178.192176061554</v>
+        <v>177.716457089867</v>
       </c>
       <c r="O24" s="15" t="n">
-        <v>0.0103695435697967</v>
+        <v>0.00929484017764972</v>
       </c>
       <c r="P24" s="16" t="n">
-        <v>-0.0331493054962576</v>
+        <v>-0.0331617814247323</v>
       </c>
       <c r="Q24" s="17" t="n">
-        <v>0.0104234936045451</v>
+        <v>0.00933817135267723</v>
       </c>
       <c r="R24" s="18" t="n">
-        <v>1.00809739317152</v>
+        <v>1.00901585653915</v>
       </c>
       <c r="S24" s="19" t="n">
-        <v>0.995826843277563</v>
+        <v>0.987217957603693</v>
       </c>
     </row>
     <row r="25">
@@ -2823,46 +2881,46 @@
         <v>186.889</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>1.74086724741139</v>
+        <v>2.04041957775156</v>
       </c>
       <c r="G25" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>186.940295873065</v>
+        <v>186.599327911265</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>178.8734755774</v>
+        <v>179.866995982239</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>179.800775870595</v>
+        <v>180.166827426895</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>185.148132752589</v>
+        <v>184.848580422248</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>185.148132752589</v>
+        <v>184.848580422248</v>
       </c>
       <c r="M25" s="13" t="n">
-        <v>186.000765535238</v>
+        <v>185.676291884888</v>
       </c>
       <c r="N25" s="14" t="n">
-        <v>186.000765535238</v>
+        <v>185.676291884888</v>
       </c>
       <c r="O25" s="15" t="n">
-        <v>0.0428881807912267</v>
+        <v>0.0438154487857245</v>
       </c>
       <c r="P25" s="16" t="n">
-        <v>0.01881040991856</v>
+        <v>0.0201322714599002</v>
       </c>
       <c r="Q25" s="17" t="n">
-        <v>0.043821169067416</v>
+        <v>0.0447895199204638</v>
       </c>
       <c r="R25" s="18" t="n">
-        <v>0.994974168980321</v>
+        <v>0.995053379684113</v>
       </c>
       <c r="S25" s="19" t="n">
-        <v>1.03984542668963</v>
+        <v>1.03229773128153</v>
       </c>
     </row>
     <row r="26">
@@ -2882,46 +2940,46 @@
         <v>195.657</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>-1.20735442820657</v>
+        <v>-2.20787489378991</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>1</v>
+        <v>0.796261269651909</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>193.111484726086</v>
+        <v>192.878465739207</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>178.824795540102</v>
+        <v>179.733046243431</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>179.505551400605</v>
+        <v>179.798063596373</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>196.864354428207</v>
+        <v>197.86487489379</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>196.864354428207</v>
+        <v>196.848950223639</v>
       </c>
       <c r="M26" s="13" t="n">
-        <v>190.889905692821</v>
+        <v>190.690064676392</v>
       </c>
       <c r="N26" s="14" t="n">
-        <v>190.889905692821</v>
+        <v>190.690064676392</v>
       </c>
       <c r="O26" s="15" t="n">
-        <v>0.0259460623877174</v>
+        <v>0.0266446207105827</v>
       </c>
       <c r="P26" s="16" t="n">
-        <v>0.0643403909787843</v>
+        <v>0.0644194246861223</v>
       </c>
       <c r="Q26" s="17" t="n">
-        <v>0.0262855915862161</v>
+        <v>0.027002762391509</v>
       </c>
       <c r="R26" s="18" t="n">
-        <v>0.988495873063085</v>
+        <v>0.988653989679835</v>
       </c>
       <c r="S26" s="19" t="n">
-        <v>1.06746888828408</v>
+        <v>1.06096273702567</v>
       </c>
     </row>
     <row r="27">
@@ -2941,46 +2999,46 @@
         <v>183.563</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>-1.11978116228228</v>
+        <v>-0.650777836042982</v>
       </c>
       <c r="G27" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H27" s="8" t="n">
-        <v>185.252963473401</v>
+        <v>184.862919419203</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>178.792704657439</v>
+        <v>179.614913710903</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>179.034348787833</v>
+        <v>179.308143814662</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>184.682781162282</v>
+        <v>184.213777836043</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>184.682781162282</v>
+        <v>184.213777836043</v>
       </c>
       <c r="M27" s="13" t="n">
-        <v>184.658878704177</v>
+        <v>184.339602236566</v>
       </c>
       <c r="N27" s="14" t="n">
-        <v>184.658878704177</v>
+        <v>184.339602236566</v>
       </c>
       <c r="O27" s="15" t="n">
-        <v>-0.0331866277655105</v>
+        <v>-0.0338696912242375</v>
       </c>
       <c r="P27" s="16" t="n">
-        <v>0.0470923778433419</v>
+        <v>0.0469542330300248</v>
       </c>
       <c r="Q27" s="17" t="n">
-        <v>-0.0326419931217908</v>
+        <v>-0.0333025344063064</v>
       </c>
       <c r="R27" s="18" t="n">
-        <v>0.996793115974581</v>
+        <v>0.997169160888073</v>
       </c>
       <c r="S27" s="19" t="n">
-        <v>1.03280991837993</v>
+        <v>1.02630454469537</v>
       </c>
     </row>
     <row r="28">
@@ -3000,46 +3058,46 @@
         <v>173.725</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>1.31940193606469</v>
+        <v>1.64309694946071</v>
       </c>
       <c r="G28" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>175.21211477829</v>
+        <v>174.878842986618</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>178.788306220438</v>
+        <v>179.522611013026</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>178.449113349259</v>
+        <v>178.755297345462</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>172.405598063935</v>
+        <v>172.081903050539</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>172.405598063935</v>
+        <v>172.081903050539</v>
       </c>
       <c r="M28" s="13" t="n">
-        <v>176.390906871443</v>
+        <v>176.152460002539</v>
       </c>
       <c r="N28" s="14" t="n">
-        <v>176.390906871443</v>
+        <v>176.152460002539</v>
       </c>
       <c r="O28" s="15" t="n">
-        <v>-0.0458076302115892</v>
+        <v>-0.0454298507180131</v>
       </c>
       <c r="P28" s="16" t="n">
-        <v>-0.0101085762008374</v>
+        <v>-0.00880051916935021</v>
       </c>
       <c r="Q28" s="17" t="n">
-        <v>-0.044774298916756</v>
+        <v>-0.0444133660629271</v>
       </c>
       <c r="R28" s="18" t="n">
-        <v>1.00672780015608</v>
+        <v>1.00728285362695</v>
       </c>
       <c r="S28" s="19" t="n">
-        <v>0.986590849258123</v>
+        <v>0.981227150209826</v>
       </c>
     </row>
     <row r="29">
@@ -3059,46 +3117,46 @@
         <v>176.801</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>0.731349804381589</v>
+        <v>0.568743926965265</v>
       </c>
       <c r="G29" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H29" s="8" t="n">
-        <v>173.203296144834</v>
+        <v>173.639053675129</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>178.826384817941</v>
+        <v>179.46902506825</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>177.840032563739</v>
+        <v>178.222281622578</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>176.069650195618</v>
+        <v>176.232256073035</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>176.069650195618</v>
+        <v>176.232256073035</v>
       </c>
       <c r="M29" s="13" t="n">
-        <v>174.508649074626</v>
+        <v>174.757082248033</v>
       </c>
       <c r="N29" s="14" t="n">
-        <v>174.508649074626</v>
+        <v>174.757082248033</v>
       </c>
       <c r="O29" s="15" t="n">
-        <v>-0.0107282885844479</v>
+        <v>-0.00795296189614429</v>
       </c>
       <c r="P29" s="16" t="n">
-        <v>-0.0617853180740553</v>
+        <v>-0.0588077752200327</v>
       </c>
       <c r="Q29" s="17" t="n">
-        <v>-0.0106709457431892</v>
+        <v>-0.0079214207652073</v>
       </c>
       <c r="R29" s="18" t="n">
-        <v>1.00753653630645</v>
+        <v>1.00643880825909</v>
       </c>
       <c r="S29" s="19" t="n">
-        <v>0.975855152763329</v>
+        <v>0.973745091564266</v>
       </c>
     </row>
     <row r="30">
@@ -3118,46 +3176,46 @@
         <v>171.71</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>-1.77969784333074</v>
+        <v>-2.77191379552169</v>
       </c>
       <c r="G30" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>176.274424466613</v>
+        <v>176.42274981333</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>178.917735846194</v>
+        <v>179.462392352547</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>177.267076333701</v>
+        <v>177.758487108345</v>
       </c>
       <c r="K30" s="11" t="n">
-        <v>173.489697843331</v>
+        <v>174.481913795522</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>173.489697843331</v>
+        <v>174.481913795522</v>
       </c>
       <c r="M30" s="13" t="n">
-        <v>176.14163987151</v>
+        <v>176.290245929246</v>
       </c>
       <c r="N30" s="14" t="n">
-        <v>176.14163987151</v>
+        <v>176.290245929246</v>
       </c>
       <c r="O30" s="15" t="n">
-        <v>0.0093141380682648</v>
+        <v>0.00873485314489074</v>
       </c>
       <c r="P30" s="16" t="n">
-        <v>-0.0772605851932481</v>
+        <v>-0.0755142580269387</v>
       </c>
       <c r="Q30" s="17" t="n">
-        <v>0.00935764963824592</v>
+        <v>0.00877311329241048</v>
       </c>
       <c r="R30" s="18" t="n">
-        <v>0.999246716615271</v>
+        <v>0.999248941056499</v>
       </c>
       <c r="S30" s="19" t="n">
-        <v>0.984483953133238</v>
+        <v>0.982324171757002</v>
       </c>
     </row>
     <row r="31">
@@ -3177,46 +3235,46 @@
         <v>181.36</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>-0.157513603759004</v>
+        <v>1.39509994709541</v>
       </c>
       <c r="G31" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>179.201972235484</v>
+        <v>178.648449891523</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>179.071431742303</v>
+        <v>179.508926361268</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>176.781362649731</v>
+        <v>177.403354137347</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>181.517513603759</v>
+        <v>179.964900052905</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>181.517513603759</v>
+        <v>179.964900052905</v>
       </c>
       <c r="M31" s="13" t="n">
-        <v>178.901067658983</v>
+        <v>178.448653608532</v>
       </c>
       <c r="N31" s="14" t="n">
-        <v>178.901067658983</v>
+        <v>178.448653608532</v>
       </c>
       <c r="O31" s="15" t="n">
-        <v>0.0155445150261992</v>
+        <v>0.0121691436616237</v>
       </c>
       <c r="P31" s="16" t="n">
-        <v>-0.0311807971845097</v>
+        <v>-0.0319570431776997</v>
       </c>
       <c r="Q31" s="17" t="n">
-        <v>0.0156659594488047</v>
+        <v>0.0122434889571414</v>
       </c>
       <c r="R31" s="18" t="n">
-        <v>0.998320863477407</v>
+        <v>0.998881623192856</v>
       </c>
       <c r="S31" s="19" t="n">
-        <v>0.9990486250003</v>
+        <v>0.994093481732478</v>
       </c>
     </row>
     <row r="32">
@@ -3236,46 +3294,46 @@
         <v>181.025</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>1.94545441491791</v>
+        <v>1.64209946720238</v>
       </c>
       <c r="G32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>180.093944307141</v>
+        <v>179.878170471675</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>179.293152419621</v>
+        <v>179.611727790667</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>176.415122609964</v>
+        <v>177.179940177604</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>179.079545585082</v>
+        <v>179.382900532798</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>179.079545585082</v>
+        <v>179.382900532798</v>
       </c>
       <c r="M32" s="13" t="n">
-        <v>179.078578706954</v>
+        <v>179.024274869318</v>
       </c>
       <c r="N32" s="14" t="n">
-        <v>179.078578706954</v>
+        <v>179.024274869318</v>
       </c>
       <c r="O32" s="15" t="n">
-        <v>0.000991738297537545</v>
+        <v>0.00322050545616903</v>
       </c>
       <c r="P32" s="16" t="n">
-        <v>0.01523702033841</v>
+        <v>0.0163030074444459</v>
       </c>
       <c r="Q32" s="17" t="n">
-        <v>0.00099223023257311</v>
+        <v>0.00322569685534613</v>
       </c>
       <c r="R32" s="18" t="n">
-        <v>0.994362022531664</v>
+        <v>0.995252922574663</v>
       </c>
       <c r="S32" s="19" t="n">
-        <v>0.998803224162372</v>
+        <v>0.996729317575333</v>
       </c>
     </row>
     <row r="33">
@@ -3295,46 +3353,46 @@
         <v>176.741</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>0.10328994610887</v>
+        <v>-0.625398358771956</v>
       </c>
       <c r="G33" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>175.342350858034</v>
+        <v>175.971431730635</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>179.590106592667</v>
+        <v>179.774182320553</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>176.224268067307</v>
+        <v>177.124110426715</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>176.637710053891</v>
+        <v>177.366398358772</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>176.637710053891</v>
+        <v>177.366398358772</v>
       </c>
       <c r="M33" s="13" t="n">
-        <v>175.798436117305</v>
+        <v>176.47911725572</v>
       </c>
       <c r="N33" s="14" t="n">
-        <v>175.798436117305</v>
+        <v>176.47911725572</v>
       </c>
       <c r="O33" s="15" t="n">
-        <v>-0.0184866072982434</v>
+        <v>-0.0143188568992399</v>
       </c>
       <c r="P33" s="16" t="n">
-        <v>0.00739096342513146</v>
+        <v>0.0098538782264832</v>
       </c>
       <c r="Q33" s="17" t="n">
-        <v>-0.0183167781056374</v>
+        <v>-0.0142168296196457</v>
       </c>
       <c r="R33" s="18" t="n">
-        <v>1.00260111294869</v>
+        <v>1.00288504514677</v>
       </c>
       <c r="S33" s="19" t="n">
-        <v>0.978887086002114</v>
+        <v>0.981671088571787</v>
       </c>
     </row>
     <row r="34">
@@ -3354,46 +3412,46 @@
         <v>168.454</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>-2.38477877635707</v>
+        <v>-3.34677177253939</v>
       </c>
       <c r="G34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>173.581249826356</v>
+        <v>175.299384243324</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>179.969369471687</v>
+        <v>179.999532613701</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>176.27803298954</v>
+        <v>177.282744884055</v>
       </c>
       <c r="K34" s="11" t="n">
-        <v>170.838778776357</v>
+        <v>171.800771772539</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>170.838778776357</v>
+        <v>171.800771772539</v>
       </c>
       <c r="M34" s="13" t="n">
-        <v>173.407231995604</v>
+        <v>175.14386178683</v>
       </c>
       <c r="N34" s="14" t="n">
-        <v>173.407231995604</v>
+        <v>175.14386178683</v>
       </c>
       <c r="O34" s="15" t="n">
-        <v>-0.013695318918375</v>
+        <v>-0.00759484997733589</v>
       </c>
       <c r="P34" s="16" t="n">
-        <v>-0.0155239151736063</v>
+        <v>-0.00650282229951338</v>
       </c>
       <c r="Q34" s="17" t="n">
-        <v>-0.0136019646961212</v>
+        <v>-0.0075660819798592</v>
       </c>
       <c r="R34" s="18" t="n">
-        <v>0.998997484861265</v>
+        <v>0.999112818010371</v>
       </c>
       <c r="S34" s="19" t="n">
-        <v>0.963537475875222</v>
+        <v>0.973023980916155</v>
       </c>
     </row>
     <row r="35">
@@ -3413,46 +3471,46 @@
         <v>182.36</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>-0.125354470844568</v>
+        <v>2.66710146287074</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>0.204304076352378</v>
+        <v>0.977495051945642</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>173.47224546539</v>
+        <v>175.898475486138</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>180.436171019089</v>
+        <v>180.289516467908</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>176.647718554378</v>
+        <v>177.703934988658</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>182.485354470845</v>
+        <v>179.692898537129</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>175.313660375813</v>
+        <v>179.60750524347</v>
       </c>
       <c r="M35" s="13" t="n">
-        <v>172.60980150993</v>
+        <v>175.231034622967</v>
       </c>
       <c r="N35" s="14" t="n">
-        <v>172.60980150993</v>
+        <v>175.231034622967</v>
       </c>
       <c r="O35" s="15" t="n">
-        <v>-0.00460920602297828</v>
+        <v>0.000497597509575846</v>
       </c>
       <c r="P35" s="16" t="n">
-        <v>-0.0351661744190638</v>
+        <v>-0.0180310633927416</v>
       </c>
       <c r="Q35" s="17" t="n">
-        <v>-0.00459859993437006</v>
+        <v>0.000497721331753631</v>
       </c>
       <c r="R35" s="18" t="n">
-        <v>0.995028346159087</v>
+        <v>0.996205533553795</v>
       </c>
       <c r="S35" s="19" t="n">
-        <v>0.956625273829763</v>
+        <v>0.971942451541043</v>
       </c>
     </row>
     <row r="36">
@@ -3472,46 +3530,46 @@
         <v>171.866</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>2.89289348826167</v>
+        <v>1.95764376761113</v>
       </c>
       <c r="G36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>168.479879417088</v>
+        <v>170.249121641081</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>180.990034578099</v>
+        <v>180.640747455446</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>177.377429668468</v>
+        <v>178.408362314001</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>168.973106511738</v>
+        <v>169.908356232389</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>168.973106511738</v>
+        <v>169.908356232389</v>
       </c>
       <c r="M36" s="13" t="n">
-        <v>168.518746736665</v>
+        <v>170.368327642134</v>
       </c>
       <c r="N36" s="14" t="n">
-        <v>168.518746736665</v>
+        <v>170.368327642134</v>
       </c>
       <c r="O36" s="15" t="n">
-        <v>-0.0239865642628779</v>
+        <v>-0.0281425745997373</v>
       </c>
       <c r="P36" s="16" t="n">
-        <v>-0.0589675886783132</v>
+        <v>-0.0483506900586685</v>
       </c>
       <c r="Q36" s="17" t="n">
-        <v>-0.0237011730358189</v>
+        <v>-0.0277502611982884</v>
       </c>
       <c r="R36" s="18" t="n">
-        <v>1.00023069413221</v>
+        <v>1.00070018570377</v>
       </c>
       <c r="S36" s="19" t="n">
-        <v>0.931094063435562</v>
+        <v>0.94313342942823</v>
       </c>
     </row>
     <row r="37">
@@ -3531,46 +3589,46 @@
         <v>160.682</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>-0.133113547370722</v>
+        <v>-1.36709286028644</v>
       </c>
       <c r="G37" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>162.599480062384</v>
+        <v>164.038912916932</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>181.627281922789</v>
+        <v>181.049412891573</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>178.504600947565</v>
+        <v>179.426226284836</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>160.815113547371</v>
+        <v>162.049092860286</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>160.815113547371</v>
+        <v>162.049092860286</v>
       </c>
       <c r="M37" s="13" t="n">
-        <v>164.946995400355</v>
+        <v>166.147291926218</v>
       </c>
       <c r="N37" s="14" t="n">
-        <v>164.946995400355</v>
+        <v>166.147291926218</v>
       </c>
       <c r="O37" s="15" t="n">
-        <v>-0.0214228179071664</v>
+        <v>-0.0250880307760927</v>
       </c>
       <c r="P37" s="16" t="n">
-        <v>-0.0617266055183184</v>
+        <v>-0.0585441806949374</v>
       </c>
       <c r="Q37" s="17" t="n">
-        <v>-0.0211949792262057</v>
+        <v>-0.0247759414812231</v>
       </c>
       <c r="R37" s="18" t="n">
-        <v>1.01443740986792</v>
+        <v>1.0128529199066</v>
       </c>
       <c r="S37" s="19" t="n">
-        <v>0.908161998870166</v>
+        <v>0.917690310466352</v>
       </c>
     </row>
     <row r="38">
@@ -3590,46 +3648,46 @@
         <v>166.629</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>-2.55564799494095</v>
+        <v>-3.95362575191154</v>
       </c>
       <c r="G38" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>170.336030484191</v>
+        <v>169.97870645738</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>182.33672424719</v>
+        <v>181.50499234703</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>180.024645391642</v>
+        <v>180.745226295506</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>169.184647994941</v>
+        <v>170.582625751912</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>169.184647994941</v>
+        <v>170.582625751912</v>
       </c>
       <c r="M38" s="13" t="n">
-        <v>171.663072912787</v>
+        <v>171.553686270854</v>
       </c>
       <c r="N38" s="14" t="n">
-        <v>171.663072912787</v>
+        <v>171.553686270854</v>
       </c>
       <c r="O38" s="15" t="n">
-        <v>0.0399094949937651</v>
+        <v>0.032021561401278</v>
       </c>
       <c r="P38" s="16" t="n">
-        <v>-0.0100581680633811</v>
+        <v>-0.0204984375664058</v>
       </c>
       <c r="Q38" s="17" t="n">
-        <v>0.0407165798693738</v>
+        <v>0.0325397680693842</v>
       </c>
       <c r="R38" s="18" t="n">
-        <v>1.00779073238248</v>
+        <v>1.00926574772981</v>
       </c>
       <c r="S38" s="19" t="n">
-        <v>0.941461867440741</v>
+        <v>0.945173375412451</v>
       </c>
     </row>
     <row r="39">
@@ -3649,46 +3707,46 @@
         <v>186.602</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>-0.865882113895329</v>
+        <v>3.60159928069444</v>
       </c>
       <c r="G39" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>185.645958297875</v>
+        <v>183.823530692097</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>183.094165140099</v>
+        <v>181.985090192542</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>181.844528563668</v>
+        <v>182.26617607323</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>187.467882113895</v>
+        <v>183.000400719306</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>187.467882113895</v>
+        <v>183.000400719306</v>
       </c>
       <c r="M39" s="13" t="n">
-        <v>184.372666859394</v>
+        <v>182.900524098828</v>
       </c>
       <c r="N39" s="14" t="n">
-        <v>184.372666859394</v>
+        <v>182.900524098828</v>
       </c>
       <c r="O39" s="15" t="n">
-        <v>0.0714253954042092</v>
+        <v>0.0640461637870245</v>
       </c>
       <c r="P39" s="16" t="n">
-        <v>0.0681471460285936</v>
+        <v>0.0437678718975936</v>
       </c>
       <c r="Q39" s="17" t="n">
-        <v>0.0740380195399628</v>
+        <v>0.0661416147599398</v>
       </c>
       <c r="R39" s="18" t="n">
-        <v>0.993141291896923</v>
+        <v>0.99497884416759</v>
       </c>
       <c r="S39" s="19" t="n">
-        <v>1.0069827551212</v>
+        <v>1.00503026871772</v>
       </c>
     </row>
     <row r="40">
@@ -3708,46 +3766,46 @@
         <v>197.311</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>3.94074478515573</v>
+        <v>2.29233079521018</v>
       </c>
       <c r="G40" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>192.71129990934</v>
+        <v>192.606489790614</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>183.867188142655</v>
+        <v>182.460484319708</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>183.817016039631</v>
+        <v>183.839076342512</v>
       </c>
       <c r="K40" s="11" t="n">
-        <v>193.370255214844</v>
+        <v>195.01866920479</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>193.370255214844</v>
+        <v>195.01866920479</v>
       </c>
       <c r="M40" s="13" t="n">
-        <v>190.904616590158</v>
+        <v>191.045293870863</v>
       </c>
       <c r="N40" s="14" t="n">
-        <v>190.904616590158</v>
+        <v>191.045293870863</v>
       </c>
       <c r="O40" s="15" t="n">
-        <v>0.0348148410377147</v>
+        <v>0.0435681197317889</v>
       </c>
       <c r="P40" s="16" t="n">
-        <v>0.132839047803237</v>
+        <v>0.121366256949839</v>
       </c>
       <c r="Q40" s="17" t="n">
-        <v>0.0354279722804349</v>
+        <v>0.0445311450700607</v>
       </c>
       <c r="R40" s="18" t="n">
-        <v>0.990624922772917</v>
+        <v>0.991894375306626</v>
       </c>
       <c r="S40" s="19" t="n">
-        <v>1.03827452042201</v>
+        <v>1.0470502398542</v>
       </c>
     </row>
     <row r="41">
@@ -3767,46 +3825,46 @@
         <v>188.755</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>-0.655073817049895</v>
+        <v>-2.38843635456752</v>
       </c>
       <c r="G41" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H41" s="8" t="n">
-        <v>190.925998564668</v>
+        <v>192.849068838281</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>184.626110369105</v>
+        <v>182.902587189209</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>185.822990163269</v>
+        <v>185.317598951085</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>189.41007381705</v>
+        <v>191.143436354568</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>189.41007381705</v>
+        <v>191.143436354568</v>
       </c>
       <c r="M41" s="13" t="n">
-        <v>189.8175977433</v>
+        <v>191.509458884028</v>
       </c>
       <c r="N41" s="14" t="n">
-        <v>189.8175977433</v>
+        <v>191.509458884028</v>
       </c>
       <c r="O41" s="15" t="n">
-        <v>-0.00571031455322234</v>
+        <v>0.00242666043278221</v>
       </c>
       <c r="P41" s="16" t="n">
-        <v>0.150779359651743</v>
+        <v>0.152648692998695</v>
       </c>
       <c r="Q41" s="17" t="n">
-        <v>-0.00569404169618526</v>
+        <v>0.00242960715629392</v>
       </c>
       <c r="R41" s="18" t="n">
-        <v>0.994194605084164</v>
+        <v>0.993053583497589</v>
       </c>
       <c r="S41" s="19" t="n">
-        <v>1.02811892296174</v>
+        <v>1.04705713476822</v>
       </c>
     </row>
     <row r="42">
@@ -3826,46 +3884,46 @@
         <v>184.912</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>-2.16798812425516</v>
+        <v>-3.82029362218765</v>
       </c>
       <c r="G42" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>184.247768406567</v>
+        <v>186.787834084949</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>185.347188350617</v>
+        <v>183.290660127278</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>187.791099474197</v>
+        <v>186.611313710992</v>
       </c>
       <c r="K42" s="11" t="n">
-        <v>187.079988124255</v>
+        <v>188.732293622188</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>187.079988124255</v>
+        <v>188.732293622188</v>
       </c>
       <c r="M42" s="13" t="n">
-        <v>185.128782550628</v>
+        <v>188.256477492326</v>
       </c>
       <c r="N42" s="14" t="n">
-        <v>185.128782550628</v>
+        <v>188.256477492326</v>
       </c>
       <c r="O42" s="15" t="n">
-        <v>-0.0250118943834292</v>
+        <v>-0.0171319259733453</v>
       </c>
       <c r="P42" s="16" t="n">
-        <v>0.0784426691737148</v>
+        <v>0.0973618905227218</v>
       </c>
       <c r="Q42" s="17" t="n">
-        <v>-0.0247016886127319</v>
+        <v>-0.0169860089974566</v>
       </c>
       <c r="R42" s="18" t="n">
-        <v>1.00478168149161</v>
+        <v>1.00786262881933</v>
       </c>
       <c r="S42" s="19" t="n">
-        <v>0.998821639529938</v>
+        <v>1.02709258268588</v>
       </c>
     </row>
     <row r="43">
@@ -3885,46 +3943,46 @@
         <v>173.805</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>-1.210414364782</v>
+        <v>4.37941988510076</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>0.684642807332228</v>
+        <v>0</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>181.134398859303</v>
+        <v>184.417886370361</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>186.009668595514</v>
+        <v>183.609114990877</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>189.667927930297</v>
+        <v>187.658919621295</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>175.015414364782</v>
+        <v>169.425580114899</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>176.945080136952</v>
+        <v>184.417886370361</v>
       </c>
       <c r="M43" s="13" t="n">
-        <v>182.56029574269</v>
+        <v>187.216509413466</v>
       </c>
       <c r="N43" s="14" t="n">
-        <v>182.56029574269</v>
+        <v>187.216509413466</v>
       </c>
       <c r="O43" s="15" t="n">
-        <v>-0.0139711987053988</v>
+        <v>-0.00553952361168792</v>
       </c>
       <c r="P43" s="16" t="n">
-        <v>-0.00982993383767561</v>
+        <v>0.0235974464037412</v>
       </c>
       <c r="Q43" s="17" t="n">
-        <v>-0.0138740544422652</v>
+        <v>-0.0055242087428411</v>
       </c>
       <c r="R43" s="18" t="n">
-        <v>1.00787203806879</v>
+        <v>1.01517544256789</v>
       </c>
       <c r="S43" s="19" t="n">
-        <v>0.981455948613485</v>
+        <v>1.01964714236964</v>
       </c>
     </row>
     <row r="44">
@@ -3944,46 +4002,46 @@
         <v>193.59</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>4.31896542739741</v>
+        <v>2.29202870904416</v>
       </c>
       <c r="G44" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>188.283869327204</v>
+        <v>191.699355010717</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>186.593880611976</v>
+        <v>183.845764657902</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>191.396503932703</v>
+        <v>188.409720580612</v>
       </c>
       <c r="K44" s="11" t="n">
-        <v>189.271034572603</v>
+        <v>191.297971290956</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>189.271034572603</v>
+        <v>191.297971290956</v>
       </c>
       <c r="M44" s="13" t="n">
-        <v>188.231408557127</v>
+        <v>191.983625493482</v>
       </c>
       <c r="N44" s="14" t="n">
-        <v>188.231408557127</v>
+        <v>191.983625493482</v>
       </c>
       <c r="O44" s="15" t="n">
-        <v>0.0305915963905394</v>
+        <v>0.0251443330366729</v>
       </c>
       <c r="P44" s="16" t="n">
-        <v>-0.0140028464516925</v>
+        <v>0.00491156627628575</v>
       </c>
       <c r="Q44" s="17" t="n">
-        <v>0.0310643274944626</v>
+        <v>0.0254631180495299</v>
       </c>
       <c r="R44" s="18" t="n">
-        <v>0.999721374060007</v>
+        <v>1.00148289743985</v>
       </c>
       <c r="S44" s="19" t="n">
-        <v>1.00877589307742</v>
+        <v>1.04426460871004</v>
       </c>
     </row>
     <row r="45">
@@ -4003,46 +4061,46 @@
         <v>209.016</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>-1.95416668681902</v>
+        <v>-3.95827330422656</v>
       </c>
       <c r="G45" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H45" s="8" t="n">
-        <v>197.438484946352</v>
+        <v>200.920673021657</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>187.074488540399</v>
+        <v>183.988927488361</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>192.856241643581</v>
+        <v>188.796815321305</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>210.970166686819</v>
+        <v>212.974273304227</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>197.438484946352</v>
+        <v>200.920673021657</v>
       </c>
       <c r="M45" s="13" t="n">
-        <v>195.367178772454</v>
+        <v>198.093038701128</v>
       </c>
       <c r="N45" s="14" t="n">
-        <v>195.367178772454</v>
+        <v>198.093038701128</v>
       </c>
       <c r="O45" s="15" t="n">
-        <v>0.0372086535872184</v>
+        <v>0.0313267282568075</v>
       </c>
       <c r="P45" s="16" t="n">
-        <v>0.0292363884862734</v>
+        <v>0.0343773088570356</v>
       </c>
       <c r="Q45" s="17" t="n">
-        <v>0.037909561799625</v>
+        <v>0.0318225744093634</v>
       </c>
       <c r="R45" s="18" t="n">
-        <v>0.989509106218776</v>
+        <v>0.985926613334487</v>
       </c>
       <c r="S45" s="19" t="n">
-        <v>1.04432827958936</v>
+        <v>1.07665739131861</v>
       </c>
     </row>
     <row r="46">
@@ -4062,46 +4120,46 @@
         <v>196.596</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>-0.724710624509793</v>
+        <v>-2.63683747024258</v>
       </c>
       <c r="G46" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>198.09305428712</v>
+        <v>200.233615722232</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>187.427829742402</v>
+        <v>184.031579471408</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>193.915927878299</v>
+        <v>188.76774382929</v>
       </c>
       <c r="K46" s="11" t="n">
-        <v>197.32071062451</v>
+        <v>199.232837470243</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>197.32071062451</v>
+        <v>199.232837470243</v>
       </c>
       <c r="M46" s="13" t="n">
-        <v>197.918589287808</v>
+        <v>198.223551067469</v>
       </c>
       <c r="N46" s="14" t="n">
-        <v>197.918589287808</v>
+        <v>198.223551067469</v>
       </c>
       <c r="O46" s="15" t="n">
-        <v>0.0129750248643443</v>
+        <v>0.000658626837370689</v>
       </c>
       <c r="P46" s="16" t="n">
-        <v>0.0690859981952443</v>
+        <v>0.052944120212538</v>
       </c>
       <c r="Q46" s="17" t="n">
-        <v>0.0130595657437731</v>
+        <v>0.00065884377965153</v>
       </c>
       <c r="R46" s="18" t="n">
-        <v>0.999119277553979</v>
+        <v>0.989961402597096</v>
       </c>
       <c r="S46" s="19" t="n">
-        <v>1.0559722617491</v>
+        <v>1.07711704500295</v>
       </c>
     </row>
     <row r="47">
@@ -4121,46 +4179,46 @@
         <v>198.82</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>-0.77445095586221</v>
+        <v>5.3121436922676</v>
       </c>
       <c r="G47" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H47" s="8" t="n">
-        <v>200.941255880808</v>
+        <v>192.677258651057</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>187.636719077358</v>
+        <v>183.977278937156</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>194.467260668736</v>
+        <v>188.330665378982</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>199.594450955862</v>
+        <v>193.507856307732</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>199.594450955862</v>
+        <v>193.507856307732</v>
       </c>
       <c r="M47" s="13" t="n">
-        <v>202.211850139525</v>
+        <v>193.379946396435</v>
       </c>
       <c r="N47" s="14" t="n">
-        <v>202.211850139525</v>
+        <v>193.379946396435</v>
       </c>
       <c r="O47" s="15" t="n">
-        <v>0.021460129970532</v>
+        <v>-0.0247385517345196</v>
       </c>
       <c r="P47" s="16" t="n">
-        <v>0.107644185812081</v>
+        <v>0.0329214394728203</v>
       </c>
       <c r="Q47" s="17" t="n">
-        <v>0.0216920546329951</v>
+        <v>-0.0244350615502066</v>
       </c>
       <c r="R47" s="18" t="n">
-        <v>1.00632321248888</v>
+        <v>1.00364696773401</v>
       </c>
       <c r="S47" s="19" t="n">
-        <v>1.07767739243063</v>
+        <v>1.05110776457614</v>
       </c>
     </row>
     <row r="48">
@@ -4168,58 +4226,58 @@
         <v>98</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>215.841377232835</v>
+        <v>188.675</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>215.841377232835</v>
+        <v>188.675</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>215.841377232835</v>
+        <v>188.675</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>215.841377232835</v>
+        <v>188.675</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>3.50358921096978</v>
+        <v>1.40376449996935</v>
       </c>
       <c r="G48" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>213.083182590193</v>
+        <v>190.054405699985</v>
       </c>
       <c r="I48" s="9" t="n">
-        <v>187.690154455192</v>
+        <v>183.839085001965</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>194.418961960503</v>
+        <v>187.546064713003</v>
       </c>
       <c r="K48" s="11" t="n">
-        <v>212.337788021865</v>
+        <v>187.271235500031</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>212.337788021865</v>
+        <v>187.271235500031</v>
       </c>
       <c r="M48" s="13" t="n">
-        <v>211.894162133538</v>
+        <v>190.235079279541</v>
       </c>
       <c r="N48" s="14" t="n">
-        <v>211.894162133538</v>
+        <v>190.235079279541</v>
       </c>
       <c r="O48" s="15" t="n">
-        <v>0.0467710038930725</v>
+        <v>-0.0163963211105793</v>
       </c>
       <c r="P48" s="16" t="n">
-        <v>0.125710973305653</v>
+        <v>-0.00910778827854375</v>
       </c>
       <c r="Q48" s="17" t="n">
-        <v>0.0478820206992425</v>
+        <v>-0.0162626330987129</v>
       </c>
       <c r="R48" s="18" t="n">
-        <v>0.994419923514368</v>
+        <v>1.00095064136446</v>
       </c>
       <c r="S48" s="19" t="n">
-        <v>1.12895725803307</v>
+        <v>1.03479126474932</v>
       </c>
     </row>
     <row r="49">
@@ -4227,58 +4285,58 @@
         <v>99</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>219.761148615733</v>
+        <v>187.299</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>219.761148615733</v>
+        <v>187.299</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>219.761148615733</v>
+        <v>187.299</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>219.761148615733</v>
+        <v>187.299</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>-3.5454729188252</v>
+        <v>-5.59098981036842</v>
       </c>
       <c r="G49" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H49" s="8" t="n">
-        <v>220.72343440622</v>
+        <v>189.773411039277</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>187.584607368255</v>
+        <v>183.636013393053</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>193.705389650648</v>
+        <v>186.500312528618</v>
       </c>
       <c r="K49" s="11" t="n">
-        <v>223.306621534558</v>
+        <v>192.889989810368</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>223.306621534558</v>
+        <v>192.889989810368</v>
       </c>
       <c r="M49" s="13" t="n">
-        <v>217.264079543981</v>
+        <v>189.469555409415</v>
       </c>
       <c r="N49" s="14" t="n">
-        <v>217.264079543981</v>
+        <v>189.469555409415</v>
       </c>
       <c r="O49" s="15" t="n">
-        <v>0.0250266552796268</v>
+        <v>-0.00403221260629185</v>
       </c>
       <c r="P49" s="16" t="n">
-        <v>0.112080754347335</v>
+        <v>-0.0435324903300829</v>
       </c>
       <c r="Q49" s="17" t="n">
-        <v>0.0253424509499205</v>
+        <v>-0.0040240941524835</v>
       </c>
       <c r="R49" s="18" t="n">
-        <v>0.984327197193426</v>
+        <v>0.998398850354228</v>
       </c>
       <c r="S49" s="19" t="n">
-        <v>1.15821912358439</v>
+        <v>1.03176687354825</v>
       </c>
     </row>
     <row r="50">
@@ -4286,58 +4344,58 @@
         <v>100</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>210.994764990349</v>
+        <v>183.9625</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>210.994764990349</v>
+        <v>183.9625</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>210.994764990349</v>
+        <v>183.9625</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>210.994764990349</v>
+        <v>183.9625</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>0.88947790540547</v>
+        <v>-0.864506516890492</v>
       </c>
       <c r="G50" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H50" s="8" t="n">
-        <v>208.618468153461</v>
+        <v>185.628548718244</v>
       </c>
       <c r="I50" s="9" t="n">
-        <v>187.331954079873</v>
+        <v>183.389224931701</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>192.350495766523</v>
+        <v>185.278405377027</v>
       </c>
       <c r="K50" s="11" t="n">
-        <v>210.105287084944</v>
+        <v>184.82700651689</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>210.105287084944</v>
+        <v>184.82700651689</v>
       </c>
       <c r="M50" s="13" t="n">
-        <v>207.258966119556</v>
+        <v>185.633502608475</v>
       </c>
       <c r="N50" s="14" t="n">
-        <v>207.258966119556</v>
+        <v>185.633502608475</v>
       </c>
       <c r="O50" s="15" t="n">
-        <v>-0.0471445146554414</v>
+        <v>-0.0204540403394639</v>
       </c>
       <c r="P50" s="16" t="n">
-        <v>0.0471930244923331</v>
+        <v>-0.0635143926702655</v>
       </c>
       <c r="Q50" s="17" t="n">
-        <v>-0.0460504720588203</v>
+        <v>-0.0202462754116375</v>
       </c>
       <c r="R50" s="18" t="n">
-        <v>0.99348330928734</v>
+        <v>1.00002668711394</v>
       </c>
       <c r="S50" s="19" t="n">
-        <v>1.10637273356571</v>
+        <v>1.01223778374989</v>
       </c>
     </row>
     <row r="51">
@@ -4357,46 +4415,46 @@
         <v>186.559</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>1.04033122622199</v>
+        <v>6.56899241024942</v>
       </c>
       <c r="G51" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H51" s="8" t="n">
-        <v>190.216506546129</v>
+        <v>182.331484046181</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>186.96639711223</v>
+        <v>183.125664174448</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>190.526238494902</v>
+        <v>183.997288195838</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>185.518668773778</v>
+        <v>179.990007589751</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>185.518668773778</v>
+        <v>179.990007589751</v>
       </c>
       <c r="M51" s="13" t="n">
-        <v>190.930833290772</v>
+        <v>182.294373821645</v>
       </c>
       <c r="N51" s="14" t="n">
-        <v>190.930833290772</v>
+        <v>182.294373821645</v>
       </c>
       <c r="O51" s="15" t="n">
-        <v>-0.0820578223233734</v>
+        <v>-0.018151494793879</v>
       </c>
       <c r="P51" s="16" t="n">
-        <v>-0.0557881095542584</v>
+        <v>-0.057325347231527</v>
       </c>
       <c r="Q51" s="17" t="n">
-        <v>-0.0787813098486916</v>
+        <v>-0.0179877486547934</v>
       </c>
       <c r="R51" s="18" t="n">
-        <v>1.00375533521046</v>
+        <v>0.999796468367872</v>
       </c>
       <c r="S51" s="19" t="n">
-        <v>1.02120400371283</v>
+        <v>0.995460546960738</v>
       </c>
     </row>
     <row r="52">
@@ -4416,46 +4474,46 @@
         <v>183.76</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>1.17929146941279</v>
+        <v>-0.610473590187663</v>
       </c>
       <c r="G52" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>178.854001180379</v>
+        <v>180.478279666829</v>
       </c>
       <c r="I52" s="9" t="n">
-        <v>186.536372320635</v>
+        <v>182.873174291326</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>188.493349979151</v>
+        <v>182.77164892836</v>
       </c>
       <c r="K52" s="11" t="n">
-        <v>182.580708530587</v>
+        <v>184.370473590188</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>182.580708530587</v>
+        <v>184.370473590188</v>
       </c>
       <c r="M52" s="13" t="n">
-        <v>180.25633944791</v>
+        <v>180.200540122641</v>
       </c>
       <c r="N52" s="14" t="n">
-        <v>180.25633944791</v>
+        <v>180.200540122641</v>
       </c>
       <c r="O52" s="15" t="n">
-        <v>-0.0575312872402643</v>
+        <v>-0.0115524764915431</v>
       </c>
       <c r="P52" s="16" t="n">
-        <v>-0.149309553255597</v>
+        <v>-0.0527481009018034</v>
       </c>
       <c r="Q52" s="17" t="n">
-        <v>-0.0559076481199096</v>
+        <v>-0.0114860028595981</v>
       </c>
       <c r="R52" s="18" t="n">
-        <v>1.00784068714301</v>
+        <v>0.998461091580101</v>
       </c>
       <c r="S52" s="19" t="n">
-        <v>0.966333467330811</v>
+        <v>0.985385313187449</v>
       </c>
     </row>
     <row r="53">
@@ -4475,46 +4533,46 @@
         <v>165.582</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>-4.76327195668843</v>
+        <v>-6.48920572043718</v>
       </c>
       <c r="G53" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H53" s="8" t="n">
-        <v>171.775081148474</v>
+        <v>174.189251096484</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>186.089410730187</v>
+        <v>182.657638666998</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>186.487524514028</v>
+        <v>181.696139114871</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>170.345271956688</v>
+        <v>172.071205720437</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>170.345271956688</v>
+        <v>172.071205720437</v>
       </c>
       <c r="M53" s="13" t="n">
-        <v>172.972920490525</v>
+        <v>174.678966149646</v>
       </c>
       <c r="N53" s="14" t="n">
-        <v>172.972920490525</v>
+        <v>174.678966149646</v>
       </c>
       <c r="O53" s="15" t="n">
-        <v>-0.0412448925646635</v>
+        <v>-0.0311205324596286</v>
       </c>
       <c r="P53" s="16" t="n">
-        <v>-0.203858636671186</v>
+        <v>-0.07806314438121</v>
       </c>
       <c r="Q53" s="17" t="n">
-        <v>-0.0404058962902091</v>
+        <v>-0.0306412731573233</v>
       </c>
       <c r="R53" s="18" t="n">
-        <v>1.00697330098197</v>
+        <v>1.00281139651315</v>
       </c>
       <c r="S53" s="19" t="n">
-        <v>0.929515117554543</v>
+        <v>0.956318976991165</v>
       </c>
     </row>
     <row r="54">
@@ -4534,46 +4592,46 @@
         <v>171.329</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>2.70857048186305</v>
+        <v>1.12602043247919</v>
       </c>
       <c r="G54" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H54" s="8" t="n">
-        <v>170.442247075622</v>
+        <v>171.401577507189</v>
       </c>
       <c r="I54" s="9" t="n">
-        <v>185.670571076116</v>
+        <v>182.505876498194</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v>184.714893187051</v>
+        <v>180.873404418956</v>
       </c>
       <c r="K54" s="11" t="n">
-        <v>168.620429518137</v>
+        <v>170.202979567521</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>168.620429518137</v>
+        <v>170.202979567521</v>
       </c>
       <c r="M54" s="13" t="n">
-        <v>170.672756613548</v>
+        <v>171.920545822755</v>
       </c>
       <c r="N54" s="14" t="n">
-        <v>170.672756613548</v>
+        <v>171.920545822755</v>
       </c>
       <c r="O54" s="15" t="n">
-        <v>-0.0133870342720672</v>
+        <v>-0.0159173828670593</v>
       </c>
       <c r="P54" s="16" t="n">
-        <v>-0.176524133990436</v>
+        <v>-0.0738711309813653</v>
       </c>
       <c r="Q54" s="17" t="n">
-        <v>-0.0132978264485215</v>
+        <v>-0.0157913708083657</v>
       </c>
       <c r="R54" s="18" t="n">
-        <v>1.00135242020028</v>
+        <v>1.003027791944</v>
       </c>
       <c r="S54" s="19" t="n">
-        <v>0.919223523816173</v>
+        <v>0.942000055677417</v>
       </c>
     </row>
     <row r="55">
@@ -4593,46 +4651,46 @@
         <v>196.137</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>2.8953571025364</v>
+        <v>7.30863891930882</v>
       </c>
       <c r="G55" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H55" s="8" t="n">
-        <v>175.104895461231</v>
+        <v>175.20501843554</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>185.315072006918</v>
+        <v>182.438090461048</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>183.30087582295</v>
+        <v>180.357965837232</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>193.241642897464</v>
+        <v>188.828361080691</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>175.104895461231</v>
+        <v>175.20501843554</v>
       </c>
       <c r="M55" s="13" t="n">
-        <v>173.015762851749</v>
+        <v>173.777241359934</v>
       </c>
       <c r="N55" s="14" t="n">
-        <v>173.015762851749</v>
+        <v>173.777241359934</v>
       </c>
       <c r="O55" s="15" t="n">
-        <v>0.0136346860798034</v>
+        <v>0.0107418297668182</v>
       </c>
       <c r="P55" s="16" t="n">
-        <v>-0.0938301589651545</v>
+        <v>-0.0467218613671752</v>
       </c>
       <c r="Q55" s="17" t="n">
-        <v>0.0137280623146327</v>
+        <v>0.0107997303538891</v>
       </c>
       <c r="R55" s="18" t="n">
-        <v>0.988069250696967</v>
+        <v>0.991850820893402</v>
       </c>
       <c r="S55" s="19" t="n">
-        <v>0.933630281541752</v>
+        <v>0.952527188378111</v>
       </c>
     </row>
     <row r="56">
@@ -4652,46 +4710,46 @@
         <v>171.817</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>-1.41583096639817</v>
+        <v>-2.6789490011348</v>
       </c>
       <c r="G56" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>172.08195265082</v>
+        <v>173.229885304634</v>
       </c>
       <c r="I56" s="9" t="n">
-        <v>185.047475832617</v>
+        <v>182.466793921115</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>182.290419928111</v>
+        <v>180.150992242055</v>
       </c>
       <c r="K56" s="11" t="n">
-        <v>173.232830966398</v>
+        <v>174.495949001135</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>173.232830966398</v>
+        <v>174.495949001135</v>
       </c>
       <c r="M56" s="13" t="n">
-        <v>171.936016296195</v>
+        <v>173.358473184092</v>
       </c>
       <c r="N56" s="14" t="n">
-        <v>171.936016296195</v>
+        <v>173.358473184092</v>
       </c>
       <c r="O56" s="15" t="n">
-        <v>-0.0062602957700834</v>
+        <v>-0.0024127069698662</v>
       </c>
       <c r="P56" s="16" t="n">
-        <v>-0.0461582831272316</v>
+        <v>-0.0379691810795482</v>
       </c>
       <c r="Q56" s="17" t="n">
-        <v>-0.00624074094612559</v>
+        <v>-0.00240979873178393</v>
       </c>
       <c r="R56" s="18" t="n">
-        <v>0.999151936897643</v>
+        <v>1.00074229616461</v>
       </c>
       <c r="S56" s="19" t="n">
-        <v>0.929145428882899</v>
+        <v>0.950082310642444</v>
       </c>
     </row>
     <row r="57">
@@ -4711,46 +4769,46 @@
         <v>159.256</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>-5.64408408681493</v>
+        <v>-6.93631740759734</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>0.779041695615327</v>
+        <v>0.56645375296775</v>
       </c>
       <c r="H57" s="8" t="n">
-        <v>170.66326962304</v>
+        <v>173.215002788458</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>184.885963502895</v>
+        <v>182.599979573933</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>181.687493107109</v>
+        <v>180.227887768774</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>164.900084086815</v>
+        <v>166.192317407597</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>166.173507790754</v>
+        <v>169.236976298558</v>
       </c>
       <c r="M57" s="13" t="n">
-        <v>172.578354361126</v>
+        <v>174.694452251535</v>
       </c>
       <c r="N57" s="14" t="n">
-        <v>172.578354361126</v>
+        <v>174.694452251535</v>
       </c>
       <c r="O57" s="15" t="n">
-        <v>0.00372895219446961</v>
+        <v>0.00767691078641316</v>
       </c>
       <c r="P57" s="16" t="n">
-        <v>-0.00228108612770261</v>
+        <v>0.0000886546458969129</v>
       </c>
       <c r="Q57" s="17" t="n">
-        <v>0.00373591338666546</v>
+        <v>0.007706453817373</v>
       </c>
       <c r="R57" s="18" t="n">
-        <v>1.01122142299463</v>
+        <v>1.00854111618082</v>
       </c>
       <c r="S57" s="19" t="n">
-        <v>0.933431349202581</v>
+        <v>0.956705760094587</v>
       </c>
     </row>
     <row r="58">
@@ -4770,46 +4828,46 @@
         <v>189.021</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>4.28742910340086</v>
+        <v>3.2130925921089</v>
       </c>
       <c r="G58" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H58" s="8" t="n">
-        <v>184.296698674969</v>
+        <v>184.790503485975</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>184.84133181439</v>
+        <v>182.840658336964</v>
       </c>
       <c r="J58" s="10" t="n">
-        <v>181.450775019715</v>
+        <v>180.535781336534</v>
       </c>
       <c r="K58" s="11" t="n">
-        <v>184.733570896599</v>
+        <v>185.807907407891</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>184.733570896599</v>
+        <v>185.807907407891</v>
       </c>
       <c r="M58" s="13" t="n">
-        <v>183.568919766548</v>
+        <v>184.180061117979</v>
       </c>
       <c r="N58" s="14" t="n">
-        <v>183.568919766548</v>
+        <v>184.180061117979</v>
       </c>
       <c r="O58" s="15" t="n">
-        <v>0.061738820017783</v>
+        <v>0.0528754113540981</v>
       </c>
       <c r="P58" s="16" t="n">
-        <v>0.0755607597186745</v>
+        <v>0.0713091924909492</v>
       </c>
       <c r="Q58" s="17" t="n">
-        <v>0.0636844953476856</v>
+        <v>0.0542982833409347</v>
       </c>
       <c r="R58" s="18" t="n">
-        <v>0.996051047503005</v>
+        <v>0.996696570676086</v>
       </c>
       <c r="S58" s="19" t="n">
-        <v>0.993116193032413</v>
+        <v>1.00732551935219</v>
       </c>
     </row>
     <row r="59">
@@ -4829,46 +4887,46 @@
         <v>203.006</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>4.37097051775792</v>
+        <v>7.1385466424255</v>
       </c>
       <c r="G59" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H59" s="8" t="n">
-        <v>194.207078365186</v>
+        <v>192.894662538633</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>184.912682278925</v>
+        <v>183.183489250625</v>
       </c>
       <c r="J59" s="10" t="n">
-        <v>181.461375399114</v>
+        <v>180.966847307127</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>198.635029482242</v>
+        <v>195.867453357575</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>198.635029482242</v>
+        <v>195.867453357575</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>191.742486453939</v>
+        <v>190.786516561236</v>
       </c>
       <c r="N59" s="14" t="n">
-        <v>191.742486453939</v>
+        <v>190.786516561236</v>
       </c>
       <c r="O59" s="15" t="n">
-        <v>0.0435630738670751</v>
+        <v>0.0352412164675701</v>
       </c>
       <c r="P59" s="16" t="n">
-        <v>0.10823709524222</v>
+        <v>0.0978797630126458</v>
       </c>
       <c r="Q59" s="17" t="n">
-        <v>0.0445258745205106</v>
+        <v>0.0358695474589139</v>
       </c>
       <c r="R59" s="18" t="n">
-        <v>0.987309464042232</v>
+        <v>0.989070998908665</v>
       </c>
       <c r="S59" s="19" t="n">
-        <v>1.03693529340898</v>
+        <v>1.04150498138077</v>
       </c>
     </row>
     <row r="60">
@@ -4888,46 +4946,46 @@
         <v>181.525</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>-3.44131595467465</v>
+        <v>-4.07825212190228</v>
       </c>
       <c r="G60" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H60" s="8" t="n">
-        <v>187.625414759017</v>
+        <v>187.262708483368</v>
       </c>
       <c r="I60" s="9" t="n">
-        <v>185.099049057745</v>
+        <v>183.624985886</v>
       </c>
       <c r="J60" s="10" t="n">
-        <v>181.616817957878</v>
+        <v>181.439620672705</v>
       </c>
       <c r="K60" s="11" t="n">
-        <v>184.966315954675</v>
+        <v>185.603252121902</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>184.966315954675</v>
+        <v>185.603252121902</v>
       </c>
       <c r="M60" s="13" t="n">
-        <v>187.333460331443</v>
+        <v>187.148816344954</v>
       </c>
       <c r="N60" s="14" t="n">
-        <v>187.333460331443</v>
+        <v>187.148816344954</v>
       </c>
       <c r="O60" s="15" t="n">
-        <v>-0.0232630162551175</v>
+        <v>-0.0192509789014974</v>
       </c>
       <c r="P60" s="16" t="n">
-        <v>0.0895533371479462</v>
+        <v>0.0795481346113236</v>
       </c>
       <c r="Q60" s="17" t="n">
-        <v>-0.0229945183461228</v>
+        <v>-0.0190668621758421</v>
       </c>
       <c r="R60" s="18" t="n">
-        <v>0.998443950527977</v>
+        <v>0.999391805558422</v>
       </c>
       <c r="S60" s="19" t="n">
-        <v>1.01207143572629</v>
+        <v>1.01919036476409</v>
       </c>
     </row>
     <row r="61">
@@ -4947,46 +5005,46 @@
         <v>174.433</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>-6.33317993418127</v>
+        <v>-7.08830777843496</v>
       </c>
       <c r="G61" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H61" s="8" t="n">
-        <v>181.950045328435</v>
+        <v>183.059688116693</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>185.4080427791</v>
+        <v>184.169589291743</v>
       </c>
       <c r="J61" s="10" t="n">
-        <v>181.900494678993</v>
+        <v>181.94713945567</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>180.766179934181</v>
+        <v>181.521307778435</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>180.766179934181</v>
+        <v>181.521307778435</v>
       </c>
       <c r="M61" s="13" t="n">
-        <v>183.339413405998</v>
+        <v>184.043319218742</v>
       </c>
       <c r="N61" s="14" t="n">
-        <v>183.339413405998</v>
+        <v>184.043319218742</v>
       </c>
       <c r="O61" s="15" t="n">
-        <v>-0.0215510861099977</v>
+        <v>-0.0167329492613317</v>
       </c>
       <c r="P61" s="16" t="n">
-        <v>0.0623546277556553</v>
+        <v>0.0535155343899876</v>
       </c>
       <c r="Q61" s="17" t="n">
-        <v>-0.0213205207354786</v>
+        <v>-0.0165937310577855</v>
       </c>
       <c r="R61" s="18" t="n">
-        <v>1.00763598643273</v>
+        <v>1.00537328077071</v>
       </c>
       <c r="S61" s="19" t="n">
-        <v>0.98884282827166</v>
+        <v>0.999314381524735</v>
       </c>
     </row>
     <row r="62">
@@ -5006,46 +5064,46 @@
         <v>192.638</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>5.77902219904645</v>
+        <v>5.11059080380243</v>
       </c>
       <c r="G62" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H62" s="8" t="n">
-        <v>185.779330804006</v>
+        <v>185.912126001736</v>
       </c>
       <c r="I62" s="9" t="n">
-        <v>185.847191113047</v>
+        <v>184.822976932902</v>
       </c>
       <c r="J62" s="10" t="n">
-        <v>182.312545035429</v>
+        <v>182.503259835669</v>
       </c>
       <c r="K62" s="11" t="n">
-        <v>186.858977800954</v>
+        <v>187.527409196198</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>186.858977800954</v>
+        <v>187.527409196198</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>185.607520573097</v>
+        <v>185.788049083025</v>
       </c>
       <c r="N62" s="14" t="n">
-        <v>185.607520573097</v>
+        <v>185.788049083025</v>
       </c>
       <c r="O62" s="15" t="n">
-        <v>0.0122951868191556</v>
+        <v>0.00943534247021432</v>
       </c>
       <c r="P62" s="16" t="n">
-        <v>0.0111053701745456</v>
+        <v>0.00873052140001174</v>
       </c>
       <c r="Q62" s="17" t="n">
-        <v>0.0123710833637127</v>
+        <v>0.00947999564281088</v>
       </c>
       <c r="R62" s="18" t="n">
-        <v>0.999075191894787</v>
+        <v>0.99933260448697</v>
       </c>
       <c r="S62" s="19" t="n">
-        <v>0.998710389226145</v>
+        <v>1.00522160267158</v>
       </c>
     </row>
     <row r="63">
@@ -5065,46 +5123,46 @@
         <v>192.737</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>4.79105324369856</v>
+        <v>6.16092983873176</v>
       </c>
       <c r="G63" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H63" s="8" t="n">
-        <v>186.0947402298</v>
+        <v>185.500079404621</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>186.42112056537</v>
+        <v>185.589171098582</v>
       </c>
       <c r="J63" s="10" t="n">
-        <v>182.847436926435</v>
+        <v>183.119708833965</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>187.945946756301</v>
+        <v>186.576070161268</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>187.945946756301</v>
+        <v>186.576070161268</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>186.54573979457</v>
+        <v>186.074993180521</v>
       </c>
       <c r="N63" s="14" t="n">
-        <v>186.54573979457</v>
+        <v>186.074993180521</v>
       </c>
       <c r="O63" s="15" t="n">
-        <v>0.00504212274394855</v>
+        <v>0.00154327869045984</v>
       </c>
       <c r="P63" s="16" t="n">
-        <v>-0.0271027394891851</v>
+        <v>-0.0246952639297378</v>
       </c>
       <c r="Q63" s="17" t="n">
-        <v>0.00505485563610453</v>
+        <v>0.0015444701578613</v>
       </c>
       <c r="R63" s="18" t="n">
-        <v>1.00242349442124</v>
+        <v>1.00309926431161</v>
       </c>
       <c r="S63" s="19" t="n">
-        <v>1.00066848235233</v>
+        <v>1.00261772860487</v>
       </c>
     </row>
     <row r="64">
@@ -5124,46 +5182,46 @@
         <v>178.853</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>-4.57908786472255</v>
+        <v>-4.76742320334839</v>
       </c>
       <c r="G64" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H64" s="8" t="n">
-        <v>189.051478934268</v>
+        <v>188.85700792939</v>
       </c>
       <c r="I64" s="9" t="n">
-        <v>187.135090008529</v>
+        <v>186.47388434805</v>
       </c>
       <c r="J64" s="10" t="n">
-        <v>183.522370415082</v>
+        <v>183.833334218623</v>
       </c>
       <c r="K64" s="11" t="n">
-        <v>183.432087864723</v>
+        <v>183.620423203348</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>183.432087864723</v>
+        <v>183.620423203348</v>
       </c>
       <c r="M64" s="13" t="n">
-        <v>188.186048628393</v>
+        <v>188.021121693136</v>
       </c>
       <c r="N64" s="14" t="n">
-        <v>188.186048628393</v>
+        <v>188.021121693136</v>
       </c>
       <c r="O64" s="15" t="n">
-        <v>0.00875463123801744</v>
+        <v>0.0104045243539124</v>
       </c>
       <c r="P64" s="16" t="n">
-        <v>0.00455117999443821</v>
+        <v>0.00466102519491329</v>
       </c>
       <c r="Q64" s="17" t="n">
-        <v>0.00879306509829259</v>
+        <v>0.0104588396288525</v>
       </c>
       <c r="R64" s="18" t="n">
-        <v>0.995422250538562</v>
+        <v>0.995573972893995</v>
       </c>
       <c r="S64" s="19" t="n">
-        <v>1.00561604250606</v>
+        <v>1.00829734067317</v>
       </c>
     </row>
     <row r="65">
@@ -5183,46 +5241,46 @@
         <v>191.494</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>-6.44007202782359</v>
+        <v>-6.77357020457712</v>
       </c>
       <c r="G65" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H65" s="8" t="n">
-        <v>191.648025773173</v>
+        <v>191.772603489531</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>187.995311331354</v>
+        <v>187.48344605249</v>
       </c>
       <c r="J65" s="10" t="n">
-        <v>184.380038113597</v>
+        <v>184.698265564344</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>197.934072027824</v>
+        <v>198.267570204577</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>197.934072027824</v>
+        <v>198.267570204577</v>
       </c>
       <c r="M65" s="13" t="n">
-        <v>190.06051847678</v>
+        <v>190.039983271679</v>
       </c>
       <c r="N65" s="14" t="n">
-        <v>190.06051847678</v>
+        <v>190.039983271679</v>
       </c>
       <c r="O65" s="15" t="n">
-        <v>0.00991144590081767</v>
+        <v>0.0106801823426594</v>
       </c>
       <c r="P65" s="16" t="n">
-        <v>0.0366593573412344</v>
+        <v>0.0325828944967554</v>
       </c>
       <c r="Q65" s="17" t="n">
-        <v>0.00996072696169614</v>
+        <v>0.010737419074857</v>
       </c>
       <c r="R65" s="18" t="n">
-        <v>0.991716547613846</v>
+        <v>0.990965235980925</v>
       </c>
       <c r="S65" s="19" t="n">
-        <v>1.0109854183639</v>
+        <v>1.01363606906646</v>
       </c>
     </row>
     <row r="66">
@@ -5242,46 +5300,46 @@
         <v>202.1</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>6.42007138117874</v>
+        <v>6.12532926591473</v>
       </c>
       <c r="G66" s="7" t="n">
-        <v>0.0404771296907236</v>
+        <v>0</v>
       </c>
       <c r="H66" s="8" t="n">
-        <v>180.320121064345</v>
+        <v>180.004369474215</v>
       </c>
       <c r="I66" s="9" t="n">
-        <v>189.005682046337</v>
+        <v>188.622402169867</v>
       </c>
       <c r="J66" s="10" t="n">
-        <v>185.462681221449</v>
+        <v>185.767567890753</v>
       </c>
       <c r="K66" s="11" t="n">
-        <v>195.679928618821</v>
+        <v>195.974670734085</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>180.941841986752</v>
+        <v>180.004369474215</v>
       </c>
       <c r="M66" s="13" t="n">
-        <v>181.079918318769</v>
+        <v>180.64696798256</v>
       </c>
       <c r="N66" s="14" t="n">
-        <v>181.079918318769</v>
+        <v>180.64696798256</v>
       </c>
       <c r="O66" s="15" t="n">
-        <v>-0.0484040682536383</v>
+        <v>-0.0506898147733442</v>
       </c>
       <c r="P66" s="16" t="n">
-        <v>-0.0243934202684714</v>
+        <v>-0.0276717535161095</v>
       </c>
       <c r="Q66" s="17" t="n">
-        <v>-0.0472512662281759</v>
+        <v>-0.049426521342569</v>
       </c>
       <c r="R66" s="18" t="n">
-        <v>1.00421360217562</v>
+        <v>1.0035699050541</v>
       </c>
       <c r="S66" s="19" t="n">
-        <v>0.958066002874851</v>
+        <v>0.957717460410006</v>
       </c>
     </row>
     <row r="67">
@@ -5301,46 +5359,46 @@
         <v>137.864</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>4.7623167790199</v>
+        <v>5.20251291628637</v>
       </c>
       <c r="G67" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H67" s="8" t="n">
-        <v>164.501917273748</v>
+        <v>164.311562777234</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>190.176311391402</v>
+        <v>189.902038735745</v>
       </c>
       <c r="J67" s="10" t="n">
-        <v>186.880311107682</v>
+        <v>187.162152740677</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>133.10168322098</v>
+        <v>132.661487083714</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>164.501917273748</v>
+        <v>164.311562777234</v>
       </c>
       <c r="M67" s="13" t="n">
-        <v>169.531380053538</v>
+        <v>169.217410277947</v>
       </c>
       <c r="N67" s="14" t="n">
-        <v>169.531380053538</v>
+        <v>169.217410277947</v>
       </c>
       <c r="O67" s="15" t="n">
-        <v>-0.06590042874479</v>
+        <v>-0.0653603340177862</v>
       </c>
       <c r="P67" s="16" t="n">
-        <v>-0.0912074419912683</v>
+        <v>-0.0905956389648732</v>
       </c>
       <c r="Q67" s="17" t="n">
-        <v>-0.0637759193424245</v>
+        <v>-0.0632701330792155</v>
       </c>
       <c r="R67" s="18" t="n">
-        <v>1.03057388547892</v>
+        <v>1.02985698278194</v>
       </c>
       <c r="S67" s="19" t="n">
-        <v>0.891443202432428</v>
+        <v>0.891077375495785</v>
       </c>
     </row>
     <row r="68">
@@ -5360,46 +5418,46 @@
         <v>163.457</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>-4.72284367990514</v>
+        <v>-4.78514608310468</v>
       </c>
       <c r="G68" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>168.502319627904</v>
+        <v>168.573532282584</v>
       </c>
       <c r="I68" s="9" t="n">
-        <v>191.512268704439</v>
+        <v>191.328255515251</v>
       </c>
       <c r="J68" s="10" t="n">
-        <v>188.720334945166</v>
+        <v>188.974115664858</v>
       </c>
       <c r="K68" s="11" t="n">
-        <v>168.179843679905</v>
+        <v>168.242146083105</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>168.179843679905</v>
+        <v>168.242146083105</v>
       </c>
       <c r="M68" s="13" t="n">
-        <v>171.81529671816</v>
+        <v>171.782122416524</v>
       </c>
       <c r="N68" s="14" t="n">
-        <v>171.81529671816</v>
+        <v>171.782122416524</v>
       </c>
       <c r="O68" s="15" t="n">
-        <v>0.0133820007821922</v>
+        <v>0.0150426041938406</v>
       </c>
       <c r="P68" s="16" t="n">
-        <v>-0.0869923781786784</v>
+        <v>-0.086367952336307</v>
       </c>
       <c r="Q68" s="17" t="n">
-        <v>0.0134719404979815</v>
+        <v>0.0151563136107817</v>
       </c>
       <c r="R68" s="18" t="n">
-        <v>1.01966131444108</v>
+        <v>1.01903377173447</v>
       </c>
       <c r="S68" s="19" t="n">
-        <v>0.897150338620459</v>
+        <v>0.897839798695237</v>
       </c>
     </row>
     <row r="69">
@@ -5419,46 +5477,46 @@
         <v>180.02</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>-6.37958223908277</v>
+        <v>-6.31263472265178</v>
       </c>
       <c r="G69" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H69" s="8" t="n">
-        <v>185.814204059089</v>
+        <v>185.830087905487</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>193.002576827013</v>
+        <v>192.890958226037</v>
       </c>
       <c r="J69" s="10" t="n">
-        <v>190.9582679376</v>
+        <v>191.181299264223</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>186.399582239083</v>
+        <v>186.332634722652</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>186.399582239083</v>
+        <v>186.332634722652</v>
       </c>
       <c r="M69" s="13" t="n">
-        <v>185.331359177905</v>
+        <v>185.350876905701</v>
       </c>
       <c r="N69" s="14" t="n">
-        <v>185.331359177905</v>
+        <v>185.350876905701</v>
       </c>
       <c r="O69" s="15" t="n">
-        <v>0.0757253100810523</v>
+        <v>0.0760237169695059</v>
       </c>
       <c r="P69" s="16" t="n">
-        <v>-0.0248823866038915</v>
+        <v>-0.0246743147691992</v>
       </c>
       <c r="Q69" s="17" t="n">
-        <v>0.0786662347178326</v>
+        <v>0.0789881641832109</v>
       </c>
       <c r="R69" s="18" t="n">
-        <v>0.997401464093507</v>
+        <v>0.997421241063879</v>
       </c>
       <c r="S69" s="19" t="n">
-        <v>0.960253288970416</v>
+        <v>0.960910136018398</v>
       </c>
     </row>
     <row r="70">
@@ -5478,46 +5536,46 @@
         <v>206.268</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>5.9215714464502</v>
+        <v>5.77190790560575</v>
       </c>
       <c r="G70" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H70" s="8" t="n">
-        <v>198.353736339674</v>
+        <v>198.426315647652</v>
       </c>
       <c r="I70" s="9" t="n">
-        <v>194.621675835049</v>
+        <v>194.565623767363</v>
       </c>
       <c r="J70" s="10" t="n">
-        <v>193.466922832357</v>
+        <v>193.657886291788</v>
       </c>
       <c r="K70" s="11" t="n">
-        <v>200.34642855355</v>
+        <v>200.496092094394</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>200.34642855355</v>
+        <v>200.496092094394</v>
       </c>
       <c r="M70" s="13" t="n">
-        <v>198.114892552544</v>
+        <v>198.211386970557</v>
       </c>
       <c r="N70" s="14" t="n">
-        <v>198.114892552544</v>
+        <v>198.211386970557</v>
       </c>
       <c r="O70" s="15" t="n">
-        <v>0.0667017742145808</v>
+        <v>0.067083411499982</v>
       </c>
       <c r="P70" s="16" t="n">
-        <v>0.0940743423784114</v>
+        <v>0.0972306326762828</v>
       </c>
       <c r="Q70" s="17" t="n">
-        <v>0.0689766342368814</v>
+        <v>0.0693846734342622</v>
       </c>
       <c r="R70" s="18" t="n">
-        <v>0.998795869482784</v>
+        <v>0.998916833806072</v>
       </c>
       <c r="S70" s="19" t="n">
-        <v>1.01794875469295</v>
+        <v>1.01873796168409</v>
       </c>
     </row>
     <row r="71">
@@ -5537,46 +5595,46 @@
         <v>188.803</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>5.07500148150888</v>
+        <v>5.04276293917768</v>
       </c>
       <c r="G71" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H71" s="8" t="n">
-        <v>205.367130863992</v>
+        <v>205.520728970787</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>196.339878932854</v>
+        <v>196.323630086296</v>
       </c>
       <c r="J71" s="10" t="n">
-        <v>196.096318948319</v>
+        <v>196.253816177865</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>183.727998518491</v>
+        <v>183.760237060822</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>205.367130863992</v>
+        <v>205.520728970787</v>
       </c>
       <c r="M71" s="13" t="n">
-        <v>205.13048426732</v>
+        <v>205.276069365527</v>
       </c>
       <c r="N71" s="14" t="n">
-        <v>205.13048426732</v>
+        <v>205.276069365527</v>
       </c>
       <c r="O71" s="15" t="n">
-        <v>0.0347991574512439</v>
+        <v>0.0350216808445754</v>
       </c>
       <c r="P71" s="16" t="n">
-        <v>0.209985338422536</v>
+        <v>0.21309071583327</v>
       </c>
       <c r="Q71" s="17" t="n">
-        <v>0.0354117331836414</v>
+        <v>0.0356421621529719</v>
       </c>
       <c r="R71" s="18" t="n">
-        <v>0.998847690009222</v>
+        <v>0.998809562390688</v>
       </c>
       <c r="S71" s="19" t="n">
-        <v>1.04477238848391</v>
+        <v>1.04560041639051</v>
       </c>
     </row>
     <row r="72">
@@ -5596,46 +5654,46 @@
         <v>205.667</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>-3.77424678774629</v>
+        <v>-3.89972742613922</v>
       </c>
       <c r="G72" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H72" s="8" t="n">
-        <v>203.602255854828</v>
+        <v>203.60679920899</v>
       </c>
       <c r="I72" s="9" t="n">
-        <v>198.131077295185</v>
+        <v>198.140061672609</v>
       </c>
       <c r="J72" s="10" t="n">
-        <v>198.730873132972</v>
+        <v>198.853219381775</v>
       </c>
       <c r="K72" s="11" t="n">
-        <v>209.441246787746</v>
+        <v>209.566727426139</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>209.441246787746</v>
+        <v>209.566727426139</v>
       </c>
       <c r="M72" s="13" t="n">
-        <v>204.291984464828</v>
+        <v>204.306678726549</v>
       </c>
       <c r="N72" s="14" t="n">
-        <v>204.291984464828</v>
+        <v>204.306678726549</v>
       </c>
       <c r="O72" s="15" t="n">
-        <v>-0.0040960183617033</v>
+        <v>-0.00473356094002862</v>
       </c>
       <c r="P72" s="16" t="n">
-        <v>0.189020933333665</v>
+        <v>0.189336095354338</v>
       </c>
       <c r="Q72" s="17" t="n">
-        <v>-0.00408764112017501</v>
+        <v>-0.00472237529671005</v>
       </c>
       <c r="R72" s="18" t="n">
-        <v>1.00338762754422</v>
+        <v>1.00343740739641</v>
       </c>
       <c r="S72" s="19" t="n">
-        <v>1.03109510761133</v>
+        <v>1.03112251506275</v>
       </c>
     </row>
     <row r="73">
@@ -5655,46 +5713,46 @@
         <v>185.9</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>-7.01831341982545</v>
+        <v>-6.67253108313201</v>
       </c>
       <c r="G73" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H73" s="8" t="n">
-        <v>198.566980647339</v>
+        <v>198.242131967803</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>199.974804129255</v>
+        <v>199.995751202879</v>
       </c>
       <c r="J73" s="10" t="n">
-        <v>201.301356293382</v>
+        <v>201.386560926806</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>192.918313419825</v>
+        <v>192.572531083132</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>192.918313419825</v>
+        <v>192.572531083132</v>
       </c>
       <c r="M73" s="13" t="n">
-        <v>199.110369067753</v>
+        <v>198.8851266663</v>
       </c>
       <c r="N73" s="14" t="n">
-        <v>199.110369067753</v>
+        <v>198.8851266663</v>
       </c>
       <c r="O73" s="15" t="n">
-        <v>-0.0256909775006287</v>
+        <v>-0.0268947869534914</v>
       </c>
       <c r="P73" s="16" t="n">
-        <v>0.0743479676130865</v>
+        <v>0.0730196154803495</v>
       </c>
       <c r="Q73" s="17" t="n">
-        <v>-0.0253637723998237</v>
+        <v>-0.0265363427864502</v>
       </c>
       <c r="R73" s="18" t="n">
-        <v>1.0027365497458</v>
+        <v>1.00324348155518</v>
       </c>
       <c r="S73" s="19" t="n">
-        <v>0.995677280119037</v>
+        <v>0.994446759344142</v>
       </c>
     </row>
     <row r="74">
@@ -5714,46 +5772,46 @@
         <v>205.218</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>4.05439735638389</v>
+        <v>4.3892829272012</v>
       </c>
       <c r="G74" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H74" s="8" t="n">
-        <v>198.430157308775</v>
+        <v>198.374685239273</v>
       </c>
       <c r="I74" s="9" t="n">
-        <v>201.857661498209</v>
+        <v>201.878673019777</v>
       </c>
       <c r="J74" s="10" t="n">
-        <v>203.792091204887</v>
+        <v>203.837873376466</v>
       </c>
       <c r="K74" s="11" t="n">
-        <v>201.163602643616</v>
+        <v>200.828717072799</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>201.163602643616</v>
+        <v>200.828717072799</v>
       </c>
       <c r="M74" s="13" t="n">
-        <v>200.371219321864</v>
+        <v>200.336341624337</v>
       </c>
       <c r="N74" s="14" t="n">
-        <v>200.371219321864</v>
+        <v>200.336341624337</v>
       </c>
       <c r="O74" s="15" t="n">
-        <v>0.00631245332710216</v>
+        <v>0.00727025706528449</v>
       </c>
       <c r="P74" s="16" t="n">
-        <v>0.0113889811121684</v>
+        <v>0.0107206487289064</v>
       </c>
       <c r="Q74" s="17" t="n">
-        <v>0.00633241884897218</v>
+        <v>0.00729674954765169</v>
       </c>
       <c r="R74" s="18" t="n">
-        <v>1.00978209179197</v>
+        <v>1.00988864271012</v>
       </c>
       <c r="S74" s="19" t="n">
-        <v>0.992636186482529</v>
+        <v>0.992360107324024</v>
       </c>
     </row>
     <row r="75">
@@ -5773,46 +5831,46 @@
         <v>213.262</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>7.02264141960248</v>
+        <v>6.14659873137969</v>
       </c>
       <c r="G75" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H75" s="8" t="n">
-        <v>207.08057442838</v>
+        <v>207.624093675187</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>203.761841158502</v>
+        <v>203.7721619534</v>
       </c>
       <c r="J75" s="10" t="n">
-        <v>206.14548542846</v>
+        <v>206.147119145047</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>206.239358580398</v>
+        <v>207.11540126862</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>206.239358580398</v>
+        <v>207.11540126862</v>
       </c>
       <c r="M75" s="13" t="n">
-        <v>207.76926683378</v>
+        <v>208.173448888392</v>
       </c>
       <c r="N75" s="14" t="n">
-        <v>207.76926683378</v>
+        <v>208.173448888392</v>
       </c>
       <c r="O75" s="15" t="n">
-        <v>0.0362564271723437</v>
+        <v>0.0383739589136517</v>
       </c>
       <c r="P75" s="16" t="n">
-        <v>0.012863922082986</v>
+        <v>0.014114550867133</v>
       </c>
       <c r="Q75" s="17" t="n">
-        <v>0.0369217073038444</v>
+        <v>0.0391197483218</v>
       </c>
       <c r="R75" s="18" t="n">
-        <v>1.00332572191912</v>
+        <v>1.00264591263702</v>
       </c>
       <c r="S75" s="19" t="n">
-        <v>1.01966720389104</v>
+        <v>1.02159905893327</v>
       </c>
     </row>
     <row r="76">
@@ -5832,46 +5890,46 @@
         <v>215.168</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>-2.26674753070889</v>
+        <v>-2.46627594352747</v>
       </c>
       <c r="G76" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H76" s="8" t="n">
-        <v>219.223849045148</v>
+        <v>219.409659297804</v>
       </c>
       <c r="I76" s="9" t="n">
-        <v>205.669101079802</v>
+        <v>205.658896611377</v>
       </c>
       <c r="J76" s="10" t="n">
-        <v>208.290804082264</v>
+        <v>208.23921486532</v>
       </c>
       <c r="K76" s="11" t="n">
-        <v>217.434747530709</v>
+        <v>217.634275943527</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>217.434747530709</v>
+        <v>217.634275943527</v>
       </c>
       <c r="M76" s="13" t="n">
-        <v>218.422807686335</v>
+        <v>218.51077010441</v>
       </c>
       <c r="N76" s="14" t="n">
-        <v>218.422807686335</v>
+        <v>218.51077010441</v>
       </c>
       <c r="O76" s="15" t="n">
-        <v>0.0500044993055684</v>
+        <v>0.0484636833209324</v>
       </c>
       <c r="P76" s="16" t="n">
-        <v>0.0691697388839061</v>
+        <v>0.0695233825266777</v>
       </c>
       <c r="Q76" s="17" t="n">
-        <v>0.0512758263765627</v>
+        <v>0.0496572510626019</v>
       </c>
       <c r="R76" s="18" t="n">
-        <v>0.996346011794326</v>
+        <v>0.995903146669702</v>
       </c>
       <c r="S76" s="19" t="n">
-        <v>1.06201080541303</v>
+        <v>1.06249121095558</v>
       </c>
     </row>
     <row r="77">
@@ -5891,46 +5949,46 @@
         <v>223.64</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>-8.94237710352328</v>
+        <v>-8.01912726196603</v>
       </c>
       <c r="G77" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H77" s="8" t="n">
-        <v>229.563484882543</v>
+        <v>228.631094731733</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>207.562747680166</v>
+        <v>207.523645125912</v>
       </c>
       <c r="J77" s="10" t="n">
-        <v>210.157781650224</v>
+        <v>210.043918580676</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>232.582377103523</v>
+        <v>231.659127261966</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>232.582377103523</v>
+        <v>231.659127261966</v>
       </c>
       <c r="M77" s="13" t="n">
-        <v>226.937124481279</v>
+        <v>226.309310352972</v>
       </c>
       <c r="N77" s="14" t="n">
-        <v>226.937124481279</v>
+        <v>226.309310352972</v>
       </c>
       <c r="O77" s="15" t="n">
-        <v>0.0382403252336263</v>
+        <v>0.0350673890159134</v>
       </c>
       <c r="P77" s="16" t="n">
-        <v>0.139755430838745</v>
+        <v>0.13788956543083</v>
       </c>
       <c r="Q77" s="17" t="n">
-        <v>0.038980896203711</v>
+        <v>0.0356895005442319</v>
       </c>
       <c r="R77" s="18" t="n">
-        <v>0.988559328576982</v>
+        <v>0.98984484423921</v>
       </c>
       <c r="S77" s="19" t="n">
-        <v>1.093342264051</v>
+        <v>1.09052301107983</v>
       </c>
     </row>
     <row r="78">
@@ -5950,46 +6008,46 @@
         <v>226.867</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>1.71800381264024</v>
+        <v>2.58228905557067</v>
       </c>
       <c r="G78" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H78" s="8" t="n">
-        <v>225.030330529464</v>
+        <v>224.885742984366</v>
       </c>
       <c r="I78" s="9" t="n">
-        <v>209.433440906683</v>
+        <v>209.358660241288</v>
       </c>
       <c r="J78" s="10" t="n">
-        <v>211.721872333508</v>
+        <v>211.537963639896</v>
       </c>
       <c r="K78" s="11" t="n">
-        <v>225.14899618736</v>
+        <v>224.284710944429</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>225.14899618736</v>
+        <v>224.284710944429</v>
       </c>
       <c r="M78" s="13" t="n">
-        <v>223.149040015819</v>
+        <v>223.018312770875</v>
       </c>
       <c r="N78" s="14" t="n">
-        <v>223.149040015819</v>
+        <v>223.018312770875</v>
       </c>
       <c r="O78" s="15" t="n">
-        <v>-0.0168331053521665</v>
+        <v>-0.0146488052952732</v>
       </c>
       <c r="P78" s="16" t="n">
-        <v>0.11367810592282</v>
+        <v>0.113219453657937</v>
       </c>
       <c r="Q78" s="17" t="n">
-        <v>-0.0166922202531564</v>
+        <v>-0.0145420335423426</v>
       </c>
       <c r="R78" s="18" t="n">
-        <v>0.991639835798053</v>
+        <v>0.991696093364082</v>
       </c>
       <c r="S78" s="19" t="n">
-        <v>1.06548905967337</v>
+        <v>1.06524522326349</v>
       </c>
     </row>
     <row r="79">
@@ -6009,46 +6067,46 @@
         <v>220.115</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>10.3992094149655</v>
+        <v>8.27029806732523</v>
       </c>
       <c r="G79" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H79" s="8" t="n">
-        <v>210.867914979406</v>
+        <v>211.980512506984</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>211.287477974832</v>
+        <v>211.171279378125</v>
       </c>
       <c r="J79" s="10" t="n">
-        <v>213.070653310548</v>
+        <v>212.806159435168</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>209.715790585035</v>
+        <v>211.844701932675</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>209.715790585035</v>
+        <v>211.844701932675</v>
       </c>
       <c r="M79" s="13" t="n">
-        <v>211.765159175606</v>
+        <v>212.61535150144</v>
       </c>
       <c r="N79" s="14" t="n">
-        <v>211.765159175606</v>
+        <v>212.61535150144</v>
       </c>
       <c r="O79" s="15" t="n">
-        <v>-0.052361968160761</v>
+        <v>-0.0477692164569643</v>
       </c>
       <c r="P79" s="16" t="n">
-        <v>0.0192323552117215</v>
+        <v>0.021337507913558</v>
       </c>
       <c r="Q79" s="17" t="n">
-        <v>-0.0510146977975172</v>
+        <v>-0.0466462199457236</v>
       </c>
       <c r="R79" s="18" t="n">
-        <v>1.00425500577595</v>
+        <v>1.00299479884707</v>
       </c>
       <c r="S79" s="19" t="n">
-        <v>1.00226081169292</v>
+        <v>1.00683839264302</v>
       </c>
     </row>
     <row r="80">
@@ -6068,46 +6126,46 @@
         <v>200.998</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>-1.48205934499608</v>
+        <v>-1.48929119598281</v>
       </c>
       <c r="G80" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H80" s="8" t="n">
-        <v>202.76422058047</v>
+        <v>203.144101550873</v>
       </c>
       <c r="I80" s="9" t="n">
-        <v>213.140978322143</v>
+        <v>212.978168738732</v>
       </c>
       <c r="J80" s="10" t="n">
-        <v>214.358837379047</v>
+        <v>213.997049095202</v>
       </c>
       <c r="K80" s="11" t="n">
-        <v>202.480059344996</v>
+        <v>202.487291195983</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>202.480059344996</v>
+        <v>202.487291195983</v>
       </c>
       <c r="M80" s="13" t="n">
-        <v>204.656043450177</v>
+        <v>204.832585837396</v>
       </c>
       <c r="N80" s="14" t="n">
-        <v>204.656043450177</v>
+        <v>204.832585837396</v>
       </c>
       <c r="O80" s="15" t="n">
-        <v>-0.0341471877718084</v>
+        <v>-0.0372916806374795</v>
       </c>
       <c r="P80" s="16" t="n">
-        <v>-0.0630280527110875</v>
+        <v>-0.0625973001718794</v>
       </c>
       <c r="Q80" s="17" t="n">
-        <v>-0.0335707523990495</v>
+        <v>-0.0366049093307907</v>
       </c>
       <c r="R80" s="18" t="n">
-        <v>1.00933016123008</v>
+        <v>1.00831175640165</v>
       </c>
       <c r="S80" s="19" t="n">
-        <v>0.960190973416935</v>
+        <v>0.961753906752159</v>
       </c>
     </row>
     <row r="81">
@@ -6127,46 +6185,46 @@
         <v>193.143</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>-10.8052645256798</v>
+        <v>-9.36805902494365</v>
       </c>
       <c r="G81" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H81" s="8" t="n">
-        <v>203.915580698835</v>
+        <v>202.259540090632</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>215.009079081526</v>
+        <v>214.796415414515</v>
       </c>
       <c r="J81" s="10" t="n">
-        <v>215.724363023081</v>
+        <v>215.254368461196</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>203.94826452568</v>
+        <v>202.511059024944</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>203.94826452568</v>
+        <v>202.511059024944</v>
       </c>
       <c r="M81" s="13" t="n">
-        <v>205.283362796116</v>
+        <v>204.194715864022</v>
       </c>
       <c r="N81" s="14" t="n">
-        <v>205.283362796116</v>
+        <v>204.194715864022</v>
       </c>
       <c r="O81" s="15" t="n">
-        <v>0.00306054907654143</v>
+        <v>-0.0031189629045122</v>
       </c>
       <c r="P81" s="16" t="n">
-        <v>-0.0954174498097551</v>
+        <v>-0.0977184476169272</v>
       </c>
       <c r="Q81" s="17" t="n">
-        <v>0.00306523733853159</v>
+        <v>-0.00311410399261369</v>
       </c>
       <c r="R81" s="18" t="n">
-        <v>1.00670758993792</v>
+        <v>1.00956778489916</v>
       </c>
       <c r="S81" s="19" t="n">
-        <v>0.954766020453851</v>
+        <v>0.95064303317151</v>
       </c>
     </row>
     <row r="82">
@@ -6186,46 +6244,46 @@
         <v>210.215</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>-0.541862788109276</v>
+        <v>0.945545789780472</v>
       </c>
       <c r="G82" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H82" s="8" t="n">
-        <v>211.455924583553</v>
+        <v>211.272081740901</v>
       </c>
       <c r="I82" s="9" t="n">
-        <v>216.900254311531</v>
+        <v>216.636549698416</v>
       </c>
       <c r="J82" s="10" t="n">
-        <v>217.245774836554</v>
+        <v>216.664304584852</v>
       </c>
       <c r="K82" s="11" t="n">
-        <v>210.756862788109</v>
+        <v>209.26945421022</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>210.756862788109</v>
+        <v>209.26945421022</v>
       </c>
       <c r="M82" s="13" t="n">
-        <v>211.362355872343</v>
+        <v>211.147835332834</v>
       </c>
       <c r="N82" s="14" t="n">
-        <v>211.362355872343</v>
+        <v>211.147835332834</v>
       </c>
       <c r="O82" s="15" t="n">
-        <v>0.0291827047244573</v>
+        <v>0.0334845013910547</v>
       </c>
       <c r="P82" s="16" t="n">
-        <v>-0.0528197842242144</v>
+        <v>-0.0532264695690534</v>
       </c>
       <c r="Q82" s="17" t="n">
-        <v>0.02961269239468</v>
+        <v>0.0340514172435396</v>
       </c>
       <c r="R82" s="18" t="n">
-        <v>0.999557502532057</v>
+        <v>0.999411912794899</v>
       </c>
       <c r="S82" s="19" t="n">
-        <v>0.974467994715976</v>
+        <v>0.974663950412696</v>
       </c>
     </row>
     <row r="83">
@@ -6245,46 +6303,46 @@
         <v>233.918</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>13.9305666125258</v>
+        <v>10.3766261140458</v>
       </c>
       <c r="G83" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H83" s="8" t="n">
-        <v>218.65478221601</v>
+        <v>220.342980749499</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>218.816065061611</v>
+        <v>218.501423535632</v>
       </c>
       <c r="J83" s="10" t="n">
-        <v>218.942736920883</v>
+        <v>218.249327970691</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>219.987433387474</v>
+        <v>223.541373885954</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>219.987433387474</v>
+        <v>223.541373885954</v>
       </c>
       <c r="M83" s="13" t="n">
-        <v>217.483182315306</v>
+        <v>218.796009366214</v>
       </c>
       <c r="N83" s="14" t="n">
-        <v>217.483182315306</v>
+        <v>218.796009366214</v>
       </c>
       <c r="O83" s="15" t="n">
-        <v>0.0285475378845784</v>
+        <v>0.0355813021237278</v>
       </c>
       <c r="P83" s="16" t="n">
-        <v>0.0270017181389031</v>
+        <v>0.0290696688697571</v>
       </c>
       <c r="Q83" s="17" t="n">
-        <v>0.0289589242024704</v>
+        <v>0.0362218917438779</v>
       </c>
       <c r="R83" s="18" t="n">
-        <v>0.994641782407728</v>
+        <v>0.992979257256017</v>
       </c>
       <c r="S83" s="19" t="n">
-        <v>0.993908661386769</v>
+        <v>1.00134821012063</v>
       </c>
     </row>
     <row r="84">
@@ -6304,46 +6362,46 @@
         <v>217.826</v>
       </c>
       <c r="F84" s="6" t="n">
-        <v>-1.37499969816596</v>
+        <v>-1.00583548272933</v>
       </c>
       <c r="G84" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H84" s="8" t="n">
-        <v>218.447067514267</v>
+        <v>218.969187944931</v>
       </c>
       <c r="I84" s="9" t="n">
-        <v>220.754232761515</v>
+        <v>220.389284436681</v>
       </c>
       <c r="J84" s="10" t="n">
-        <v>220.802468817245</v>
+        <v>219.994934871358</v>
       </c>
       <c r="K84" s="11" t="n">
-        <v>219.200999698166</v>
+        <v>218.831835482729</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>219.200999698166</v>
+        <v>218.831835482729</v>
       </c>
       <c r="M84" s="13" t="n">
-        <v>218.124364410531</v>
+        <v>218.352492428089</v>
       </c>
       <c r="N84" s="14" t="n">
-        <v>218.124364410531</v>
+        <v>218.352492428089</v>
       </c>
       <c r="O84" s="15" t="n">
-        <v>0.00294385422428979</v>
+        <v>-0.00202913695681196</v>
       </c>
       <c r="P84" s="16" t="n">
-        <v>0.0658095443129862</v>
+        <v>0.0660046668620682</v>
       </c>
       <c r="Q84" s="17" t="n">
-        <v>0.00294819161831095</v>
+        <v>-0.00202707965017146</v>
       </c>
       <c r="R84" s="18" t="n">
-        <v>0.998522740051365</v>
+        <v>0.997183642490391</v>
       </c>
       <c r="S84" s="19" t="n">
-        <v>0.988086895014035</v>
+        <v>0.990758207624307</v>
       </c>
     </row>
     <row r="85">
@@ -6363,46 +6421,46 @@
         <v>201.979</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>-12.1290248583198</v>
+        <v>-10.2259248609445</v>
       </c>
       <c r="G85" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H85" s="8" t="n">
-        <v>214.959851725362</v>
+        <v>213.872310312874</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>222.713210946199</v>
+        <v>222.30152988105</v>
       </c>
       <c r="J85" s="10" t="n">
-        <v>222.817413549148</v>
+        <v>221.91308176908</v>
       </c>
       <c r="K85" s="11" t="n">
-        <v>214.10802485832</v>
+        <v>212.204924860945</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>214.10802485832</v>
+        <v>212.204924860945</v>
       </c>
       <c r="M85" s="13" t="n">
-        <v>217.025964933734</v>
+        <v>215.523950840574</v>
       </c>
       <c r="N85" s="14" t="n">
-        <v>217.025964933734</v>
+        <v>215.523950840574</v>
       </c>
       <c r="O85" s="15" t="n">
-        <v>-0.00504837862023848</v>
+        <v>-0.0130386505365838</v>
       </c>
       <c r="P85" s="16" t="n">
-        <v>0.0572019182542336</v>
+        <v>0.0554825080982801</v>
       </c>
       <c r="Q85" s="17" t="n">
-        <v>-0.00503565697379105</v>
+        <v>-0.0129540155739091</v>
       </c>
       <c r="R85" s="18" t="n">
-        <v>1.00961162371386</v>
+        <v>1.00772255429085</v>
       </c>
       <c r="S85" s="19" t="n">
-        <v>0.974463813851443</v>
+        <v>0.969511775091685</v>
       </c>
     </row>
     <row r="86">
@@ -6422,46 +6480,46 @@
         <v>218.523</v>
       </c>
       <c r="F86" s="6" t="n">
-        <v>-2.16381032012976</v>
+        <v>-0.331118157677729</v>
       </c>
       <c r="G86" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H86" s="8" t="n">
-        <v>224.063739800129</v>
+        <v>219.40238240164</v>
       </c>
       <c r="I86" s="9" t="n">
-        <v>224.690482379951</v>
+        <v>224.23858394263</v>
       </c>
       <c r="J86" s="10" t="n">
-        <v>224.972006794504</v>
+        <v>224.009909649135</v>
       </c>
       <c r="K86" s="11" t="n">
-        <v>220.68681032013</v>
+        <v>218.854118157678</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>220.68681032013</v>
+        <v>218.854118157678</v>
       </c>
       <c r="M86" s="13" t="n">
-        <v>224.699058092234</v>
+        <v>219.910964880998</v>
       </c>
       <c r="N86" s="14" t="n">
-        <v>224.699058092234</v>
+        <v>219.910964880998</v>
       </c>
       <c r="O86" s="15" t="n">
-        <v>0.0347449868816421</v>
+        <v>0.0201507151911346</v>
       </c>
       <c r="P86" s="16" t="n">
-        <v>0.0630987583614246</v>
+        <v>0.0415023414014657</v>
       </c>
       <c r="Q86" s="17" t="n">
-        <v>0.0353556458594373</v>
+        <v>0.0203551114542677</v>
       </c>
       <c r="R86" s="18" t="n">
-        <v>1.00283543554469</v>
+        <v>1.00231803535491</v>
       </c>
       <c r="S86" s="19" t="n">
-        <v>1.00003816678033</v>
+        <v>0.980700827727582</v>
       </c>
     </row>
     <row r="87">
@@ -6481,113 +6539,165 @@
         <v>259.799</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>16.4844131296449</v>
+        <v>11.8847271582184</v>
       </c>
       <c r="G87" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H87" s="8" t="n">
-        <v>238.871403121761</v>
+        <v>229.730698347692</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>226.678151585755</v>
+        <v>226.194560317173</v>
       </c>
       <c r="J87" s="10" t="n">
-        <v>227.207137287774</v>
+        <v>226.243018712264</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>243.314586870355</v>
+        <v>247.914272841782</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>243.314586870355</v>
+        <v>229.730698347692</v>
       </c>
       <c r="M87" s="13" t="n">
-        <v>235.771994686947</v>
+        <v>228.383850799914</v>
       </c>
       <c r="N87" s="14" t="n">
-        <v>235.771994686947</v>
+        <v>228.383850799914</v>
       </c>
       <c r="O87" s="15" t="n">
-        <v>0.0481032264823238</v>
+        <v>0.0378050101515877</v>
       </c>
       <c r="P87" s="16" t="n">
-        <v>0.0840929959592265</v>
+        <v>0.0438209154795484</v>
       </c>
       <c r="Q87" s="17" t="n">
-        <v>0.0492789631105968</v>
+        <v>0.0385287105783956</v>
       </c>
       <c r="R87" s="18" t="n">
-        <v>0.987024782396265</v>
+        <v>0.994137276570065</v>
       </c>
       <c r="S87" s="19" t="n">
-        <v>1.04011786331225</v>
+        <v>1.00967879368836</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
         <v>138</v>
       </c>
-      <c r="B88" s="2"/>
+      <c r="B88" s="2" t="n">
+        <v>223.724</v>
+      </c>
       <c r="C88" s="3" t="n">
-        <v>238.766412293813</v>
+        <v>223.724</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>267.860403802143</v>
+        <v>223.724</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>209.672420785484</v>
+        <v>223.724</v>
       </c>
       <c r="F88" s="6" t="n">
-        <v>-1.61160960766326</v>
-      </c>
-      <c r="G88" s="7"/>
-      <c r="H88" s="8"/>
-      <c r="I88" s="9"/>
-      <c r="J88" s="10"/>
-      <c r="K88" s="11"/>
-      <c r="L88" s="12"/>
-      <c r="M88" s="13"/>
+        <v>-0.780061531566807</v>
+      </c>
+      <c r="G88" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="8" t="n">
+        <v>235.219888346593</v>
+      </c>
+      <c r="I88" s="9" t="n">
+        <v>228.160207409318</v>
+      </c>
+      <c r="J88" s="10" t="n">
+        <v>228.54423020175</v>
+      </c>
+      <c r="K88" s="11" t="n">
+        <v>224.504061531567</v>
+      </c>
+      <c r="L88" s="12" t="n">
+        <v>235.219888346593</v>
+      </c>
+      <c r="M88" s="13" t="n">
+        <v>233.626423090786</v>
+      </c>
       <c r="N88" s="14" t="n">
-        <v>240.378021901476</v>
-      </c>
-      <c r="O88" s="15"/>
-      <c r="P88" s="16"/>
-      <c r="Q88" s="17"/>
-      <c r="R88" s="18"/>
-      <c r="S88" s="19"/>
+        <v>233.626423090786</v>
+      </c>
+      <c r="O88" s="15" t="n">
+        <v>0.0226955876011309</v>
+      </c>
+      <c r="P88" s="16" t="n">
+        <v>0.0699507960401533</v>
+      </c>
+      <c r="Q88" s="17" t="n">
+        <v>0.0229550919318944</v>
+      </c>
+      <c r="R88" s="18" t="n">
+        <v>0.99322563552339</v>
+      </c>
+      <c r="S88" s="19" t="n">
+        <v>1.02395779589936</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
         <v>139</v>
       </c>
-      <c r="B89" s="2"/>
+      <c r="B89" s="2" t="n">
+        <v>223.584</v>
+      </c>
       <c r="C89" s="3" t="n">
-        <v>218.06567522758</v>
+        <v>223.584</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>253.522910130251</v>
+        <v>223.584</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>182.608440324908</v>
+        <v>223.584</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>-12.7100386306738</v>
-      </c>
-      <c r="G89" s="7"/>
-      <c r="H89" s="8"/>
-      <c r="I89" s="9"/>
-      <c r="J89" s="10"/>
-      <c r="K89" s="11"/>
-      <c r="L89" s="12"/>
-      <c r="M89" s="13"/>
+        <v>-10.751217322265</v>
+      </c>
+      <c r="G89" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" s="8" t="n">
+        <v>233.381186116253</v>
+      </c>
+      <c r="I89" s="9" t="n">
+        <v>230.128483709971</v>
+      </c>
+      <c r="J89" s="10" t="n">
+        <v>230.862803759051</v>
+      </c>
+      <c r="K89" s="11" t="n">
+        <v>234.335217322265</v>
+      </c>
+      <c r="L89" s="12" t="n">
+        <v>234.335217322265</v>
+      </c>
+      <c r="M89" s="13" t="n">
+        <v>234.630107663708</v>
+      </c>
       <c r="N89" s="14" t="n">
-        <v>230.775713858254</v>
-      </c>
-      <c r="O89" s="15"/>
-      <c r="P89" s="16"/>
-      <c r="Q89" s="17"/>
-      <c r="R89" s="18"/>
-      <c r="S89" s="19"/>
+        <v>234.630107663708</v>
+      </c>
+      <c r="O89" s="15" t="n">
+        <v>0.00428690704392878</v>
+      </c>
+      <c r="P89" s="16" t="n">
+        <v>0.0886498078223648</v>
+      </c>
+      <c r="Q89" s="17" t="n">
+        <v>0.00429610897450527</v>
+      </c>
+      <c r="R89" s="18" t="n">
+        <v>1.00535142342979</v>
+      </c>
+      <c r="S89" s="19" t="n">
+        <v>1.01956135060365</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
@@ -6595,16 +6705,16 @@
       </c>
       <c r="B90" s="2"/>
       <c r="C90" s="3" t="n">
-        <v>219.705568390015</v>
+        <v>225.422383998404</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>256.06567932042</v>
+        <v>253.554146895334</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>183.34545745961</v>
+        <v>197.290621101474</v>
       </c>
       <c r="F90" s="6" t="n">
-        <v>-2.88249547105168</v>
+        <v>-0.976659506990502</v>
       </c>
       <c r="G90" s="7"/>
       <c r="H90" s="8"/>
@@ -6614,7 +6724,7 @@
       <c r="L90" s="12"/>
       <c r="M90" s="13"/>
       <c r="N90" s="14" t="n">
-        <v>222.588063861067</v>
+        <v>226.399043505395</v>
       </c>
       <c r="O90" s="15"/>
       <c r="P90" s="16"/>
@@ -6628,16 +6738,16 @@
       </c>
       <c r="B91" s="2"/>
       <c r="C91" s="3" t="n">
-        <v>228.927772624304</v>
+        <v>231.746704784108</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>266.018326605397</v>
+        <v>263.708452825803</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>191.837218643211</v>
+        <v>199.784956742412</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>17.8876492004363</v>
+        <v>12.6132209836113</v>
       </c>
       <c r="G91" s="7"/>
       <c r="H91" s="8"/>
@@ -6647,7 +6757,7 @@
       <c r="L91" s="12"/>
       <c r="M91" s="13"/>
       <c r="N91" s="14" t="n">
-        <v>211.040123423868</v>
+        <v>219.133483800497</v>
       </c>
       <c r="O91" s="15"/>
       <c r="P91" s="16"/>
@@ -6660,10 +6770,18 @@
         <v>142</v>
       </c>
       <c r="B92" s="2"/>
-      <c r="C92" s="3"/>
-      <c r="D92" s="4"/>
-      <c r="E92" s="5"/>
-      <c r="F92" s="6"/>
+      <c r="C92" s="3" t="n">
+        <v>224.549500035969</v>
+      </c>
+      <c r="D92" s="4" t="n">
+        <v>256.907668581367</v>
+      </c>
+      <c r="E92" s="5" t="n">
+        <v>192.19133149057</v>
+      </c>
+      <c r="F92" s="6" t="n">
+        <v>-0.545925905853313</v>
+      </c>
       <c r="G92" s="7"/>
       <c r="H92" s="8"/>
       <c r="I92" s="9"/>
@@ -6671,7 +6789,9 @@
       <c r="K92" s="11"/>
       <c r="L92" s="12"/>
       <c r="M92" s="13"/>
-      <c r="N92" s="14"/>
+      <c r="N92" s="14" t="n">
+        <v>225.095425941822</v>
+      </c>
       <c r="O92" s="15"/>
       <c r="P92" s="16"/>
       <c r="Q92" s="17"/>
@@ -6683,10 +6803,18 @@
         <v>143</v>
       </c>
       <c r="B93" s="2"/>
-      <c r="C93" s="3"/>
-      <c r="D93" s="4"/>
-      <c r="E93" s="5"/>
-      <c r="F93" s="6"/>
+      <c r="C93" s="3" t="n">
+        <v>220.300031029583</v>
+      </c>
+      <c r="D93" s="4" t="n">
+        <v>253.253275979595</v>
+      </c>
+      <c r="E93" s="5" t="n">
+        <v>187.346786079571</v>
+      </c>
+      <c r="F93" s="6" t="n">
+        <v>-11.3553681956846</v>
+      </c>
       <c r="G93" s="7"/>
       <c r="H93" s="8"/>
       <c r="I93" s="9"/>
@@ -6694,7 +6822,9 @@
       <c r="K93" s="11"/>
       <c r="L93" s="12"/>
       <c r="M93" s="13"/>
-      <c r="N93" s="14"/>
+      <c r="N93" s="14" t="n">
+        <v>231.655399225268</v>
+      </c>
       <c r="O93" s="15"/>
       <c r="P93" s="16"/>
       <c r="Q93" s="17"/>
@@ -7082,150 +7212,98 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>160</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>160</v>
-      </c>
-      <c r="B2" s="1"/>
+        <v>161</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3"/>
-      <c r="B3" s="1"/>
+      <c r="A3" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>161</v>
-      </c>
-      <c r="B4" s="1"/>
+        <v>163</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>162</v>
-      </c>
-      <c r="B5" s="1" t="n">
-        <v>-0.213962470861911</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>163</v>
-      </c>
-      <c r="B6" s="1" t="n">
-        <v>-0.234322032221841</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>164</v>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>-0.212161988410589</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>165</v>
-      </c>
-      <c r="B8" s="1" t="n">
-        <v>-0.0318087106349507</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>166</v>
-      </c>
-      <c r="B9" s="1" t="n">
-        <v>0.229267584248025</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>167</v>
-      </c>
-      <c r="B10" s="1" t="n">
-        <v>0.322680640744442</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>168</v>
-      </c>
-      <c r="B11" s="1" t="n">
-        <v>0.139830067626085</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>169</v>
-      </c>
-      <c r="B12" s="1" t="n">
-        <v>-0.125788760476751</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>170</v>
-      </c>
-      <c r="B13" s="1" t="n">
-        <v>-0.275245794687074</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="1"/>
+      <c r="A14" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="15">
-      <c r="B15" s="1"/>
+      <c r="A15" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="16">
-      <c r="B16" s="1"/>
+      <c r="A16" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="17">
-      <c r="B17" s="1"/>
+      <c r="A17" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="18">
-      <c r="B18" s="1"/>
+      <c r="A18" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="19">
-      <c r="B19" s="1"/>
-    </row>
-    <row r="20">
-      <c r="B20" s="1"/>
-    </row>
-    <row r="21">
-      <c r="B21" s="1"/>
-    </row>
-    <row r="22">
-      <c r="B22" s="1"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="1"/>
-    </row>
-    <row r="24">
-      <c r="B24" s="1"/>
-    </row>
-    <row r="25">
-      <c r="B25" s="1"/>
-    </row>
-    <row r="26">
-      <c r="B26" s="1"/>
-    </row>
-    <row r="27">
-      <c r="B27" s="1"/>
-    </row>
-    <row r="28">
-      <c r="B28" s="1"/>
-    </row>
-    <row r="29">
-      <c r="B29" s="1"/>
-    </row>
-    <row r="30">
-      <c r="B30" s="1"/>
+      <c r="A19" t="s">
+        <v>178</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7233,235 +7311,160 @@
 </worksheet>
 </file>
 
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C5B9F2161CEE1040BBC03CB11300495F" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a7cec21613a3259523bdab11a1e26aca">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5dd4176-d247-4204-85b8-921214f3ccea" xmlns:ns3="359b39ce-e1f9-4933-8424-33b611e6fdcd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="68943c349d3a016936c8f8cb3335004b" ns2:_="" ns3:_="">
-    <xsd:import namespace="b5dd4176-d247-4204-85b8-921214f3ccea"/>
-    <xsd:import namespace="359b39ce-e1f9-4933-8424-33b611e6fdcd"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b5dd4176-d247-4204-85b8-921214f3ccea" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="01529062-7a8b-4d76-943d-e0db5644ee6d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="19" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="359b39ce-e1f9-4933-8424-33b611e6fdcd" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{c9b73259-0823-4f05-8927-4a40ee49fbe1}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="359b39ce-e1f9-4933-8424-33b611e6fdcd">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="359b39ce-e1f9-4933-8424-33b611e6fdcd" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b5dd4176-d247-4204-85b8-921214f3ccea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7E87C8A-406E-4F8F-98EB-D8D91A6B3E80}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6839BA49-78E8-42D8-8438-B9079567A6F9}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32F1F3AD-3220-4246-9DA0-5B7C7D7FA384}"/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B2" s="1"/>
+    </row>
+    <row r="3">
+      <c r="A3"/>
+      <c r="B3" s="1"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B4" s="1"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>-0.173164063293851</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>182</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>-0.138709406221347</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>183</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>-0.108842455893944</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>184</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>0.0391864012261878</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>185</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>0.198757636051749</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>186</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>0.212661182770697</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>0.0763193656971647</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>188</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>-0.130224129393615</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>189</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>-0.234116698817283</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="1"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="1"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="1"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="1"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="1"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="1"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="1"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="1"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="1"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="1"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="1"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="1"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="1"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="1"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="1"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="1"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
 </file>
--- a/indicadores/GR-EPRIV-INF_out.xlsx
+++ b/indicadores/GR-EPRIV-INF_out.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="192">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -23,7 +23,7 @@
     <t xml:space="preserve">Título</t>
   </si>
   <si>
-    <t xml:space="preserve">Ocupados informales en el sector privado del Gran Rosario</t>
+    <t xml:space="preserve">Ocupados informales en el sector privado</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad de medida</t>
@@ -74,6 +74,12 @@
     <t xml:space="preserve">const</t>
   </si>
   <si>
+    <t xml:space="preserve">Alcance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aglomerado Gran Rosario</t>
+  </si>
+  <si>
     <t xml:space="preserve">Resumen del correlograma</t>
   </si>
   <si>
@@ -107,13 +113,13 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">07/05/2026</t>
+    <t xml:space="preserve">17/06/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">vcorvalan</t>
+    <t xml:space="preserve">focampo</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>
@@ -1086,9 +1092,13 @@
       <c r="J6" s="1"/>
     </row>
     <row r="7">
-      <c r="A7"/>
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
       <c r="B7"/>
-      <c r="C7"/>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
       <c r="D7"/>
       <c r="E7"/>
       <c r="F7"/>
@@ -1099,7 +1109,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B8"/>
       <c r="C8"/>
@@ -1113,12 +1123,12 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B9"/>
       <c r="C9"/>
       <c r="D9" t="n">
-        <v>-0.234116698817283</v>
+        <v>-0.227429780760657</v>
       </c>
       <c r="E9"/>
       <c r="F9"/>
@@ -1129,7 +1139,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B10"/>
       <c r="C10"/>
@@ -1157,7 +1167,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B12"/>
       <c r="C12"/>
@@ -1171,12 +1181,12 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13" t="n">
-        <v>0.0395045978888794</v>
+        <v>0.038995877860649</v>
       </c>
       <c r="E13"/>
       <c r="F13"/>
@@ -1199,7 +1209,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B15"/>
       <c r="C15"/>
@@ -1213,7 +1223,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B16"/>
       <c r="C16"/>
@@ -1227,7 +1237,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B17"/>
       <c r="C17"/>
@@ -1241,12 +1251,12 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18" t="n">
-        <v>0.661942796338858</v>
+        <v>0.673305892777082</v>
       </c>
       <c r="E18"/>
       <c r="F18"/>
@@ -1257,7 +1267,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B19"/>
       <c r="C19"/>
@@ -1271,12 +1281,12 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20" t="n">
-        <v>0.455952867215112</v>
+        <v>0.514476773648625</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -1419,10 +1429,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C32"/>
       <c r="D32"/>
@@ -1435,10 +1445,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C33"/>
       <c r="D33"/>
@@ -1462,66 +1472,66 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="P1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Q1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="R1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>184.844</v>
@@ -1574,7 +1584,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>187.087</v>
@@ -1631,7 +1641,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>186.517</v>
@@ -1688,7 +1698,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>189.606</v>
@@ -1745,7 +1755,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>178.421</v>
@@ -1804,7 +1814,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>183.734</v>
@@ -1863,7 +1873,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>190.427</v>
@@ -1922,7 +1932,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>190.167</v>
@@ -1981,7 +1991,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>186.12</v>
@@ -2040,7 +2050,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>178.072</v>
@@ -2099,7 +2109,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>188.752</v>
@@ -2158,7 +2168,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>185.205</v>
@@ -2217,7 +2227,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>175.164</v>
@@ -2276,7 +2286,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>163.593</v>
@@ -2335,7 +2345,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>188.0315</v>
@@ -2394,7 +2404,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>191.384</v>
@@ -2453,7 +2463,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>174.593</v>
@@ -2512,7 +2522,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>179.795</v>
@@ -2571,7 +2581,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>187.311</v>
@@ -2630,7 +2640,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>184.615</v>
@@ -2689,7 +2699,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>194.435</v>
@@ -2748,7 +2758,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>169.467</v>
@@ -2807,7 +2817,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>178.154</v>
@@ -2866,7 +2876,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>186.889</v>
@@ -2925,7 +2935,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>195.657</v>
@@ -2984,7 +2994,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>183.563</v>
@@ -3043,7 +3053,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>173.725</v>
@@ -3102,7 +3112,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>176.801</v>
@@ -3161,7 +3171,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>171.71</v>
@@ -3220,7 +3230,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>181.36</v>
@@ -3279,7 +3289,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>181.025</v>
@@ -3338,7 +3348,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>176.741</v>
@@ -3397,7 +3407,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>168.454</v>
@@ -3456,7 +3466,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>182.36</v>
@@ -3515,7 +3525,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>171.866</v>
@@ -3574,7 +3584,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>160.682</v>
@@ -3633,7 +3643,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>166.629</v>
@@ -3692,7 +3702,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>186.602</v>
@@ -3751,7 +3761,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>197.311</v>
@@ -3810,7 +3820,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>188.755</v>
@@ -3869,7 +3879,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B42" s="2" t="n">
         <v>184.912</v>
@@ -3928,7 +3938,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B43" s="2" t="n">
         <v>173.805</v>
@@ -3987,7 +3997,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B44" s="2" t="n">
         <v>193.59</v>
@@ -4046,7 +4056,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B45" s="2" t="n">
         <v>209.016</v>
@@ -4105,7 +4115,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B46" s="2" t="n">
         <v>196.596</v>
@@ -4164,7 +4174,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B47" s="2" t="n">
         <v>198.82</v>
@@ -4223,7 +4233,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B48" s="2" t="n">
         <v>188.675</v>
@@ -4282,7 +4292,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B49" s="2" t="n">
         <v>187.299</v>
@@ -4341,7 +4351,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B50" s="2" t="n">
         <v>183.9625</v>
@@ -4400,7 +4410,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B51" s="2" t="n">
         <v>186.559</v>
@@ -4459,7 +4469,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B52" s="2" t="n">
         <v>183.76</v>
@@ -4518,7 +4528,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B53" s="2" t="n">
         <v>165.582</v>
@@ -4577,7 +4587,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B54" s="2" t="n">
         <v>171.329</v>
@@ -4636,7 +4646,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B55" s="2" t="n">
         <v>196.137</v>
@@ -4695,7 +4705,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B56" s="2" t="n">
         <v>171.817</v>
@@ -4754,7 +4764,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B57" s="2" t="n">
         <v>159.256</v>
@@ -4813,7 +4823,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B58" s="2" t="n">
         <v>189.021</v>
@@ -4872,7 +4882,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B59" s="2" t="n">
         <v>203.006</v>
@@ -4931,7 +4941,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B60" s="2" t="n">
         <v>181.525</v>
@@ -4990,7 +5000,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B61" s="2" t="n">
         <v>174.433</v>
@@ -5049,7 +5059,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B62" s="2" t="n">
         <v>192.638</v>
@@ -5108,7 +5118,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B63" s="2" t="n">
         <v>192.737</v>
@@ -5167,7 +5177,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B64" s="2" t="n">
         <v>178.853</v>
@@ -5226,7 +5236,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B65" s="2" t="n">
         <v>191.494</v>
@@ -5285,7 +5295,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B66" s="2" t="n">
         <v>202.1</v>
@@ -5344,7 +5354,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B67" s="2" t="n">
         <v>137.864</v>
@@ -5403,7 +5413,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B68" s="2" t="n">
         <v>163.457</v>
@@ -5462,7 +5472,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B69" s="2" t="n">
         <v>180.02</v>
@@ -5521,7 +5531,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B70" s="2" t="n">
         <v>206.268</v>
@@ -5580,7 +5590,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B71" s="2" t="n">
         <v>188.803</v>
@@ -5639,7 +5649,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B72" s="2" t="n">
         <v>205.667</v>
@@ -5698,7 +5708,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B73" s="2" t="n">
         <v>185.9</v>
@@ -5757,7 +5767,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B74" s="2" t="n">
         <v>205.218</v>
@@ -5816,7 +5826,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B75" s="2" t="n">
         <v>213.262</v>
@@ -5875,7 +5885,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B76" s="2" t="n">
         <v>215.168</v>
@@ -5934,7 +5944,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B77" s="2" t="n">
         <v>223.64</v>
@@ -5993,7 +6003,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B78" s="2" t="n">
         <v>226.867</v>
@@ -6052,7 +6062,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B79" s="2" t="n">
         <v>220.115</v>
@@ -6111,7 +6121,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B80" s="2" t="n">
         <v>200.998</v>
@@ -6170,7 +6180,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B81" s="2" t="n">
         <v>193.143</v>
@@ -6229,7 +6239,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B82" s="2" t="n">
         <v>210.215</v>
@@ -6288,7 +6298,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B83" s="2" t="n">
         <v>233.918</v>
@@ -6347,7 +6357,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B84" s="2" t="n">
         <v>217.826</v>
@@ -6406,7 +6416,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B85" s="2" t="n">
         <v>201.979</v>
@@ -6465,7 +6475,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B86" s="2" t="n">
         <v>218.523</v>
@@ -6524,7 +6534,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B87" s="2" t="n">
         <v>259.799</v>
@@ -6583,7 +6593,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B88" s="2" t="n">
         <v>223.724</v>
@@ -6642,7 +6652,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B89" s="2" t="n">
         <v>223.584</v>
@@ -6701,7 +6711,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B90" s="2"/>
       <c r="C90" s="3" t="n">
@@ -6734,7 +6744,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B91" s="2"/>
       <c r="C91" s="3" t="n">
@@ -6767,7 +6777,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B92" s="2"/>
       <c r="C92" s="3" t="n">
@@ -6800,7 +6810,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B93" s="2"/>
       <c r="C93" s="3" t="n">
@@ -6833,7 +6843,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B94" s="2"/>
       <c r="C94" s="3"/>
@@ -6856,7 +6866,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B95" s="2"/>
       <c r="C95" s="3"/>
@@ -6879,7 +6889,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B96" s="2"/>
       <c r="C96" s="3"/>
@@ -6902,7 +6912,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B97" s="2"/>
       <c r="C97" s="3"/>
@@ -6925,7 +6935,7 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B98" s="2"/>
       <c r="C98" s="3"/>
@@ -6948,7 +6958,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B99" s="2"/>
       <c r="C99" s="3"/>
@@ -6971,7 +6981,7 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B100" s="2"/>
       <c r="C100" s="3"/>
@@ -6994,7 +7004,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B101" s="2"/>
       <c r="C101" s="3"/>
@@ -7017,7 +7027,7 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B102" s="2"/>
       <c r="C102" s="3"/>
@@ -7040,7 +7050,7 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B103" s="2"/>
       <c r="C103" s="3"/>
@@ -7063,7 +7073,7 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B104" s="2"/>
       <c r="C104" s="3"/>
@@ -7086,7 +7096,7 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B105" s="2"/>
       <c r="C105" s="3"/>
@@ -7109,7 +7119,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B106" s="2"/>
       <c r="C106" s="3"/>
@@ -7132,7 +7142,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B107" s="2"/>
       <c r="C107" s="3"/>
@@ -7155,7 +7165,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B108" s="2"/>
       <c r="C108" s="3"/>
@@ -7178,7 +7188,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B109" s="2"/>
       <c r="C109" s="3"/>
@@ -7212,97 +7222,97 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -7326,7 +7336,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B2" s="1"/>
     </row>
@@ -7336,80 +7346,80 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B4" s="1"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>-0.173164063293851</v>
+        <v>-0.168159348791623</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>-0.138709406221347</v>
+        <v>-0.136509896938198</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>-0.108842455893944</v>
+        <v>-0.11340327541941</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.0391864012261878</v>
+        <v>0.0301876153557199</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.198757636051749</v>
+        <v>0.19747373967353</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.212661182770697</v>
+        <v>0.218167362850277</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.0763193656971647</v>
+        <v>0.0778593441887351</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>-0.130224129393615</v>
+        <v>-0.128855970090904</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>-0.234116698817283</v>
+        <v>-0.227429780760657</v>
       </c>
     </row>
     <row r="14">

--- a/indicadores/GR-EPRIV-INF_out.xlsx
+++ b/indicadores/GR-EPRIV-INF_out.xlsx
@@ -113,13 +113,13 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">17/06/2026</t>
+    <t xml:space="preserve">04/08/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">focampo</t>
+    <t xml:space="preserve">fleiva</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>
@@ -1108,9 +1108,7 @@
       <c r="J7" s="1"/>
     </row>
     <row r="8">
-      <c r="A8" t="s">
-        <v>21</v>
-      </c>
+      <c r="A8"/>
       <c r="B8"/>
       <c r="C8"/>
       <c r="D8"/>
@@ -1122,14 +1120,10 @@
       <c r="J8" s="1"/>
     </row>
     <row r="9">
-      <c r="A9" t="s">
-        <v>22</v>
-      </c>
+      <c r="A9"/>
       <c r="B9"/>
       <c r="C9"/>
-      <c r="D9" t="n">
-        <v>-0.227429780760657</v>
-      </c>
+      <c r="D9"/>
       <c r="E9"/>
       <c r="F9"/>
       <c r="G9"/>
@@ -1139,13 +1133,11 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B10"/>
       <c r="C10"/>
-      <c r="D10" t="n">
-        <v>4</v>
-      </c>
+      <c r="D10"/>
       <c r="E10"/>
       <c r="F10"/>
       <c r="G10"/>
@@ -1154,10 +1146,14 @@
       <c r="J10" s="1"/>
     </row>
     <row r="11">
-      <c r="A11"/>
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
       <c r="B11"/>
       <c r="C11"/>
-      <c r="D11"/>
+      <c r="D11" t="n">
+        <v>-0.242682477526942</v>
+      </c>
       <c r="E11"/>
       <c r="F11"/>
       <c r="G11"/>
@@ -1167,11 +1163,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12"/>
       <c r="C12"/>
-      <c r="D12"/>
+      <c r="D12" t="n">
+        <v>4</v>
+      </c>
       <c r="E12"/>
       <c r="F12"/>
       <c r="G12"/>
@@ -1180,14 +1178,10 @@
       <c r="J12" s="1"/>
     </row>
     <row r="13">
-      <c r="A13" t="s">
-        <v>25</v>
-      </c>
+      <c r="A13"/>
       <c r="B13"/>
       <c r="C13"/>
-      <c r="D13" t="n">
-        <v>0.038995877860649</v>
-      </c>
+      <c r="D13"/>
       <c r="E13"/>
       <c r="F13"/>
       <c r="G13"/>
@@ -1196,7 +1190,9 @@
       <c r="J13" s="1"/>
     </row>
     <row r="14">
-      <c r="A14"/>
+      <c r="A14" t="s">
+        <v>24</v>
+      </c>
       <c r="B14"/>
       <c r="C14"/>
       <c r="D14"/>
@@ -1209,11 +1205,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B15"/>
       <c r="C15"/>
-      <c r="D15"/>
+      <c r="D15" t="n">
+        <v>0.0375336604798402</v>
+      </c>
       <c r="E15"/>
       <c r="F15"/>
       <c r="G15"/>
@@ -1222,9 +1220,7 @@
       <c r="J15" s="1"/>
     </row>
     <row r="16">
-      <c r="A16" t="s">
-        <v>27</v>
-      </c>
+      <c r="A16"/>
       <c r="B16"/>
       <c r="C16"/>
       <c r="D16"/>
@@ -1237,7 +1233,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B17"/>
       <c r="C17"/>
@@ -1251,13 +1247,11 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B18"/>
       <c r="C18"/>
-      <c r="D18" t="n">
-        <v>0.673305892777082</v>
-      </c>
+      <c r="D18"/>
       <c r="E18"/>
       <c r="F18"/>
       <c r="G18"/>
@@ -1267,7 +1261,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B19"/>
       <c r="C19"/>
@@ -1286,7 +1280,7 @@
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20" t="n">
-        <v>0.514476773648625</v>
+        <v>0.686219683349348</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -1296,7 +1290,9 @@
       <c r="J20" s="1"/>
     </row>
     <row r="21">
-      <c r="A21"/>
+      <c r="A21" t="s">
+        <v>30</v>
+      </c>
       <c r="B21"/>
       <c r="C21"/>
       <c r="D21"/>
@@ -1308,10 +1304,14 @@
       <c r="J21" s="1"/>
     </row>
     <row r="22">
-      <c r="A22"/>
+      <c r="A22" t="s">
+        <v>29</v>
+      </c>
       <c r="B22"/>
       <c r="C22"/>
-      <c r="D22"/>
+      <c r="D22" t="n">
+        <v>0.486054705327746</v>
+      </c>
       <c r="E22"/>
       <c r="F22"/>
       <c r="G22"/>
@@ -1546,40 +1546,40 @@
         <v>184.844</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>-3.7457939628279</v>
+        <v>-3.74579396197321</v>
       </c>
       <c r="G2" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H2" s="8" t="n">
-        <v>191.045083655607</v>
+        <v>191.045083654291</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>187.656366159075</v>
+        <v>187.656401890067</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>188.233046615371</v>
+        <v>188.233046677968</v>
       </c>
       <c r="K2" s="11" t="n">
-        <v>188.589793962828</v>
+        <v>188.589793961973</v>
       </c>
       <c r="L2" s="12" t="n">
-        <v>188.589793962828</v>
+        <v>188.589793961973</v>
       </c>
       <c r="M2" s="13" t="n">
-        <v>189.879483082141</v>
+        <v>189.879483081504</v>
       </c>
       <c r="N2" s="14" t="n">
-        <v>189.879483082141</v>
+        <v>189.879483081504</v>
       </c>
       <c r="O2" s="15"/>
       <c r="P2" s="16"/>
       <c r="Q2" s="17"/>
       <c r="R2" s="18" t="n">
-        <v>0.993898819319701</v>
+        <v>0.993898819323214</v>
       </c>
       <c r="S2" s="19" t="n">
-        <v>1.01184674396382</v>
+        <v>1.01184655129826</v>
       </c>
     </row>
     <row r="3">
@@ -1599,44 +1599,44 @@
         <v>187.087</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>-5.37186132076815</v>
+        <v>-5.37186132056702</v>
       </c>
       <c r="G3" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>189.12463927302</v>
+        <v>189.124639273618</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>187.202043372929</v>
+        <v>187.20208295012</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>187.672267121634</v>
+        <v>187.672267200742</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>192.458861320768</v>
+        <v>192.458861320567</v>
       </c>
       <c r="L3" s="12" t="n">
-        <v>192.458861320768</v>
+        <v>192.458861320567</v>
       </c>
       <c r="M3" s="13" t="n">
-        <v>189.114990042871</v>
+        <v>189.114990043298</v>
       </c>
       <c r="N3" s="14" t="n">
-        <v>189.114990042871</v>
+        <v>189.114990043298</v>
       </c>
       <c r="O3" s="15" t="n">
-        <v>-0.00403432836295332</v>
+        <v>-0.00403432835734053</v>
       </c>
       <c r="P3" s="16"/>
       <c r="Q3" s="17" t="n">
-        <v>-0.00402620139291177</v>
+        <v>-0.00402620138732157</v>
       </c>
       <c r="R3" s="18" t="n">
-        <v>0.999948979518552</v>
+        <v>0.999948979517649</v>
       </c>
       <c r="S3" s="19" t="n">
-        <v>1.01021862067035</v>
+        <v>1.010218407098</v>
       </c>
     </row>
     <row r="4">
@@ -1656,44 +1656,44 @@
         <v>186.517</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>3.56455643288175</v>
+        <v>3.5645564299161</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>185.698939889549</v>
+        <v>185.698939891301</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>186.748303979161</v>
+        <v>186.748347380219</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>187.113271364633</v>
+        <v>187.113271459936</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>182.952443567118</v>
+        <v>182.952443570084</v>
       </c>
       <c r="L4" s="12" t="n">
-        <v>182.952443567118</v>
+        <v>182.952443570084</v>
       </c>
       <c r="M4" s="13" t="n">
-        <v>185.593680776486</v>
+        <v>185.593680777781</v>
       </c>
       <c r="N4" s="14" t="n">
-        <v>185.593680776486</v>
+        <v>185.593680777781</v>
       </c>
       <c r="O4" s="15" t="n">
-        <v>-0.0187954707447947</v>
+        <v>-0.0187954707400712</v>
       </c>
       <c r="P4" s="16"/>
       <c r="Q4" s="17" t="n">
-        <v>-0.0186199373491588</v>
+        <v>-0.0186199373445233</v>
       </c>
       <c r="R4" s="18" t="n">
-        <v>0.999433173322766</v>
+        <v>0.999433173320315</v>
       </c>
       <c r="S4" s="19" t="n">
-        <v>0.993817222549963</v>
+        <v>0.993816991589829</v>
       </c>
     </row>
     <row r="5">
@@ -1713,44 +1713,44 @@
         <v>189.606</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>5.59502534906231</v>
+        <v>5.59502534960905</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>182.156230495883</v>
+        <v>182.156230495493</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>186.299016881364</v>
+        <v>186.299064036889</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>186.581776052103</v>
+        <v>186.58177616257</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>184.010974650938</v>
+        <v>184.010974650391</v>
       </c>
       <c r="L5" s="12" t="n">
-        <v>184.010974650938</v>
+        <v>184.010974650391</v>
       </c>
       <c r="M5" s="13" t="n">
-        <v>183.286154297388</v>
+        <v>183.286154297008</v>
       </c>
       <c r="N5" s="14" t="n">
-        <v>183.286154297388</v>
+        <v>183.286154297008</v>
       </c>
       <c r="O5" s="15" t="n">
-        <v>-0.0125111559873121</v>
+        <v>-0.0125111559963675</v>
       </c>
       <c r="P5" s="16"/>
       <c r="Q5" s="17" t="n">
-        <v>-0.0124332168500758</v>
+        <v>-0.0124332168590187</v>
       </c>
       <c r="R5" s="18" t="n">
-        <v>1.00620304778172</v>
+        <v>1.00620304778179</v>
       </c>
       <c r="S5" s="19" t="n">
-        <v>0.983827812758159</v>
+        <v>0.983827563732235</v>
       </c>
     </row>
     <row r="6">
@@ -1770,46 +1770,46 @@
         <v>178.421</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>-3.74922432055751</v>
+        <v>-3.7492243171653</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>184.387060489615</v>
+        <v>184.387060486742</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>185.855678570377</v>
+        <v>185.855729336775</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>186.082693752789</v>
+        <v>186.082693876213</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>182.170224320558</v>
+        <v>182.170224317165</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>182.170224320558</v>
+        <v>182.170224317165</v>
       </c>
       <c r="M6" s="13" t="n">
-        <v>184.394308646302</v>
+        <v>184.394308644378</v>
       </c>
       <c r="N6" s="14" t="n">
-        <v>184.394308646302</v>
+        <v>184.394308644378</v>
       </c>
       <c r="O6" s="15" t="n">
-        <v>0.00602783022744576</v>
+        <v>0.00602783021908769</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>-0.028887662567876</v>
+        <v>-0.028887662574749</v>
       </c>
       <c r="Q6" s="17" t="n">
-        <v>0.00604603415441773</v>
+        <v>0.00604603414600913</v>
       </c>
       <c r="R6" s="18" t="n">
-        <v>1.00003930946492</v>
+        <v>1.00003930947007</v>
       </c>
       <c r="S6" s="19" t="n">
-        <v>0.992137071434586</v>
+        <v>0.992136800422501</v>
       </c>
     </row>
     <row r="7">
@@ -1829,46 +1829,46 @@
         <v>183.734</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>-5.49181129315402</v>
+        <v>-5.49181129279125</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>187.149141164796</v>
+        <v>187.149141165622</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>185.418355510642</v>
+        <v>185.418409640656</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>185.608083028429</v>
+        <v>185.608083160874</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>189.225811293154</v>
+        <v>189.225811292791</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>189.225811293154</v>
+        <v>189.225811292791</v>
       </c>
       <c r="M7" s="13" t="n">
-        <v>186.851000960686</v>
+        <v>186.851000961327</v>
       </c>
       <c r="N7" s="14" t="n">
-        <v>186.851000960686</v>
+        <v>186.851000961327</v>
       </c>
       <c r="O7" s="15" t="n">
-        <v>0.0132350664730482</v>
+        <v>0.01323506648691</v>
       </c>
       <c r="P7" s="16" t="n">
-        <v>-0.0119714946005699</v>
+        <v>-0.0119714945994122</v>
       </c>
       <c r="Q7" s="17" t="n">
-        <v>0.0133230376383049</v>
+        <v>0.0133230376523514</v>
       </c>
       <c r="R7" s="18" t="n">
-        <v>0.99840693789854</v>
+        <v>0.998406937897558</v>
       </c>
       <c r="S7" s="19" t="n">
-        <v>1.00772655676995</v>
+        <v>1.00772626258335</v>
       </c>
     </row>
     <row r="8">
@@ -1888,46 +1888,46 @@
         <v>190.427</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>3.64484306412342</v>
+        <v>3.64484305744165</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>187.040522442146</v>
+        <v>187.040522446671</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>184.984810757698</v>
+        <v>184.984867868674</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>185.130440093603</v>
+        <v>185.130440228766</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>186.782156935877</v>
+        <v>186.782156942558</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>186.782156935877</v>
+        <v>186.782156942558</v>
       </c>
       <c r="M8" s="13" t="n">
-        <v>186.879019286987</v>
+        <v>186.879019290159</v>
       </c>
       <c r="N8" s="14" t="n">
-        <v>186.879019286987</v>
+        <v>186.879019290159</v>
       </c>
       <c r="O8" s="15" t="n">
-        <v>0.000149938858728021</v>
+        <v>0.000149938872267159</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>0.00692555104852732</v>
+        <v>0.00692555105858417</v>
       </c>
       <c r="Q8" s="17" t="n">
-        <v>0.000149950100120533</v>
+        <v>0.000149950113661701</v>
       </c>
       <c r="R8" s="18" t="n">
-        <v>0.999136533874852</v>
+        <v>0.999136533867635</v>
       </c>
       <c r="S8" s="19" t="n">
-        <v>1.01023980575233</v>
+        <v>1.01023949387487</v>
       </c>
     </row>
     <row r="9">
@@ -1947,46 +1947,46 @@
         <v>190.167</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>5.44104801695833</v>
+        <v>5.44104801727398</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>186.438705092461</v>
+        <v>186.438705091266</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>184.555187026943</v>
+        <v>184.555246567002</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>184.640349804213</v>
+        <v>184.640349932764</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>184.725951983042</v>
+        <v>184.725951982726</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>184.725951983042</v>
+        <v>184.725951982726</v>
       </c>
       <c r="M9" s="13" t="n">
-        <v>186.414813984482</v>
+        <v>186.414813983484</v>
       </c>
       <c r="N9" s="14" t="n">
-        <v>186.414813984482</v>
+        <v>186.414813983484</v>
       </c>
       <c r="O9" s="15" t="n">
-        <v>-0.00248707854462953</v>
+        <v>-0.00248707856695228</v>
       </c>
       <c r="P9" s="16" t="n">
-        <v>0.0170698092231116</v>
+        <v>0.0170698092197759</v>
       </c>
       <c r="Q9" s="17" t="n">
-        <v>-0.00248398832718799</v>
+        <v>-0.00248398834945529</v>
       </c>
       <c r="R9" s="18" t="n">
-        <v>0.999871855428479</v>
+        <v>0.999871855429535</v>
       </c>
       <c r="S9" s="19" t="n">
-        <v>1.01007626492377</v>
+        <v>1.01007593905387</v>
       </c>
     </row>
     <row r="10">
@@ -2006,46 +2006,46 @@
         <v>186.12</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>-3.30519503596801</v>
+        <v>-3.30519502592613</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>186.951327015127</v>
+        <v>186.951327008485</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>184.130750375142</v>
+        <v>184.130811587486</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>184.136655600372</v>
+        <v>184.136655709309</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>189.425195035968</v>
+        <v>189.425195025926</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>189.425195035968</v>
+        <v>189.425195025926</v>
       </c>
       <c r="M10" s="13" t="n">
-        <v>186.874540148524</v>
+        <v>186.874540143622</v>
       </c>
       <c r="N10" s="14" t="n">
-        <v>186.874540148524</v>
+        <v>186.874540143622</v>
       </c>
       <c r="O10" s="15" t="n">
-        <v>0.00246311013897403</v>
+        <v>0.00246311011810047</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>0.0134506944407888</v>
+        <v>0.013450694424781</v>
       </c>
       <c r="Q10" s="17" t="n">
-        <v>0.00246614608686535</v>
+        <v>0.00246614606594031</v>
       </c>
       <c r="R10" s="18" t="n">
-        <v>0.99958926813824</v>
+        <v>0.999589268147537</v>
       </c>
       <c r="S10" s="19" t="n">
-        <v>1.01490131207195</v>
+        <v>1.0149009746521</v>
       </c>
     </row>
     <row r="11">
@@ -2065,46 +2065,46 @@
         <v>178.072</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>-5.84981853911663</v>
+        <v>-5.84981853991157</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>186.039983098494</v>
+        <v>186.039983097534</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>183.712873587154</v>
+        <v>183.712935472855</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>183.618628933087</v>
+        <v>183.618629005094</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>183.921818539117</v>
+        <v>183.921818539912</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>183.921818539117</v>
+        <v>183.921818539912</v>
       </c>
       <c r="M11" s="13" t="n">
-        <v>185.554578357555</v>
+        <v>185.554578357738</v>
       </c>
       <c r="N11" s="14" t="n">
-        <v>185.554578357555</v>
+        <v>185.554578357738</v>
       </c>
       <c r="O11" s="15" t="n">
-        <v>-0.00708842167405468</v>
+        <v>-0.00708842164684063</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>-0.00693826951135113</v>
+        <v>-0.0069382695137773</v>
       </c>
       <c r="Q11" s="17" t="n">
-        <v>-0.00706335806857328</v>
+        <v>-0.00706335804155145</v>
       </c>
       <c r="R11" s="18" t="n">
-        <v>0.99739085796045</v>
+        <v>0.997390857966582</v>
       </c>
       <c r="S11" s="19" t="n">
-        <v>1.01002490862202</v>
+        <v>1.01002456838514</v>
       </c>
     </row>
     <row r="12">
@@ -2124,46 +2124,46 @@
         <v>188.752</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>3.80251868398283</v>
+        <v>3.80251867479819</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>183.519786251726</v>
+        <v>183.519786265425</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>183.306238475753</v>
+        <v>183.306299755488</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>183.111983950545</v>
+        <v>183.111983963394</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>184.949481316017</v>
+        <v>184.949481325202</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>184.949481316017</v>
+        <v>184.949481325202</v>
       </c>
       <c r="M12" s="13" t="n">
-        <v>183.553809840552</v>
+        <v>183.553809849348</v>
       </c>
       <c r="N12" s="14" t="n">
-        <v>183.553809840552</v>
+        <v>183.553809849348</v>
       </c>
       <c r="O12" s="15" t="n">
-        <v>-0.0108411955785957</v>
+        <v>-0.0108411955316639</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>-0.017793380225998</v>
+        <v>-0.0177933801955992</v>
       </c>
       <c r="Q12" s="17" t="n">
-        <v>-0.0107826416071877</v>
+        <v>-0.0107826415607619</v>
       </c>
       <c r="R12" s="18" t="n">
-        <v>1.00018539466246</v>
+        <v>1.00018539463572</v>
       </c>
       <c r="S12" s="19" t="n">
-        <v>1.00135058886625</v>
+        <v>1.00135025416033</v>
       </c>
     </row>
     <row r="13">
@@ -2183,46 +2183,46 @@
         <v>185.205</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>4.81054180894204</v>
+        <v>4.81054179292318</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>181.323192470001</v>
+        <v>181.323192469186</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>182.915657444306</v>
+        <v>182.915716519682</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>182.64395074896</v>
+        <v>182.643950675157</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>180.394458191058</v>
+        <v>180.394458207077</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>180.394458191058</v>
+        <v>180.394458207077</v>
       </c>
       <c r="M13" s="13" t="n">
-        <v>180.838126712014</v>
+        <v>180.838126712498</v>
       </c>
       <c r="N13" s="14" t="n">
-        <v>180.838126712014</v>
+        <v>180.838126712498</v>
       </c>
       <c r="O13" s="15" t="n">
-        <v>-0.0149055625871792</v>
+        <v>-0.0149055626324193</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>-0.0299154726669539</v>
+        <v>-0.0299154726591621</v>
       </c>
       <c r="Q13" s="17" t="n">
-        <v>-0.0147950245810606</v>
+        <v>-0.0147950246256314</v>
       </c>
       <c r="R13" s="18" t="n">
-        <v>0.997324855406639</v>
+        <v>0.997324855413794</v>
       </c>
       <c r="S13" s="19" t="n">
-        <v>0.988642138342233</v>
+        <v>0.988641819048066</v>
       </c>
     </row>
     <row r="14">
@@ -2242,46 +2242,46 @@
         <v>175.164</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>-2.45010914992275</v>
+        <v>-2.4501091106382</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>175.529823485402</v>
+        <v>175.529823470205</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>182.546969922956</v>
+        <v>182.547024838212</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>182.250946911375</v>
+        <v>182.250946718144</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>177.614109149923</v>
+        <v>177.614109110638</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>177.614109149923</v>
+        <v>177.614109110638</v>
       </c>
       <c r="M14" s="13" t="n">
-        <v>176.773369154893</v>
+        <v>176.773369140871</v>
       </c>
       <c r="N14" s="14" t="n">
-        <v>176.773369154893</v>
+        <v>176.773369140871</v>
       </c>
       <c r="O14" s="15" t="n">
-        <v>-0.0227337916522047</v>
+        <v>-0.0227337917342081</v>
       </c>
       <c r="P14" s="16" t="n">
-        <v>-0.054053221940251</v>
+        <v>-0.0540532219904785</v>
       </c>
       <c r="Q14" s="17" t="n">
-        <v>-0.0224773261647087</v>
+        <v>-0.0224773262448688</v>
       </c>
       <c r="R14" s="18" t="n">
-        <v>1.00708452640582</v>
+        <v>1.00708452641312</v>
       </c>
       <c r="S14" s="19" t="n">
-        <v>0.968371971495884</v>
+        <v>0.968371680105669</v>
       </c>
     </row>
     <row r="15">
@@ -2301,46 +2301,46 @@
         <v>163.593</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>-5.77601345271781</v>
+        <v>-5.77601346264258</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>0.640970274043334</v>
+        <v>0.640970273660769</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>175.223087708967</v>
+        <v>175.223087703005</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>182.204439592314</v>
+        <v>182.204487997411</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>181.958142558045</v>
+        <v>181.95814220777</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>169.369013452718</v>
+        <v>169.369013462643</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>171.470800128669</v>
+        <v>171.470800135129</v>
       </c>
       <c r="M15" s="13" t="n">
-        <v>176.288665726119</v>
+        <v>176.28866572212</v>
       </c>
       <c r="N15" s="14" t="n">
-        <v>176.288665726119</v>
+        <v>176.28866572212</v>
       </c>
       <c r="O15" s="15" t="n">
-        <v>-0.00274571426775113</v>
+        <v>-0.00274571421111223</v>
       </c>
       <c r="P15" s="16" t="n">
-        <v>-0.0499363190790195</v>
+        <v>-0.0499363191015101</v>
       </c>
       <c r="Q15" s="17" t="n">
-        <v>-0.00274194824192986</v>
+        <v>-0.00274194818544626</v>
       </c>
       <c r="R15" s="18" t="n">
-        <v>1.00608126492396</v>
+        <v>1.00608126493536</v>
       </c>
       <c r="S15" s="19" t="n">
-        <v>0.967532218866718</v>
+        <v>0.967531961806696</v>
       </c>
     </row>
     <row r="16">
@@ -2360,46 +2360,46 @@
         <v>188.0315</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>3.43254650278531</v>
+        <v>3.43254649241844</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>182.554630611875</v>
+        <v>182.554630639496</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>181.889247095007</v>
+        <v>181.88928621128</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>181.767523620415</v>
+        <v>181.767523071417</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>184.598953497215</v>
+        <v>184.598953507582</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>184.598953497215</v>
+        <v>184.598953507582</v>
       </c>
       <c r="M16" s="13" t="n">
-        <v>182.007431600444</v>
+        <v>182.007431617388</v>
       </c>
       <c r="N16" s="14" t="n">
-        <v>182.007431600444</v>
+        <v>182.007431617388</v>
       </c>
       <c r="O16" s="15" t="n">
-        <v>0.0319247215741744</v>
+        <v>0.0319247216899528</v>
       </c>
       <c r="P16" s="16" t="n">
-        <v>-0.00842465891310784</v>
+        <v>-0.00842465886831467</v>
       </c>
       <c r="Q16" s="17" t="n">
-        <v>0.0324397819381648</v>
+        <v>0.0324397820576989</v>
       </c>
       <c r="R16" s="18" t="n">
-        <v>0.997002546527597</v>
+        <v>0.997002546469561</v>
       </c>
       <c r="S16" s="19" t="n">
-        <v>1.00064976081503</v>
+        <v>1.00064954571305</v>
       </c>
     </row>
     <row r="17">
@@ -2419,46 +2419,46 @@
         <v>191.384</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>4.02298072132175</v>
+        <v>4.02298068074148</v>
       </c>
       <c r="G17" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>184.965930524754</v>
+        <v>184.965930534954</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>181.595864548996</v>
+        <v>181.595891138908</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>181.628639317785</v>
+        <v>181.628638526102</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>187.361019278678</v>
+        <v>187.361019319259</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>187.361019278678</v>
+        <v>187.361019319259</v>
       </c>
       <c r="M17" s="13" t="n">
-        <v>184.150945115933</v>
+        <v>184.150945129419</v>
       </c>
       <c r="N17" s="14" t="n">
-        <v>184.150945115933</v>
+        <v>184.150945129419</v>
       </c>
       <c r="O17" s="15" t="n">
-        <v>0.0117082559809636</v>
+        <v>0.011708255961104</v>
       </c>
       <c r="P17" s="16" t="n">
-        <v>0.0183192475179483</v>
+        <v>0.0183192475897951</v>
       </c>
       <c r="Q17" s="17" t="n">
-        <v>0.0117770658958305</v>
+        <v>0.011777065875737</v>
       </c>
       <c r="R17" s="18" t="n">
-        <v>0.995593862034438</v>
+        <v>0.995593862052447</v>
       </c>
       <c r="S17" s="19" t="n">
-        <v>1.01407014732017</v>
+        <v>1.0140699989107</v>
       </c>
     </row>
     <row r="18">
@@ -2478,46 +2478,46 @@
         <v>174.593</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>-1.60218334144013</v>
+        <v>-1.60218327243252</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>0.793374754069144</v>
+        <v>0.793374750285373</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>181.458843465946</v>
+        <v>181.458843452632</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>181.320457638744</v>
+        <v>181.320467981442</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>181.505196018839</v>
+        <v>181.505194941023</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>176.19518334144</v>
+        <v>176.195183272433</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>177.282788409163</v>
+        <v>177.282788371579</v>
       </c>
       <c r="M18" s="13" t="n">
-        <v>181.711700036735</v>
+        <v>181.711700030263</v>
       </c>
       <c r="N18" s="14" t="n">
-        <v>181.711700036735</v>
+        <v>181.711700030263</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>-0.0133344098076615</v>
+        <v>-0.0133344099165125</v>
       </c>
       <c r="P18" s="16" t="n">
-        <v>0.0279359436630708</v>
+        <v>0.0279359437079985</v>
       </c>
       <c r="Q18" s="17" t="n">
-        <v>-0.0132459004088324</v>
+        <v>-0.0132459005162416</v>
       </c>
       <c r="R18" s="18" t="n">
-        <v>1.00139346512939</v>
+        <v>1.0013934651672</v>
       </c>
       <c r="S18" s="19" t="n">
-        <v>1.0021577399654</v>
+        <v>1.00215768276564</v>
       </c>
     </row>
     <row r="19">
@@ -2537,46 +2537,46 @@
         <v>179.795</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>-5.12520404993815</v>
+        <v>-5.12520405863624</v>
       </c>
       <c r="G19" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>182.633528941698</v>
+        <v>182.633528925143</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>181.062795270422</v>
+        <v>181.062785145142</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>181.389561992063</v>
+        <v>181.389560589344</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>184.920204049938</v>
+        <v>184.920204058636</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>184.920204049938</v>
+        <v>184.920204058636</v>
       </c>
       <c r="M19" s="13" t="n">
-        <v>182.892410256826</v>
+        <v>182.892410252803</v>
       </c>
       <c r="N19" s="14" t="n">
-        <v>182.892410256826</v>
+        <v>182.892410252803</v>
       </c>
       <c r="O19" s="15" t="n">
-        <v>0.00647669246768384</v>
+        <v>0.00647669248130636</v>
       </c>
       <c r="P19" s="16" t="n">
-        <v>0.0374598361358458</v>
+        <v>0.0374598361365619</v>
       </c>
       <c r="Q19" s="17" t="n">
-        <v>0.00649771159398105</v>
+        <v>0.00649771160769208</v>
       </c>
       <c r="R19" s="18" t="n">
-        <v>1.00141749062523</v>
+        <v>1.00141749069398</v>
       </c>
       <c r="S19" s="19" t="n">
-        <v>1.01010486435754</v>
+        <v>1.01010492082177</v>
       </c>
     </row>
     <row r="20">
@@ -2596,46 +2596,46 @@
         <v>187.311</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>2.86455548173446</v>
+        <v>2.86455547763807</v>
       </c>
       <c r="G20" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>184.285005439437</v>
+        <v>184.285005473042</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>180.820122806929</v>
+        <v>180.820087486515</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>181.252993467898</v>
+        <v>181.252991711382</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>184.446444518266</v>
+        <v>184.446444522362</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>184.446444518266</v>
+        <v>184.446444522362</v>
       </c>
       <c r="M20" s="13" t="n">
-        <v>183.811990129797</v>
+        <v>183.81199015313</v>
       </c>
       <c r="N20" s="14" t="n">
-        <v>183.811990129797</v>
+        <v>183.81199015313</v>
       </c>
       <c r="O20" s="15" t="n">
-        <v>0.00501538459641807</v>
+        <v>0.00501538474535482</v>
       </c>
       <c r="P20" s="16" t="n">
-        <v>0.00991475190592306</v>
+        <v>0.00991475194010749</v>
       </c>
       <c r="Q20" s="17" t="n">
-        <v>0.00502798269036631</v>
+        <v>0.0050279828400519</v>
       </c>
       <c r="R20" s="18" t="n">
-        <v>0.997433240384847</v>
+        <v>0.997433240329578</v>
       </c>
       <c r="S20" s="19" t="n">
-        <v>1.01654609717339</v>
+        <v>1.01654629586903</v>
       </c>
     </row>
     <row r="21">
@@ -2655,46 +2655,46 @@
         <v>184.615</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>3.18013256728208</v>
+        <v>3.18013249083927</v>
       </c>
       <c r="G21" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>183.216519286244</v>
+        <v>183.216519332574</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>180.592096491655</v>
+        <v>180.592030748885</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>181.084399887072</v>
+        <v>181.084397764798</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>181.434867432718</v>
+        <v>181.434867509161</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>181.434867432718</v>
+        <v>181.434867509161</v>
       </c>
       <c r="M21" s="13" t="n">
-        <v>182.011977347966</v>
+        <v>182.011977372433</v>
       </c>
       <c r="N21" s="14" t="n">
-        <v>182.011977347966</v>
+        <v>182.011977372433</v>
       </c>
       <c r="O21" s="15" t="n">
-        <v>-0.00984094793438337</v>
+        <v>-0.0098409479268971</v>
       </c>
       <c r="P21" s="16" t="n">
-        <v>-0.0116152961725012</v>
+        <v>-0.0116152961120175</v>
       </c>
       <c r="Q21" s="17" t="n">
-        <v>-0.00979268425612445</v>
+        <v>-0.00979268424871149</v>
       </c>
       <c r="R21" s="18" t="n">
-        <v>0.993425582240233</v>
+        <v>0.993425582122569</v>
       </c>
       <c r="S21" s="19" t="n">
-        <v>1.00786236432211</v>
+        <v>1.00786273136007</v>
       </c>
     </row>
     <row r="22">
@@ -2714,46 +2714,46 @@
         <v>194.435</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>-1.70012671810568</v>
+        <v>-1.70012667654715</v>
       </c>
       <c r="G22" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>180.731730008162</v>
+        <v>180.73172994905</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>180.380639019058</v>
+        <v>180.380537148725</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>180.888657945566</v>
+        <v>180.888655471312</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>196.135126718106</v>
+        <v>196.135126676547</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>180.731730008162</v>
+        <v>180.73172994905</v>
       </c>
       <c r="M22" s="13" t="n">
-        <v>179.149365610857</v>
+        <v>179.149365559556</v>
       </c>
       <c r="N22" s="14" t="n">
-        <v>179.149365610857</v>
+        <v>179.149365559556</v>
       </c>
       <c r="O22" s="15" t="n">
-        <v>-0.0158525918769694</v>
+        <v>-0.015852592297757</v>
       </c>
       <c r="P22" s="16" t="n">
-        <v>-0.0141010976473182</v>
+        <v>-0.0141010978945246</v>
       </c>
       <c r="Q22" s="17" t="n">
-        <v>-0.0157276008909896</v>
+        <v>-0.0157276013051593</v>
       </c>
       <c r="R22" s="18" t="n">
-        <v>0.991244678523061</v>
+        <v>0.991244678563415</v>
       </c>
       <c r="S22" s="19" t="n">
-        <v>0.993174026797465</v>
+        <v>0.993174587410426</v>
       </c>
     </row>
     <row r="23">
@@ -2773,46 +2773,46 @@
         <v>169.467</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>-3.03843236605636</v>
+        <v>-3.03843226197312</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>0.686477414889831</v>
+        <v>0.686477428947127</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>176.312821961007</v>
+        <v>176.312821838365</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>180.188199815432</v>
+        <v>180.188055675483</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>180.672396677089</v>
+        <v>180.672393901363</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>172.505432366056</v>
+        <v>172.505432261973</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>173.699134994387</v>
+        <v>173.699134830963</v>
       </c>
       <c r="M23" s="13" t="n">
-        <v>176.072264117088</v>
+        <v>176.072264031286</v>
       </c>
       <c r="N23" s="14" t="n">
-        <v>176.072264117088</v>
+        <v>176.072264031286</v>
       </c>
       <c r="O23" s="15" t="n">
-        <v>-0.0173254002958146</v>
+        <v>-0.0173254004967679</v>
       </c>
       <c r="P23" s="16" t="n">
-        <v>-0.037290482038925</v>
+        <v>-0.0372904824868913</v>
       </c>
       <c r="Q23" s="17" t="n">
-        <v>-0.0171761785662863</v>
+        <v>-0.017176178763788</v>
       </c>
       <c r="R23" s="18" t="n">
-        <v>0.998635619115824</v>
+        <v>0.99863561932382</v>
       </c>
       <c r="S23" s="19" t="n">
-        <v>0.977157573567196</v>
+        <v>0.977158354760151</v>
       </c>
     </row>
     <row r="24">
@@ -2832,46 +2832,46 @@
         <v>178.154</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>1.99494352858279</v>
+        <v>1.99494348583328</v>
       </c>
       <c r="G24" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>176.128507731704</v>
+        <v>176.128507694431</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>180.017447738942</v>
+        <v>180.017254814109</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>180.441460475662</v>
+        <v>180.44145749778</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>176.159056471417</v>
+        <v>176.159056514167</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>176.159056471417</v>
+        <v>176.159056514167</v>
       </c>
       <c r="M24" s="13" t="n">
-        <v>177.716457089867</v>
+        <v>177.716457105137</v>
       </c>
       <c r="N24" s="14" t="n">
-        <v>177.716457089867</v>
+        <v>177.716457105137</v>
       </c>
       <c r="O24" s="15" t="n">
-        <v>0.00929484017764972</v>
+        <v>0.00929484075088504</v>
       </c>
       <c r="P24" s="16" t="n">
-        <v>-0.0331617814247323</v>
+        <v>-0.0331617814643915</v>
       </c>
       <c r="Q24" s="17" t="n">
-        <v>0.00933817135267723</v>
+        <v>0.00933817193126552</v>
       </c>
       <c r="R24" s="18" t="n">
-        <v>1.00901585653915</v>
+        <v>1.00901585683938</v>
       </c>
       <c r="S24" s="19" t="n">
-        <v>0.987217957603693</v>
+        <v>0.987219015691872</v>
       </c>
     </row>
     <row r="25">
@@ -2891,46 +2891,46 @@
         <v>186.889</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>2.04041957775156</v>
+        <v>2.04041943874801</v>
       </c>
       <c r="G25" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>186.599327911265</v>
+        <v>186.599328230084</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>179.866995982239</v>
+        <v>179.866747474021</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>180.166827426895</v>
+        <v>180.166824408038</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>184.848580422248</v>
+        <v>184.848580561252</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>184.848580422248</v>
+        <v>184.848580561252</v>
       </c>
       <c r="M25" s="13" t="n">
-        <v>185.676291884888</v>
+        <v>185.676292125131</v>
       </c>
       <c r="N25" s="14" t="n">
-        <v>185.676291884888</v>
+        <v>185.676292125131</v>
       </c>
       <c r="O25" s="15" t="n">
-        <v>0.0438154487857245</v>
+        <v>0.0438154499936821</v>
       </c>
       <c r="P25" s="16" t="n">
-        <v>0.0201322714599002</v>
+        <v>0.0201322726426942</v>
       </c>
       <c r="Q25" s="17" t="n">
-        <v>0.0447895199204638</v>
+        <v>0.0447895211825251</v>
       </c>
       <c r="R25" s="18" t="n">
-        <v>0.995053379684113</v>
+        <v>0.995053379271469</v>
       </c>
       <c r="S25" s="19" t="n">
-        <v>1.03229773128153</v>
+        <v>1.03229915886453</v>
       </c>
     </row>
     <row r="26">
@@ -2950,46 +2950,46 @@
         <v>195.657</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>-2.20787489378991</v>
+        <v>-2.20787491138018</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>0.796261269651909</v>
+        <v>0.796261382616674</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>192.878465739207</v>
+        <v>192.878466048032</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>179.733046243431</v>
+        <v>179.732735190703</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>179.798063596373</v>
+        <v>179.798060774697</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>197.86487489379</v>
+        <v>197.86487491138</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>196.848950223639</v>
+        <v>196.848950863854</v>
       </c>
       <c r="M26" s="13" t="n">
-        <v>190.690064676392</v>
+        <v>190.690064955595</v>
       </c>
       <c r="N26" s="14" t="n">
-        <v>190.690064676392</v>
+        <v>190.690064955595</v>
       </c>
       <c r="O26" s="15" t="n">
-        <v>0.0266446207105827</v>
+        <v>0.0266446208808741</v>
       </c>
       <c r="P26" s="16" t="n">
-        <v>0.0644194246861223</v>
+        <v>0.0644194265494211</v>
       </c>
       <c r="Q26" s="17" t="n">
-        <v>0.027002762391509</v>
+        <v>0.0270027625663987</v>
       </c>
       <c r="R26" s="18" t="n">
-        <v>0.988653989679835</v>
+        <v>0.988653989544422</v>
       </c>
       <c r="S26" s="19" t="n">
-        <v>1.06096273702567</v>
+        <v>1.06096457472405</v>
       </c>
     </row>
     <row r="27">
@@ -3009,46 +3009,46 @@
         <v>183.563</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>-0.650777836042982</v>
+        <v>-0.650777533421709</v>
       </c>
       <c r="G27" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H27" s="8" t="n">
-        <v>184.862919419203</v>
+        <v>184.862919437265</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>179.614913710903</v>
+        <v>179.614533145319</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>179.308143814662</v>
+        <v>179.308141521081</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>184.213777836043</v>
+        <v>184.213777533422</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>184.213777836043</v>
+        <v>184.213777533422</v>
       </c>
       <c r="M27" s="13" t="n">
-        <v>184.339602236566</v>
+        <v>184.339602265215</v>
       </c>
       <c r="N27" s="14" t="n">
-        <v>184.339602236566</v>
+        <v>184.339602265215</v>
       </c>
       <c r="O27" s="15" t="n">
-        <v>-0.0338696912242375</v>
+        <v>-0.0338696925329939</v>
       </c>
       <c r="P27" s="16" t="n">
-        <v>0.0469542330300248</v>
+        <v>0.0469542337029312</v>
       </c>
       <c r="Q27" s="17" t="n">
-        <v>-0.0333025344063064</v>
+        <v>-0.0333025356714779</v>
       </c>
       <c r="R27" s="18" t="n">
-        <v>0.997169160888073</v>
+        <v>0.997169160945619</v>
       </c>
       <c r="S27" s="19" t="n">
-        <v>1.02630454469537</v>
+        <v>1.02630671937929</v>
       </c>
     </row>
     <row r="28">
@@ -3068,46 +3068,46 @@
         <v>173.725</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>1.64309694946071</v>
+        <v>1.64309686983671</v>
       </c>
       <c r="G28" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>174.878842986618</v>
+        <v>174.8788429595</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>179.522611013026</v>
+        <v>179.522154153826</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>178.755297345462</v>
+        <v>178.755296020959</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>172.081903050539</v>
+        <v>172.081903130163</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>172.081903050539</v>
+        <v>172.081903130163</v>
       </c>
       <c r="M28" s="13" t="n">
-        <v>176.152460002539</v>
+        <v>176.152460027636</v>
       </c>
       <c r="N28" s="14" t="n">
-        <v>176.152460002539</v>
+        <v>176.152460027636</v>
       </c>
       <c r="O28" s="15" t="n">
-        <v>-0.0454298507180131</v>
+        <v>-0.045429850730952</v>
       </c>
       <c r="P28" s="16" t="n">
-        <v>-0.00880051916935021</v>
+        <v>-0.00880051911329438</v>
       </c>
       <c r="Q28" s="17" t="n">
-        <v>-0.0444133660629271</v>
+        <v>-0.0444133660752913</v>
       </c>
       <c r="R28" s="18" t="n">
-        <v>1.00728285362695</v>
+        <v>1.00728285392666</v>
       </c>
       <c r="S28" s="19" t="n">
-        <v>0.981227150209826</v>
+        <v>0.981229647437822</v>
       </c>
     </row>
     <row r="29">
@@ -3127,46 +3127,46 @@
         <v>176.801</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>0.568743926965265</v>
+        <v>0.568743683202229</v>
       </c>
       <c r="G29" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H29" s="8" t="n">
-        <v>173.639053675129</v>
+        <v>173.63905390835</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>179.46902506825</v>
+        <v>179.468485559924</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>178.222281622578</v>
+        <v>178.222281828165</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>176.232256073035</v>
+        <v>176.232256316798</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>176.232256073035</v>
+        <v>176.232256316798</v>
       </c>
       <c r="M29" s="13" t="n">
-        <v>174.757082248033</v>
+        <v>174.757082411459</v>
       </c>
       <c r="N29" s="14" t="n">
-        <v>174.757082248033</v>
+        <v>174.757082411459</v>
       </c>
       <c r="O29" s="15" t="n">
-        <v>-0.00795296189614429</v>
+        <v>-0.00795296110345726</v>
       </c>
       <c r="P29" s="16" t="n">
-        <v>-0.0588077752200327</v>
+        <v>-0.0588077755576543</v>
       </c>
       <c r="Q29" s="17" t="n">
-        <v>-0.0079214207652073</v>
+        <v>-0.00792141997879947</v>
       </c>
       <c r="R29" s="18" t="n">
-        <v>1.00643880825909</v>
+        <v>1.00643880784849</v>
       </c>
       <c r="S29" s="19" t="n">
-        <v>0.973745091564266</v>
+        <v>0.973748019694009</v>
       </c>
     </row>
     <row r="30">
@@ -3186,46 +3186,46 @@
         <v>171.71</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>-2.77191379552169</v>
+        <v>-2.77191388207685</v>
       </c>
       <c r="G30" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>176.42274981333</v>
+        <v>176.422749813813</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>179.462392352547</v>
+        <v>179.461764550426</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>177.758487108345</v>
+        <v>177.758489532075</v>
       </c>
       <c r="K30" s="11" t="n">
-        <v>174.481913795522</v>
+        <v>174.481913882077</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>174.481913795522</v>
+        <v>174.481913882077</v>
       </c>
       <c r="M30" s="13" t="n">
-        <v>176.290245929246</v>
+        <v>176.290245945544</v>
       </c>
       <c r="N30" s="14" t="n">
-        <v>176.290245929246</v>
+        <v>176.290245945544</v>
       </c>
       <c r="O30" s="15" t="n">
-        <v>0.00873485314489074</v>
+        <v>0.00873485230218171</v>
       </c>
       <c r="P30" s="16" t="n">
-        <v>-0.0755142580269387</v>
+        <v>-0.0755142592950716</v>
       </c>
       <c r="Q30" s="17" t="n">
-        <v>0.00877311329241048</v>
+        <v>0.00877311244230827</v>
       </c>
       <c r="R30" s="18" t="n">
-        <v>0.999248941056499</v>
+        <v>0.999248941146148</v>
       </c>
       <c r="S30" s="19" t="n">
-        <v>0.982324171757002</v>
+        <v>0.982327608263374</v>
       </c>
     </row>
     <row r="31">
@@ -3245,46 +3245,46 @@
         <v>181.36</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>1.39509994709541</v>
+        <v>1.39510029877407</v>
       </c>
       <c r="G31" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>178.648449891523</v>
+        <v>178.6484497602</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>179.508926361268</v>
+        <v>179.508205668864</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>177.403354137347</v>
+        <v>177.403359594512</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>179.964900052905</v>
+        <v>179.964899701226</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>179.964900052905</v>
+        <v>179.964899701226</v>
       </c>
       <c r="M31" s="13" t="n">
-        <v>178.448653608532</v>
+        <v>178.448653489733</v>
       </c>
       <c r="N31" s="14" t="n">
-        <v>178.448653608532</v>
+        <v>178.448653489733</v>
       </c>
       <c r="O31" s="15" t="n">
-        <v>0.0121691436616237</v>
+        <v>0.0121691429034354</v>
       </c>
       <c r="P31" s="16" t="n">
-        <v>-0.0319570431776997</v>
+        <v>-0.0319570439726072</v>
       </c>
       <c r="Q31" s="17" t="n">
-        <v>0.0122434889571414</v>
+        <v>0.0122434881896702</v>
       </c>
       <c r="R31" s="18" t="n">
-        <v>0.998881623192856</v>
+        <v>0.998881623262136</v>
       </c>
       <c r="S31" s="19" t="n">
-        <v>0.994093481732478</v>
+        <v>0.994097472173021</v>
       </c>
     </row>
     <row r="32">
@@ -3304,46 +3304,46 @@
         <v>181.025</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>1.64209946720238</v>
+        <v>1.64209932559803</v>
       </c>
       <c r="G32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>179.878170471675</v>
+        <v>179.87817042818</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>179.611727790667</v>
+        <v>179.610911052106</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>177.179940177604</v>
+        <v>177.179949599046</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>179.382900532798</v>
+        <v>179.382900674402</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>179.382900532798</v>
+        <v>179.382900674402</v>
       </c>
       <c r="M32" s="13" t="n">
-        <v>179.024274869318</v>
+        <v>179.02427479668</v>
       </c>
       <c r="N32" s="14" t="n">
-        <v>179.024274869318</v>
+        <v>179.02427479668</v>
       </c>
       <c r="O32" s="15" t="n">
-        <v>0.00322050545616903</v>
+        <v>0.0032205057161624</v>
       </c>
       <c r="P32" s="16" t="n">
-        <v>0.0163030074444459</v>
+        <v>0.0163030068872916</v>
       </c>
       <c r="Q32" s="17" t="n">
-        <v>0.00322569685534613</v>
+        <v>0.00322569711617815</v>
       </c>
       <c r="R32" s="18" t="n">
-        <v>0.995252922574663</v>
+        <v>0.995252922411502</v>
       </c>
       <c r="S32" s="19" t="n">
-        <v>0.996729317575333</v>
+        <v>0.996733849564096</v>
       </c>
     </row>
     <row r="33">
@@ -3363,46 +3363,46 @@
         <v>176.741</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>-0.625398358771956</v>
+        <v>-0.62539813669167</v>
       </c>
       <c r="G33" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>175.971431730635</v>
+        <v>175.971431120661</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>179.774182320553</v>
+        <v>179.773268270789</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>177.124110426715</v>
+        <v>177.124124829781</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>177.366398358772</v>
+        <v>177.366398136692</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>177.366398358772</v>
+        <v>177.366398136692</v>
       </c>
       <c r="M33" s="13" t="n">
-        <v>176.47911725572</v>
+        <v>176.479117002497</v>
       </c>
       <c r="N33" s="14" t="n">
-        <v>176.47911725572</v>
+        <v>176.479117002497</v>
       </c>
       <c r="O33" s="15" t="n">
-        <v>-0.0143188568992399</v>
+        <v>-0.0143188579283586</v>
       </c>
       <c r="P33" s="16" t="n">
-        <v>0.0098538782264832</v>
+        <v>0.00985387583310682</v>
       </c>
       <c r="Q33" s="17" t="n">
-        <v>-0.0142168296196457</v>
+        <v>-0.0142168306341335</v>
       </c>
       <c r="R33" s="18" t="n">
-        <v>1.00288504514677</v>
+        <v>1.0028850471841</v>
       </c>
       <c r="S33" s="19" t="n">
-        <v>0.981671088571787</v>
+        <v>0.981676078429362</v>
       </c>
     </row>
     <row r="34">
@@ -3422,46 +3422,46 @@
         <v>168.454</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>-3.34677177253939</v>
+        <v>-3.34677106220425</v>
       </c>
       <c r="G34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>175.299384243324</v>
+        <v>175.299385088823</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>179.999532613701</v>
+        <v>179.998522389062</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>177.282744884055</v>
+        <v>177.2827653262</v>
       </c>
       <c r="K34" s="11" t="n">
-        <v>171.800771772539</v>
+        <v>171.800771062204</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>171.800771772539</v>
+        <v>171.800771062204</v>
       </c>
       <c r="M34" s="13" t="n">
-        <v>175.14386178683</v>
+        <v>175.14386237619</v>
       </c>
       <c r="N34" s="14" t="n">
-        <v>175.14386178683</v>
+        <v>175.14386237619</v>
       </c>
       <c r="O34" s="15" t="n">
-        <v>-0.00759484997733589</v>
+        <v>-0.00759484517747408</v>
       </c>
       <c r="P34" s="16" t="n">
-        <v>-0.00650282229951338</v>
+        <v>-0.00650281904824601</v>
       </c>
       <c r="Q34" s="17" t="n">
-        <v>-0.0075660819798592</v>
+        <v>-0.00756607721631353</v>
       </c>
       <c r="R34" s="18" t="n">
-        <v>0.999112818010371</v>
+        <v>0.999112816553495</v>
       </c>
       <c r="S34" s="19" t="n">
-        <v>0.973023980916155</v>
+        <v>0.97302944519523</v>
       </c>
     </row>
     <row r="35">
@@ -3481,46 +3481,46 @@
         <v>182.36</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>2.66710146287074</v>
+        <v>2.66709912283098</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>0.977495051945642</v>
+        <v>0.977495485240518</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>175.898475486138</v>
+        <v>175.898478539115</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>180.289516467908</v>
+        <v>180.288414177242</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>177.703934988658</v>
+        <v>177.703962494318</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>179.692898537129</v>
+        <v>179.692900877169</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>179.60750524347</v>
+        <v>179.607509243659</v>
       </c>
       <c r="M35" s="13" t="n">
-        <v>175.231034622967</v>
+        <v>175.23103664824</v>
       </c>
       <c r="N35" s="14" t="n">
-        <v>175.231034622967</v>
+        <v>175.23103664824</v>
       </c>
       <c r="O35" s="15" t="n">
-        <v>0.000497597509575846</v>
+        <v>0.000497605702300022</v>
       </c>
       <c r="P35" s="16" t="n">
-        <v>-0.0180310633927416</v>
+        <v>-0.0180310513896829</v>
       </c>
       <c r="Q35" s="17" t="n">
-        <v>0.000497721331753631</v>
+        <v>0.000497729528555535</v>
       </c>
       <c r="R35" s="18" t="n">
-        <v>0.996205533553795</v>
+        <v>0.996205527777053</v>
       </c>
       <c r="S35" s="19" t="n">
-        <v>0.971942451541043</v>
+        <v>0.971948405270068</v>
       </c>
     </row>
     <row r="36">
@@ -3540,46 +3540,46 @@
         <v>171.866</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>1.95764376761113</v>
+        <v>1.95764295656298</v>
       </c>
       <c r="G36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>170.249121641081</v>
+        <v>170.249122166951</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>180.640747455446</v>
+        <v>180.639560811067</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>178.408362314001</v>
+        <v>178.408397768832</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>169.908356232389</v>
+        <v>169.908357043437</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>169.908356232389</v>
+        <v>169.908357043437</v>
       </c>
       <c r="M36" s="13" t="n">
-        <v>170.368327642134</v>
+        <v>170.368327746394</v>
       </c>
       <c r="N36" s="14" t="n">
-        <v>170.368327642134</v>
+        <v>170.368327746394</v>
       </c>
       <c r="O36" s="15" t="n">
-        <v>-0.0281425745997373</v>
+        <v>-0.0281425855454956</v>
       </c>
       <c r="P36" s="16" t="n">
-        <v>-0.0483506900586685</v>
+        <v>-0.0483506890901666</v>
       </c>
       <c r="Q36" s="17" t="n">
-        <v>-0.0277502611982884</v>
+        <v>-0.027750271840299</v>
       </c>
       <c r="R36" s="18" t="n">
-        <v>1.00070018570377</v>
+        <v>1.00070018322518</v>
       </c>
       <c r="S36" s="19" t="n">
-        <v>0.94313342942823</v>
+        <v>0.943139625569528</v>
       </c>
     </row>
     <row r="37">
@@ -3599,46 +3599,46 @@
         <v>160.682</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>-1.36709286028644</v>
+        <v>-1.36708765504161</v>
       </c>
       <c r="G37" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>164.038912916932</v>
+        <v>164.038908374385</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>181.049412891573</v>
+        <v>181.048153900691</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>179.426226284836</v>
+        <v>179.426270318184</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>162.049092860286</v>
+        <v>162.049087655042</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>162.049092860286</v>
+        <v>162.049087655042</v>
       </c>
       <c r="M37" s="13" t="n">
-        <v>166.147291926218</v>
+        <v>166.147288945073</v>
       </c>
       <c r="N37" s="14" t="n">
-        <v>166.147291926218</v>
+        <v>166.147288945073</v>
       </c>
       <c r="O37" s="15" t="n">
-        <v>-0.0250880307760927</v>
+        <v>-0.0250880493308451</v>
       </c>
       <c r="P37" s="16" t="n">
-        <v>-0.0585441806949374</v>
+        <v>-0.0585441962364192</v>
       </c>
       <c r="Q37" s="17" t="n">
-        <v>-0.0247759414812231</v>
+        <v>-0.0247759595762639</v>
       </c>
       <c r="R37" s="18" t="n">
-        <v>1.0128529199066</v>
+        <v>1.012852929781</v>
       </c>
       <c r="S37" s="19" t="n">
-        <v>0.917690310466352</v>
+        <v>0.9176966755276</v>
       </c>
     </row>
     <row r="38">
@@ -3658,46 +3658,46 @@
         <v>166.629</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>-3.95362575191154</v>
+        <v>-3.9536234267727</v>
       </c>
       <c r="G38" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>169.97870645738</v>
+        <v>169.978706684266</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>181.50499234703</v>
+        <v>181.503678053913</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>180.745226295506</v>
+        <v>180.74527910719</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>170.582625751912</v>
+        <v>170.582623426773</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>170.582625751912</v>
+        <v>170.582623426773</v>
       </c>
       <c r="M38" s="13" t="n">
-        <v>171.553686270854</v>
+        <v>171.553686671424</v>
       </c>
       <c r="N38" s="14" t="n">
-        <v>171.553686270854</v>
+        <v>171.553686671424</v>
       </c>
       <c r="O38" s="15" t="n">
-        <v>0.032021561401278</v>
+        <v>0.0320215816790198</v>
       </c>
       <c r="P38" s="16" t="n">
-        <v>-0.0204984375664058</v>
+        <v>-0.0204984385753364</v>
       </c>
       <c r="Q38" s="17" t="n">
-        <v>0.0325397680693842</v>
+        <v>0.0325397890069592</v>
       </c>
       <c r="R38" s="18" t="n">
-        <v>1.00926574772981</v>
+        <v>1.00926574873924</v>
       </c>
       <c r="S38" s="19" t="n">
-        <v>0.945173375412451</v>
+        <v>0.945180221749925</v>
       </c>
     </row>
     <row r="39">
@@ -3717,46 +3717,46 @@
         <v>186.602</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>3.60159928069444</v>
+        <v>3.60158782289013</v>
       </c>
       <c r="G39" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>183.823530692097</v>
+        <v>183.823538769605</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>181.985090192542</v>
+        <v>181.983743462128</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>182.26617607323</v>
+        <v>182.26623718735</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>183.000400719306</v>
+        <v>183.00041217711</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>183.000400719306</v>
+        <v>183.00041217711</v>
       </c>
       <c r="M39" s="13" t="n">
-        <v>182.900524098828</v>
+        <v>182.900530094914</v>
       </c>
       <c r="N39" s="14" t="n">
-        <v>182.900524098828</v>
+        <v>182.900530094914</v>
       </c>
       <c r="O39" s="15" t="n">
-        <v>0.0640461637870245</v>
+        <v>0.0640461942353862</v>
       </c>
       <c r="P39" s="16" t="n">
-        <v>0.0437678718975936</v>
+        <v>0.0437678940521853</v>
       </c>
       <c r="Q39" s="17" t="n">
-        <v>0.0661416147599398</v>
+        <v>0.0661416472222058</v>
       </c>
       <c r="R39" s="18" t="n">
-        <v>0.99497884416759</v>
+        <v>0.994978833065294</v>
       </c>
       <c r="S39" s="19" t="n">
-        <v>1.00503026871772</v>
+        <v>1.00503773917024</v>
       </c>
     </row>
     <row r="40">
@@ -3776,46 +3776,46 @@
         <v>197.311</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>2.29233079521018</v>
+        <v>2.29232740133491</v>
       </c>
       <c r="G40" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>192.606489790614</v>
+        <v>192.606493031873</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>182.460484319708</v>
+        <v>182.459134657591</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>183.839076342512</v>
+        <v>183.839144331762</v>
       </c>
       <c r="K40" s="11" t="n">
-        <v>195.01866920479</v>
+        <v>195.018672598665</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>195.01866920479</v>
+        <v>195.018672598665</v>
       </c>
       <c r="M40" s="13" t="n">
-        <v>191.045293870863</v>
+        <v>191.0452951247</v>
       </c>
       <c r="N40" s="14" t="n">
-        <v>191.045293870863</v>
+        <v>191.0452951247</v>
       </c>
       <c r="O40" s="15" t="n">
-        <v>0.0435681197317889</v>
+        <v>0.0435680935115024</v>
       </c>
       <c r="P40" s="16" t="n">
-        <v>0.121366256949839</v>
+        <v>0.121366263623162</v>
       </c>
       <c r="Q40" s="17" t="n">
-        <v>0.0445311450700607</v>
+        <v>0.0445311176821552</v>
       </c>
       <c r="R40" s="18" t="n">
-        <v>0.991894375306626</v>
+        <v>0.991894365124466</v>
       </c>
       <c r="S40" s="19" t="n">
-        <v>1.0470502398542</v>
+        <v>1.04705799182497</v>
       </c>
     </row>
     <row r="41">
@@ -3835,46 +3835,46 @@
         <v>188.755</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>-2.38843635456752</v>
+        <v>-2.38842312435818</v>
       </c>
       <c r="G41" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H41" s="8" t="n">
-        <v>192.849068838281</v>
+        <v>192.849052595144</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>182.902587189209</v>
+        <v>182.901271590502</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>185.317598951085</v>
+        <v>185.317671188473</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>191.143436354568</v>
+        <v>191.143423124358</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>191.143436354568</v>
+        <v>191.143423124358</v>
       </c>
       <c r="M41" s="13" t="n">
-        <v>191.509458884028</v>
+        <v>191.509447355081</v>
       </c>
       <c r="N41" s="14" t="n">
-        <v>191.509458884028</v>
+        <v>191.509447355081</v>
       </c>
       <c r="O41" s="15" t="n">
-        <v>0.00242666043278221</v>
+        <v>0.00242659366934078</v>
       </c>
       <c r="P41" s="16" t="n">
-        <v>0.152648692998695</v>
+        <v>0.1526486442905</v>
       </c>
       <c r="Q41" s="17" t="n">
-        <v>0.00242960715629392</v>
+        <v>0.00242954023064579</v>
       </c>
       <c r="R41" s="18" t="n">
-        <v>0.993053583497589</v>
+        <v>0.993053607357482</v>
       </c>
       <c r="S41" s="19" t="n">
-        <v>1.04705713476822</v>
+        <v>1.04706460315843</v>
       </c>
     </row>
     <row r="42">
@@ -3894,46 +3894,46 @@
         <v>184.912</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>-3.82029362218765</v>
+        <v>-3.82027057294093</v>
       </c>
       <c r="G42" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>186.787834084949</v>
+        <v>186.787822641239</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>183.290660127278</v>
+        <v>183.289423922274</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>186.611313710992</v>
+        <v>186.611386046864</v>
       </c>
       <c r="K42" s="11" t="n">
-        <v>188.732293622188</v>
+        <v>188.732270572941</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>188.732293622188</v>
+        <v>188.732270572941</v>
       </c>
       <c r="M42" s="13" t="n">
-        <v>188.256477492326</v>
+        <v>188.256469858296</v>
       </c>
       <c r="N42" s="14" t="n">
-        <v>188.256477492326</v>
+        <v>188.256469858296</v>
       </c>
       <c r="O42" s="15" t="n">
-        <v>-0.0171319259733453</v>
+        <v>-0.0171319063241545</v>
       </c>
       <c r="P42" s="16" t="n">
-        <v>0.0973618905227218</v>
+        <v>0.0973618434610679</v>
       </c>
       <c r="Q42" s="17" t="n">
-        <v>-0.0169860089974566</v>
+        <v>-0.016985989682027</v>
       </c>
       <c r="R42" s="18" t="n">
-        <v>1.00786262881933</v>
+        <v>1.00786264969681</v>
       </c>
       <c r="S42" s="19" t="n">
-        <v>1.02709258268588</v>
+        <v>1.02709946831481</v>
       </c>
     </row>
     <row r="43">
@@ -3953,46 +3953,46 @@
         <v>173.805</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>4.37941988510076</v>
+        <v>4.37939033085114</v>
       </c>
       <c r="G43" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>184.417886370361</v>
+        <v>184.417915162946</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>183.609114990877</v>
+        <v>183.608012659031</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>187.658919621295</v>
+        <v>187.658985955996</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>169.425580114899</v>
+        <v>169.425609669149</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>184.417886370361</v>
+        <v>184.417915162946</v>
       </c>
       <c r="M43" s="13" t="n">
-        <v>187.216509413466</v>
+        <v>187.216529363728</v>
       </c>
       <c r="N43" s="14" t="n">
-        <v>187.216509413466</v>
+        <v>187.216529363728</v>
       </c>
       <c r="O43" s="15" t="n">
-        <v>-0.00553952361168792</v>
+        <v>-0.00553937649796226</v>
       </c>
       <c r="P43" s="16" t="n">
-        <v>0.0235974464037412</v>
+        <v>0.0235975219239326</v>
       </c>
       <c r="Q43" s="17" t="n">
-        <v>-0.0055242087428411</v>
+        <v>-0.0055240624417916</v>
       </c>
       <c r="R43" s="18" t="n">
-        <v>1.01517544256789</v>
+        <v>1.01517539225139</v>
       </c>
       <c r="S43" s="19" t="n">
-        <v>1.01964714236964</v>
+        <v>1.01965337270655</v>
       </c>
     </row>
     <row r="44">
@@ -4012,46 +4012,46 @@
         <v>193.59</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>2.29202870904416</v>
+        <v>2.29198344392087</v>
       </c>
       <c r="G44" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>191.699355010717</v>
+        <v>191.699378732533</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>183.845764657902</v>
+        <v>183.84486058605</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>188.409720580612</v>
+        <v>188.40977238756</v>
       </c>
       <c r="K44" s="11" t="n">
-        <v>191.297971290956</v>
+        <v>191.298016556079</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>191.297971290956</v>
+        <v>191.298016556079</v>
       </c>
       <c r="M44" s="13" t="n">
-        <v>191.983625493482</v>
+        <v>191.983644445267</v>
       </c>
       <c r="N44" s="14" t="n">
-        <v>191.983625493482</v>
+        <v>191.983644445267</v>
       </c>
       <c r="O44" s="15" t="n">
-        <v>0.0251443330366729</v>
+        <v>0.0251443251897918</v>
       </c>
       <c r="P44" s="16" t="n">
-        <v>0.00491156627628575</v>
+        <v>0.00491165888149725</v>
       </c>
       <c r="Q44" s="17" t="n">
-        <v>0.0254631180495299</v>
+        <v>0.0254631100028428</v>
       </c>
       <c r="R44" s="18" t="n">
-        <v>1.00148289743985</v>
+        <v>1.00148287237347</v>
       </c>
       <c r="S44" s="19" t="n">
-        <v>1.04426460871004</v>
+        <v>1.04426984705078</v>
       </c>
     </row>
     <row r="45">
@@ -4071,46 +4071,46 @@
         <v>209.016</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>-3.95827330422656</v>
+        <v>-3.95822933134509</v>
       </c>
       <c r="G45" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H45" s="8" t="n">
-        <v>200.920673021657</v>
+        <v>200.920629505964</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>183.988927488361</v>
+        <v>183.988296677677</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>188.796815321305</v>
+        <v>188.796841459281</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>212.974273304227</v>
+        <v>212.974229331345</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>200.920673021657</v>
+        <v>200.920629505964</v>
       </c>
       <c r="M45" s="13" t="n">
-        <v>198.093038701128</v>
+        <v>198.09301090049</v>
       </c>
       <c r="N45" s="14" t="n">
-        <v>198.093038701128</v>
+        <v>198.09301090049</v>
       </c>
       <c r="O45" s="15" t="n">
-        <v>0.0313267282568075</v>
+        <v>0.0313264891998554</v>
       </c>
       <c r="P45" s="16" t="n">
-        <v>0.0343773088570356</v>
+        <v>0.034377225961093</v>
       </c>
       <c r="Q45" s="17" t="n">
-        <v>0.0318225744093634</v>
+        <v>0.0318223277450331</v>
       </c>
       <c r="R45" s="18" t="n">
-        <v>0.985926613334487</v>
+        <v>0.985926688501691</v>
       </c>
       <c r="S45" s="19" t="n">
-        <v>1.07665739131861</v>
+        <v>1.07666093157829</v>
       </c>
     </row>
     <row r="46">
@@ -4130,46 +4130,46 @@
         <v>196.596</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>-2.63683747024258</v>
+        <v>-2.63676803395376</v>
       </c>
       <c r="G46" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>200.233615722232</v>
+        <v>200.233548318875</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>184.031579471408</v>
+        <v>184.031308130736</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>188.76774382929</v>
+        <v>188.767730509729</v>
       </c>
       <c r="K46" s="11" t="n">
-        <v>199.232837470243</v>
+        <v>199.232768033954</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>199.232837470243</v>
+        <v>199.232768033954</v>
       </c>
       <c r="M46" s="13" t="n">
-        <v>198.223551067469</v>
+        <v>198.223509668947</v>
       </c>
       <c r="N46" s="14" t="n">
-        <v>198.223551067469</v>
+        <v>198.223509668947</v>
       </c>
       <c r="O46" s="15" t="n">
-        <v>0.000658626837370689</v>
+        <v>0.000658558331032815</v>
       </c>
       <c r="P46" s="16" t="n">
-        <v>0.052944120212538</v>
+        <v>0.0529439430058001</v>
       </c>
       <c r="Q46" s="17" t="n">
-        <v>0.00065884377965153</v>
+        <v>0.00065877522818103</v>
       </c>
       <c r="R46" s="18" t="n">
-        <v>0.989961402597096</v>
+        <v>0.989961529090386</v>
       </c>
       <c r="S46" s="19" t="n">
-        <v>1.07711704500295</v>
+        <v>1.07711840817938</v>
       </c>
     </row>
     <row r="47">
@@ -4189,46 +4189,46 @@
         <v>198.82</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>5.3121436922676</v>
+        <v>5.31212689808251</v>
       </c>
       <c r="G47" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H47" s="8" t="n">
-        <v>192.677258651057</v>
+        <v>192.677307692162</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>183.977278937156</v>
+        <v>183.977464850071</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>188.330665378982</v>
+        <v>188.330595817705</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>193.507856307732</v>
+        <v>193.507873101917</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>193.507856307732</v>
+        <v>193.507873101917</v>
       </c>
       <c r="M47" s="13" t="n">
-        <v>193.379946396435</v>
+        <v>193.379981236436</v>
       </c>
       <c r="N47" s="14" t="n">
-        <v>193.379946396435</v>
+        <v>193.379981236436</v>
       </c>
       <c r="O47" s="15" t="n">
-        <v>-0.0247385517345196</v>
+        <v>-0.0247381627234051</v>
       </c>
       <c r="P47" s="16" t="n">
-        <v>0.0329214394728203</v>
+        <v>0.0329215154968152</v>
       </c>
       <c r="Q47" s="17" t="n">
-        <v>-0.0244350615502066</v>
+        <v>-0.0244346820445288</v>
       </c>
       <c r="R47" s="18" t="n">
-        <v>1.00364696773401</v>
+        <v>1.00364689310169</v>
       </c>
       <c r="S47" s="19" t="n">
-        <v>1.05110776457614</v>
+        <v>1.05110689178171</v>
       </c>
     </row>
     <row r="48">
@@ -4248,46 +4248,46 @@
         <v>188.675</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>1.40376449996935</v>
+        <v>1.40358929204492</v>
       </c>
       <c r="G48" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>190.054405699985</v>
+        <v>190.054511558615</v>
       </c>
       <c r="I48" s="9" t="n">
-        <v>183.839085001965</v>
+        <v>183.839837652963</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>187.546064713003</v>
+        <v>187.545918849632</v>
       </c>
       <c r="K48" s="11" t="n">
-        <v>187.271235500031</v>
+        <v>187.271410707955</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>187.271235500031</v>
+        <v>187.271410707955</v>
       </c>
       <c r="M48" s="13" t="n">
-        <v>190.235079279541</v>
+        <v>190.235156596498</v>
       </c>
       <c r="N48" s="14" t="n">
-        <v>190.235079279541</v>
+        <v>190.235156596498</v>
       </c>
       <c r="O48" s="15" t="n">
-        <v>-0.0163963211105793</v>
+        <v>-0.0163960948456151</v>
       </c>
       <c r="P48" s="16" t="n">
-        <v>-0.00910778827854375</v>
+        <v>-0.00910748336829137</v>
       </c>
       <c r="Q48" s="17" t="n">
-        <v>-0.0162626330987129</v>
+        <v>-0.0162624105133876</v>
       </c>
       <c r="R48" s="18" t="n">
-        <v>1.00095064136446</v>
+        <v>1.00095049065871</v>
       </c>
       <c r="S48" s="19" t="n">
-        <v>1.03479126474932</v>
+        <v>1.03478744882058</v>
       </c>
     </row>
     <row r="49">
@@ -4307,46 +4307,46 @@
         <v>187.299</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>-5.59098981036842</v>
+        <v>-5.59093186816369</v>
       </c>
       <c r="G49" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H49" s="8" t="n">
-        <v>189.773411039277</v>
+        <v>189.773373891632</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>183.636013393053</v>
+        <v>183.637453861852</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>186.500312528618</v>
+        <v>186.500067458354</v>
       </c>
       <c r="K49" s="11" t="n">
-        <v>192.889989810368</v>
+        <v>192.889931868164</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>192.889989810368</v>
+        <v>192.889931868164</v>
       </c>
       <c r="M49" s="13" t="n">
-        <v>189.469555409415</v>
+        <v>189.469519757295</v>
       </c>
       <c r="N49" s="14" t="n">
-        <v>189.469555409415</v>
+        <v>189.469519757295</v>
       </c>
       <c r="O49" s="15" t="n">
-        <v>-0.00403221260629185</v>
+        <v>-0.00403280720278912</v>
       </c>
       <c r="P49" s="16" t="n">
-        <v>-0.0435324903300829</v>
+        <v>-0.0435325360748208</v>
       </c>
       <c r="Q49" s="17" t="n">
-        <v>-0.0040240941524835</v>
+        <v>-0.00402468635609243</v>
       </c>
       <c r="R49" s="18" t="n">
-        <v>0.998398850354228</v>
+        <v>0.998398857921392</v>
       </c>
       <c r="S49" s="19" t="n">
-        <v>1.03176687354825</v>
+        <v>1.03175858613151</v>
       </c>
     </row>
     <row r="50">
@@ -4366,46 +4366,46 @@
         <v>183.9625</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>-0.864506516890492</v>
+        <v>-0.864304584896614</v>
       </c>
       <c r="G50" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H50" s="8" t="n">
-        <v>185.628548718244</v>
+        <v>185.628363389111</v>
       </c>
       <c r="I50" s="9" t="n">
-        <v>183.389224931701</v>
+        <v>183.391485532339</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>185.278405377027</v>
+        <v>185.278036956007</v>
       </c>
       <c r="K50" s="11" t="n">
-        <v>184.82700651689</v>
+        <v>184.826804584897</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>184.82700651689</v>
+        <v>184.826804584897</v>
       </c>
       <c r="M50" s="13" t="n">
-        <v>185.633502608475</v>
+        <v>185.633372347092</v>
       </c>
       <c r="N50" s="14" t="n">
-        <v>185.633502608475</v>
+        <v>185.633372347092</v>
       </c>
       <c r="O50" s="15" t="n">
-        <v>-0.0204540403394639</v>
+        <v>-0.0204545538843113</v>
       </c>
       <c r="P50" s="16" t="n">
-        <v>-0.0635143926702655</v>
+        <v>-0.0635148542313799</v>
       </c>
       <c r="Q50" s="17" t="n">
-        <v>-0.0202462754116375</v>
+        <v>-0.0202467785589853</v>
       </c>
       <c r="R50" s="18" t="n">
-        <v>1.00002668711394</v>
+        <v>1.00002698379649</v>
       </c>
       <c r="S50" s="19" t="n">
-        <v>1.01223778374989</v>
+        <v>1.01222459596881</v>
       </c>
     </row>
     <row r="51">
@@ -4425,46 +4425,46 @@
         <v>186.559</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>6.56899241024942</v>
+        <v>6.56905164959072</v>
       </c>
       <c r="G51" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H51" s="8" t="n">
-        <v>182.331484046181</v>
+        <v>182.331471154947</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>183.125664174448</v>
+        <v>183.128887518775</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>183.997288195838</v>
+        <v>183.996771976776</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>179.990007589751</v>
+        <v>179.989948350409</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>179.990007589751</v>
+        <v>179.989948350409</v>
       </c>
       <c r="M51" s="13" t="n">
-        <v>182.294373821645</v>
+        <v>182.294379104654</v>
       </c>
       <c r="N51" s="14" t="n">
-        <v>182.294373821645</v>
+        <v>182.294379104654</v>
       </c>
       <c r="O51" s="15" t="n">
-        <v>-0.018151494793879</v>
+        <v>-0.0181507641003008</v>
       </c>
       <c r="P51" s="16" t="n">
-        <v>-0.057325347231527</v>
+        <v>-0.057325489747712</v>
       </c>
       <c r="Q51" s="17" t="n">
-        <v>-0.0179877486547934</v>
+        <v>-0.0179870311044854</v>
       </c>
       <c r="R51" s="18" t="n">
-        <v>0.999796468367872</v>
+        <v>0.999796568030422</v>
       </c>
       <c r="S51" s="19" t="n">
-        <v>0.995460546960738</v>
+        <v>0.995443054203909</v>
       </c>
     </row>
     <row r="52">
@@ -4484,46 +4484,46 @@
         <v>183.76</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>-0.610473590187663</v>
+        <v>-0.610815132900497</v>
       </c>
       <c r="G52" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>180.478279666829</v>
+        <v>180.478637453544</v>
       </c>
       <c r="I52" s="9" t="n">
-        <v>182.873174291326</v>
+        <v>182.877511749923</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>182.77164892836</v>
+        <v>182.770960992989</v>
       </c>
       <c r="K52" s="11" t="n">
-        <v>184.370473590188</v>
+        <v>184.3708151329</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>184.370473590188</v>
+        <v>184.3708151329</v>
       </c>
       <c r="M52" s="13" t="n">
-        <v>180.200540122641</v>
+        <v>180.200781235173</v>
       </c>
       <c r="N52" s="14" t="n">
-        <v>180.200540122641</v>
+        <v>180.200781235173</v>
       </c>
       <c r="O52" s="15" t="n">
-        <v>-0.0115524764915431</v>
+        <v>-0.0115511674497275</v>
       </c>
       <c r="P52" s="16" t="n">
-        <v>-0.0527481009018034</v>
+        <v>-0.0527472184471602</v>
       </c>
       <c r="Q52" s="17" t="n">
-        <v>-0.0114860028595981</v>
+        <v>-0.0114847088525936</v>
       </c>
       <c r="R52" s="18" t="n">
-        <v>0.998461091580101</v>
+        <v>0.998460448160005</v>
       </c>
       <c r="S52" s="19" t="n">
-        <v>0.985385313187449</v>
+        <v>0.98536326041875</v>
       </c>
     </row>
     <row r="53">
@@ -4543,46 +4543,46 @@
         <v>165.582</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>-6.48920572043718</v>
+        <v>-6.4895463244803</v>
       </c>
       <c r="G53" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H53" s="8" t="n">
-        <v>174.189251096484</v>
+        <v>174.189303299503</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>182.657638666998</v>
+        <v>182.663248317563</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>181.696139114871</v>
+        <v>181.695258358844</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>172.071205720437</v>
+        <v>172.07154632448</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>172.071205720437</v>
+        <v>172.07154632448</v>
       </c>
       <c r="M53" s="13" t="n">
-        <v>174.678966149646</v>
+        <v>174.678986064016</v>
       </c>
       <c r="N53" s="14" t="n">
-        <v>174.678966149646</v>
+        <v>174.678986064016</v>
       </c>
       <c r="O53" s="15" t="n">
-        <v>-0.0311205324596286</v>
+        <v>-0.0311217564765564</v>
       </c>
       <c r="P53" s="16" t="n">
-        <v>-0.07806314438121</v>
+        <v>-0.0780628657961722</v>
       </c>
       <c r="Q53" s="17" t="n">
-        <v>-0.0306412731573233</v>
+        <v>-0.030642459668088</v>
       </c>
       <c r="R53" s="18" t="n">
-        <v>1.00281139651315</v>
+        <v>1.00281121030532</v>
       </c>
       <c r="S53" s="19" t="n">
-        <v>0.956318976991165</v>
+        <v>0.956289717132007</v>
       </c>
     </row>
     <row r="54">
@@ -4602,46 +4602,46 @@
         <v>171.329</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>1.12602043247919</v>
+        <v>1.12696352579741</v>
       </c>
       <c r="G54" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H54" s="8" t="n">
-        <v>171.401577507189</v>
+        <v>171.40093811153</v>
       </c>
       <c r="I54" s="9" t="n">
-        <v>182.505876498194</v>
+        <v>182.51292062809</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v>180.873404418956</v>
+        <v>180.872317699238</v>
       </c>
       <c r="K54" s="11" t="n">
-        <v>170.202979567521</v>
+        <v>170.202036474203</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>170.202979567521</v>
+        <v>170.202036474203</v>
       </c>
       <c r="M54" s="13" t="n">
-        <v>171.920545822755</v>
+        <v>171.920038302085</v>
       </c>
       <c r="N54" s="14" t="n">
-        <v>171.920545822755</v>
+        <v>171.920038302085</v>
       </c>
       <c r="O54" s="15" t="n">
-        <v>-0.0159173828670593</v>
+        <v>-0.0159204489422062</v>
       </c>
       <c r="P54" s="16" t="n">
-        <v>-0.0738711309813653</v>
+        <v>-0.0738732150993082</v>
       </c>
       <c r="Q54" s="17" t="n">
-        <v>-0.0157913708083657</v>
+        <v>-0.0157943884613568</v>
       </c>
       <c r="R54" s="18" t="n">
-        <v>1.003027791944</v>
+        <v>1.0030285726337</v>
       </c>
       <c r="S54" s="19" t="n">
-        <v>0.942000055677417</v>
+        <v>0.941960918221289</v>
       </c>
     </row>
     <row r="55">
@@ -4661,46 +4661,46 @@
         <v>196.137</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>7.30863891930882</v>
+        <v>7.3086028944209</v>
       </c>
       <c r="G55" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H55" s="8" t="n">
-        <v>175.20501843554</v>
+        <v>175.204533935454</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>182.438090461048</v>
+        <v>182.446732274154</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>180.357965837232</v>
+        <v>180.356674078896</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>188.828361080691</v>
+        <v>188.828397105579</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>175.20501843554</v>
+        <v>175.204533935454</v>
       </c>
       <c r="M55" s="13" t="n">
-        <v>173.777241359934</v>
+        <v>173.776936336613</v>
       </c>
       <c r="N55" s="14" t="n">
-        <v>173.777241359934</v>
+        <v>173.776936336613</v>
       </c>
       <c r="O55" s="15" t="n">
-        <v>0.0107418297668182</v>
+        <v>0.0107430265801833</v>
       </c>
       <c r="P55" s="16" t="n">
-        <v>-0.0467218613671752</v>
+        <v>-0.0467235622396832</v>
       </c>
       <c r="Q55" s="17" t="n">
-        <v>0.0107997303538891</v>
+        <v>0.0108009400932398</v>
       </c>
       <c r="R55" s="18" t="n">
-        <v>0.991850820893402</v>
+        <v>0.991851822742403</v>
       </c>
       <c r="S55" s="19" t="n">
-        <v>0.952527188378111</v>
+        <v>0.952480398911653</v>
       </c>
     </row>
     <row r="56">
@@ -4720,46 +4720,46 @@
         <v>171.817</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>-2.6789490011348</v>
+        <v>-2.67964100134224</v>
       </c>
       <c r="G56" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>173.229885304634</v>
+        <v>173.230854830421</v>
       </c>
       <c r="I56" s="9" t="n">
-        <v>182.466793921115</v>
+        <v>182.477192545807</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>180.150992242055</v>
+        <v>180.149511156418</v>
       </c>
       <c r="K56" s="11" t="n">
-        <v>174.495949001135</v>
+        <v>174.496641001342</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>174.495949001135</v>
+        <v>174.496641001342</v>
       </c>
       <c r="M56" s="13" t="n">
-        <v>173.358473184092</v>
+        <v>173.359246702698</v>
       </c>
       <c r="N56" s="14" t="n">
-        <v>173.358473184092</v>
+        <v>173.359246702698</v>
       </c>
       <c r="O56" s="15" t="n">
-        <v>-0.0024127069698662</v>
+        <v>-0.00240648976338379</v>
       </c>
       <c r="P56" s="16" t="n">
-        <v>-0.0379691810795482</v>
+        <v>-0.0379661757600606</v>
       </c>
       <c r="Q56" s="17" t="n">
-        <v>-0.00240979873178393</v>
+        <v>-0.00240359648823751</v>
       </c>
       <c r="R56" s="18" t="n">
-        <v>1.00074229616461</v>
+        <v>1.00074116053057</v>
       </c>
       <c r="S56" s="19" t="n">
-        <v>0.950082310642444</v>
+        <v>0.950032408347032</v>
       </c>
     </row>
     <row r="57">
@@ -4779,46 +4779,46 @@
         <v>159.256</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>-6.93631740759734</v>
+        <v>-6.93702881674668</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>0.56645375296775</v>
+        <v>0.566235874852059</v>
       </c>
       <c r="H57" s="8" t="n">
-        <v>173.215002788458</v>
+        <v>173.215606017817</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>182.599979573933</v>
+        <v>182.612284359142</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>180.227887768774</v>
+        <v>180.226251889686</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>166.192317407597</v>
+        <v>166.193028816747</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>169.236976298558</v>
+        <v>169.239170872653</v>
       </c>
       <c r="M57" s="13" t="n">
-        <v>174.694452251535</v>
+        <v>174.695239615814</v>
       </c>
       <c r="N57" s="14" t="n">
-        <v>174.694452251535</v>
+        <v>174.695239615814</v>
       </c>
       <c r="O57" s="15" t="n">
-        <v>0.00767691078641316</v>
+        <v>0.00767695591979704</v>
       </c>
       <c r="P57" s="16" t="n">
-        <v>0.0000886546458969129</v>
+        <v>0.0000930481230982938</v>
       </c>
       <c r="Q57" s="17" t="n">
-        <v>0.007706453817373</v>
+        <v>0.00770649929857625</v>
       </c>
       <c r="R57" s="18" t="n">
-        <v>1.00854111618082</v>
+        <v>1.00854214947494</v>
       </c>
       <c r="S57" s="19" t="n">
-        <v>0.956705760094587</v>
+        <v>0.956645606996748</v>
       </c>
     </row>
     <row r="58">
@@ -4838,46 +4838,46 @@
         <v>189.021</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>3.2130925921089</v>
+        <v>3.21502428339242</v>
       </c>
       <c r="G58" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H58" s="8" t="n">
-        <v>184.790503485975</v>
+        <v>184.789943601416</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>182.840658336964</v>
+        <v>182.855002785534</v>
       </c>
       <c r="J58" s="10" t="n">
-        <v>180.535781336534</v>
+        <v>180.534054885808</v>
       </c>
       <c r="K58" s="11" t="n">
-        <v>185.807907407891</v>
+        <v>185.805975716608</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>185.807907407891</v>
+        <v>185.805975716608</v>
       </c>
       <c r="M58" s="13" t="n">
-        <v>184.180061117979</v>
+        <v>184.179755706739</v>
       </c>
       <c r="N58" s="14" t="n">
-        <v>184.180061117979</v>
+        <v>184.179755706739</v>
       </c>
       <c r="O58" s="15" t="n">
-        <v>0.0528754113540981</v>
+        <v>0.0528692460481317</v>
       </c>
       <c r="P58" s="16" t="n">
-        <v>0.0713091924909492</v>
+        <v>0.0713105786023143</v>
       </c>
       <c r="Q58" s="17" t="n">
-        <v>0.0542982833409347</v>
+        <v>0.0542917832894754</v>
       </c>
       <c r="R58" s="18" t="n">
-        <v>0.996696570676086</v>
+        <v>0.996697937762276</v>
       </c>
       <c r="S58" s="19" t="n">
-        <v>1.00732551935219</v>
+        <v>1.00724482732779</v>
       </c>
     </row>
     <row r="59">
@@ -4897,46 +4897,46 @@
         <v>203.006</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>7.1385466424255</v>
+        <v>7.13809947891357</v>
       </c>
       <c r="G59" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H59" s="8" t="n">
-        <v>192.894662538633</v>
+        <v>192.894416963757</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>183.183489250625</v>
+        <v>183.199984700432</v>
       </c>
       <c r="J59" s="10" t="n">
-        <v>180.966847307127</v>
+        <v>180.965143346806</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>195.867453357575</v>
+        <v>195.867900521086</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>195.867453357575</v>
+        <v>195.867900521086</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>190.786516561236</v>
+        <v>190.786485298026</v>
       </c>
       <c r="N59" s="14" t="n">
-        <v>190.786516561236</v>
+        <v>190.786485298026</v>
       </c>
       <c r="O59" s="15" t="n">
-        <v>0.0352412164675701</v>
+        <v>0.0352427108250264</v>
       </c>
       <c r="P59" s="16" t="n">
-        <v>0.0978797630126458</v>
+        <v>0.0978815101704007</v>
       </c>
       <c r="Q59" s="17" t="n">
-        <v>0.0358695474589139</v>
+        <v>0.0358710954194525</v>
       </c>
       <c r="R59" s="18" t="n">
-        <v>0.989070998908665</v>
+        <v>0.989072096025845</v>
       </c>
       <c r="S59" s="19" t="n">
-        <v>1.04150498138077</v>
+        <v>1.04141103292121</v>
       </c>
     </row>
     <row r="60">
@@ -4956,46 +4956,46 @@
         <v>181.525</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>-4.07825212190228</v>
+        <v>-4.0791644333256</v>
       </c>
       <c r="G60" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H60" s="8" t="n">
-        <v>187.262708483368</v>
+        <v>187.263983424339</v>
       </c>
       <c r="I60" s="9" t="n">
-        <v>183.624985886</v>
+        <v>183.643711337364</v>
       </c>
       <c r="J60" s="10" t="n">
-        <v>181.439620672705</v>
+        <v>181.438100078856</v>
       </c>
       <c r="K60" s="11" t="n">
-        <v>185.603252121902</v>
+        <v>185.604164433326</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>185.603252121902</v>
+        <v>185.604164433326</v>
       </c>
       <c r="M60" s="13" t="n">
-        <v>187.148816344954</v>
+        <v>187.1496210125</v>
       </c>
       <c r="N60" s="14" t="n">
-        <v>187.148816344954</v>
+        <v>187.1496210125</v>
       </c>
       <c r="O60" s="15" t="n">
-        <v>-0.0192509789014974</v>
+        <v>-0.0192465154325166</v>
       </c>
       <c r="P60" s="16" t="n">
-        <v>0.0795481346113236</v>
+        <v>0.079547959350859</v>
       </c>
       <c r="Q60" s="17" t="n">
-        <v>-0.0190668621758421</v>
+        <v>-0.0190624838014378</v>
       </c>
       <c r="R60" s="18" t="n">
-        <v>0.999391805558422</v>
+        <v>0.999389298413138</v>
       </c>
       <c r="S60" s="19" t="n">
-        <v>1.01919036476409</v>
+        <v>1.01909082347336</v>
       </c>
     </row>
     <row r="61">
@@ -5015,46 +5015,46 @@
         <v>174.433</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>-7.08830777843496</v>
+        <v>-7.0892546622608</v>
       </c>
       <c r="G61" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H61" s="8" t="n">
-        <v>183.059688116693</v>
+        <v>183.059515450448</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>184.169589291743</v>
+        <v>184.190581377248</v>
       </c>
       <c r="J61" s="10" t="n">
-        <v>181.94713945567</v>
+        <v>181.946021674006</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>181.521307778435</v>
+        <v>181.522254662261</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>181.521307778435</v>
+        <v>181.522254662261</v>
       </c>
       <c r="M61" s="13" t="n">
-        <v>184.043319218742</v>
+        <v>184.043294574265</v>
       </c>
       <c r="N61" s="14" t="n">
-        <v>184.043319218742</v>
+        <v>184.043294574265</v>
       </c>
       <c r="O61" s="15" t="n">
-        <v>-0.0167329492613317</v>
+        <v>-0.0167373827712828</v>
       </c>
       <c r="P61" s="16" t="n">
-        <v>0.0535155343899876</v>
+        <v>0.053510645046821</v>
       </c>
       <c r="Q61" s="17" t="n">
-        <v>-0.0165937310577855</v>
+        <v>-0.0165980909895999</v>
       </c>
       <c r="R61" s="18" t="n">
-        <v>1.00537328077071</v>
+        <v>1.00537409443806</v>
       </c>
       <c r="S61" s="19" t="n">
-        <v>0.999314381524735</v>
+        <v>0.999200356490099</v>
       </c>
     </row>
     <row r="62">
@@ -5074,46 +5074,46 @@
         <v>192.638</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>5.11059080380243</v>
+        <v>5.11349546078708</v>
       </c>
       <c r="G62" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H62" s="8" t="n">
-        <v>185.912126001736</v>
+        <v>185.91093839713</v>
       </c>
       <c r="I62" s="9" t="n">
-        <v>184.822976932902</v>
+        <v>184.846218784185</v>
       </c>
       <c r="J62" s="10" t="n">
-        <v>182.503259835669</v>
+        <v>182.502835046075</v>
       </c>
       <c r="K62" s="11" t="n">
-        <v>187.527409196198</v>
+        <v>187.524504539213</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>187.527409196198</v>
+        <v>187.524504539213</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>185.788049083025</v>
+        <v>185.787120814742</v>
       </c>
       <c r="N62" s="14" t="n">
-        <v>185.788049083025</v>
+        <v>185.787120814742</v>
       </c>
       <c r="O62" s="15" t="n">
-        <v>0.00943534247021432</v>
+        <v>0.00943047998041651</v>
       </c>
       <c r="P62" s="16" t="n">
-        <v>0.00873052140001174</v>
+        <v>0.00872715408832692</v>
       </c>
       <c r="Q62" s="17" t="n">
-        <v>0.00947999564281088</v>
+        <v>0.00947508706856492</v>
       </c>
       <c r="R62" s="18" t="n">
-        <v>0.99933260448697</v>
+        <v>0.999333995172873</v>
       </c>
       <c r="S62" s="19" t="n">
-        <v>1.00522160267158</v>
+        <v>1.00509018813988</v>
       </c>
     </row>
     <row r="63">
@@ -5133,46 +5133,46 @@
         <v>192.737</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>6.16092983873176</v>
+        <v>6.15978048171963</v>
       </c>
       <c r="G63" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H63" s="8" t="n">
-        <v>185.500079404621</v>
+        <v>185.500203317841</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>185.589171098582</v>
+        <v>185.614579818081</v>
       </c>
       <c r="J63" s="10" t="n">
-        <v>183.119708833965</v>
+        <v>183.120348273825</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>186.576070161268</v>
+        <v>186.57721951828</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>186.576070161268</v>
+        <v>186.57721951828</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>186.074993180521</v>
+        <v>186.07522068871</v>
       </c>
       <c r="N63" s="14" t="n">
-        <v>186.074993180521</v>
+        <v>186.07522068871</v>
       </c>
       <c r="O63" s="15" t="n">
-        <v>0.00154327869045984</v>
+        <v>0.00154949775471204</v>
       </c>
       <c r="P63" s="16" t="n">
-        <v>-0.0246952639297378</v>
+        <v>-0.0246939116361264</v>
       </c>
       <c r="Q63" s="17" t="n">
-        <v>0.0015444701578613</v>
+        <v>0.00155069884664094</v>
       </c>
       <c r="R63" s="18" t="n">
-        <v>1.00309926431161</v>
+        <v>1.00309982070415</v>
       </c>
       <c r="S63" s="19" t="n">
-        <v>1.00261772860487</v>
+        <v>1.00248170629204</v>
       </c>
     </row>
     <row r="64">
@@ -5192,46 +5192,46 @@
         <v>178.853</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>-4.76742320334839</v>
+        <v>-4.76893917906584</v>
       </c>
       <c r="G64" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H64" s="8" t="n">
-        <v>188.85700792939</v>
+        <v>188.857359549812</v>
       </c>
       <c r="I64" s="9" t="n">
-        <v>186.47388434805</v>
+        <v>186.501294667438</v>
       </c>
       <c r="J64" s="10" t="n">
-        <v>183.833334218623</v>
+        <v>183.835477783482</v>
       </c>
       <c r="K64" s="11" t="n">
-        <v>183.620423203348</v>
+        <v>183.621939179066</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>183.620423203348</v>
+        <v>183.621939179066</v>
       </c>
       <c r="M64" s="13" t="n">
-        <v>188.021121693136</v>
+        <v>188.022308974463</v>
       </c>
       <c r="N64" s="14" t="n">
-        <v>188.021121693136</v>
+        <v>188.022308974463</v>
       </c>
       <c r="O64" s="15" t="n">
-        <v>0.0104045243539124</v>
+        <v>0.0104096162821499</v>
       </c>
       <c r="P64" s="16" t="n">
-        <v>0.00466102519491329</v>
+        <v>0.00466304958162533</v>
       </c>
       <c r="Q64" s="17" t="n">
-        <v>0.0104588396288525</v>
+        <v>0.0104639848258503</v>
       </c>
       <c r="R64" s="18" t="n">
-        <v>0.995573972893995</v>
+        <v>0.995578405960248</v>
       </c>
       <c r="S64" s="19" t="n">
-        <v>1.00829734067317</v>
+        <v>1.00815551607691</v>
       </c>
     </row>
     <row r="65">
@@ -5251,46 +5251,46 @@
         <v>191.494</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>-6.77357020457712</v>
+        <v>-6.77413802144117</v>
       </c>
       <c r="G65" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H65" s="8" t="n">
-        <v>191.772603489531</v>
+        <v>191.777546167951</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>187.48344605249</v>
+        <v>187.512595170571</v>
       </c>
       <c r="J65" s="10" t="n">
-        <v>184.698265564344</v>
+        <v>184.702424357496</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>198.267570204577</v>
+        <v>198.268138021441</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>198.267570204577</v>
+        <v>198.268138021441</v>
       </c>
       <c r="M65" s="13" t="n">
-        <v>190.039983271679</v>
+        <v>190.043429995022</v>
       </c>
       <c r="N65" s="14" t="n">
-        <v>190.039983271679</v>
+        <v>190.043429995022</v>
       </c>
       <c r="O65" s="15" t="n">
-        <v>0.0106801823426594</v>
+        <v>0.0106920044138477</v>
       </c>
       <c r="P65" s="16" t="n">
-        <v>0.0325828944967554</v>
+        <v>0.0326017605511626</v>
       </c>
       <c r="Q65" s="17" t="n">
-        <v>0.010737419074857</v>
+        <v>0.0107493681552093</v>
       </c>
       <c r="R65" s="18" t="n">
-        <v>0.990965235980925</v>
+        <v>0.990957668363271</v>
       </c>
       <c r="S65" s="19" t="n">
-        <v>1.01363606906646</v>
+        <v>1.01349687908777</v>
       </c>
     </row>
     <row r="66">
@@ -5310,46 +5310,46 @@
         <v>202.1</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>6.12532926591473</v>
+        <v>6.13011229997065</v>
       </c>
       <c r="G66" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H66" s="8" t="n">
-        <v>180.004369474215</v>
+        <v>180.015504758141</v>
       </c>
       <c r="I66" s="9" t="n">
-        <v>188.622402169867</v>
+        <v>188.652913568613</v>
       </c>
       <c r="J66" s="10" t="n">
-        <v>185.767567890753</v>
+        <v>185.774321085293</v>
       </c>
       <c r="K66" s="11" t="n">
-        <v>195.974670734085</v>
+        <v>195.969887700029</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>180.004369474215</v>
+        <v>180.015504758141</v>
       </c>
       <c r="M66" s="13" t="n">
-        <v>180.64696798256</v>
+        <v>180.65550844665</v>
       </c>
       <c r="N66" s="14" t="n">
-        <v>180.64696798256</v>
+        <v>180.65550844665</v>
       </c>
       <c r="O66" s="15" t="n">
-        <v>-0.0506898147733442</v>
+        <v>-0.0506606754626571</v>
       </c>
       <c r="P66" s="16" t="n">
-        <v>-0.0276717535161095</v>
+        <v>-0.0276209262815853</v>
       </c>
       <c r="Q66" s="17" t="n">
-        <v>-0.049426521342569</v>
+        <v>-0.0493988218830739</v>
       </c>
       <c r="R66" s="18" t="n">
-        <v>1.0035699050541</v>
+        <v>1.00355526980506</v>
       </c>
       <c r="S66" s="19" t="n">
-        <v>0.957717460410006</v>
+        <v>0.957607836684406</v>
       </c>
     </row>
     <row r="67">
@@ -5369,46 +5369,46 @@
         <v>137.864</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>5.20251291628637</v>
+        <v>5.20209326694935</v>
       </c>
       <c r="G67" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H67" s="8" t="n">
-        <v>164.311562777234</v>
+        <v>164.322886248876</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>189.902038735745</v>
+        <v>189.933404316982</v>
       </c>
       <c r="J67" s="10" t="n">
-        <v>187.162152740677</v>
+        <v>187.172129624621</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>132.661487083714</v>
+        <v>132.661906733051</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>164.311562777234</v>
+        <v>164.322886248876</v>
       </c>
       <c r="M67" s="13" t="n">
-        <v>169.217410277947</v>
+        <v>169.227692561172</v>
       </c>
       <c r="N67" s="14" t="n">
-        <v>169.217410277947</v>
+        <v>169.227692561172</v>
       </c>
       <c r="O67" s="15" t="n">
-        <v>-0.0653603340177862</v>
+        <v>-0.0653468480995585</v>
       </c>
       <c r="P67" s="16" t="n">
-        <v>-0.0905956389648732</v>
+        <v>-0.090541492119053</v>
       </c>
       <c r="Q67" s="17" t="n">
-        <v>-0.0632701330792155</v>
+        <v>-0.0632575003316468</v>
       </c>
       <c r="R67" s="18" t="n">
-        <v>1.02985698278194</v>
+        <v>1.02984858910564</v>
       </c>
       <c r="S67" s="19" t="n">
-        <v>0.891077375495785</v>
+        <v>0.890984359332317</v>
       </c>
     </row>
     <row r="68">
@@ -5428,46 +5428,46 @@
         <v>163.457</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>-4.78514608310468</v>
+        <v>-4.79249298879505</v>
       </c>
       <c r="G68" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>168.573532282584</v>
+        <v>168.580611048215</v>
       </c>
       <c r="I68" s="9" t="n">
-        <v>191.328255515251</v>
+        <v>191.359823490587</v>
       </c>
       <c r="J68" s="10" t="n">
-        <v>188.974115664858</v>
+        <v>188.98801755159</v>
       </c>
       <c r="K68" s="11" t="n">
-        <v>168.242146083105</v>
+        <v>168.249492988795</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>168.242146083105</v>
+        <v>168.249492988795</v>
       </c>
       <c r="M68" s="13" t="n">
-        <v>171.782122416524</v>
+        <v>171.789176358727</v>
       </c>
       <c r="N68" s="14" t="n">
-        <v>171.782122416524</v>
+        <v>171.789176358727</v>
       </c>
       <c r="O68" s="15" t="n">
-        <v>0.0150426041938406</v>
+        <v>0.0150229047618421</v>
       </c>
       <c r="P68" s="16" t="n">
-        <v>-0.086367952336307</v>
+        <v>-0.0863362050188461</v>
       </c>
       <c r="Q68" s="17" t="n">
-        <v>0.0151563136107817</v>
+        <v>0.0151363158049873</v>
       </c>
       <c r="R68" s="18" t="n">
-        <v>1.01903377173447</v>
+        <v>1.01903282524937</v>
       </c>
       <c r="S68" s="19" t="n">
-        <v>0.897839798695237</v>
+        <v>0.897728547325807</v>
       </c>
     </row>
     <row r="69">
@@ -5487,46 +5487,46 @@
         <v>180.02</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>-6.31263472265178</v>
+        <v>-6.3148332084428</v>
       </c>
       <c r="G69" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H69" s="8" t="n">
-        <v>185.830087905487</v>
+        <v>185.829100705642</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>192.890958226037</v>
+        <v>192.921920590545</v>
       </c>
       <c r="J69" s="10" t="n">
-        <v>191.181299264223</v>
+        <v>191.199906225433</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>186.332634722652</v>
+        <v>186.334833208443</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>186.332634722652</v>
+        <v>186.334833208443</v>
       </c>
       <c r="M69" s="13" t="n">
-        <v>185.350876905701</v>
+        <v>185.349836058624</v>
       </c>
       <c r="N69" s="14" t="n">
-        <v>185.350876905701</v>
+        <v>185.349836058624</v>
       </c>
       <c r="O69" s="15" t="n">
-        <v>0.0760237169695059</v>
+        <v>0.0759770389390203</v>
       </c>
       <c r="P69" s="16" t="n">
-        <v>-0.0246743147691992</v>
+        <v>-0.0246974806575592</v>
       </c>
       <c r="Q69" s="17" t="n">
-        <v>0.0789881641832109</v>
+        <v>0.0789378003162418</v>
       </c>
       <c r="R69" s="18" t="n">
-        <v>0.997421241063879</v>
+        <v>0.997420938673232</v>
       </c>
       <c r="S69" s="19" t="n">
-        <v>0.960910136018398</v>
+        <v>0.960750522756864</v>
       </c>
     </row>
     <row r="70">
@@ -5546,46 +5546,46 @@
         <v>206.268</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>5.77190790560575</v>
+        <v>5.78781517118438</v>
       </c>
       <c r="G70" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H70" s="8" t="n">
-        <v>198.426315647652</v>
+        <v>198.411969436009</v>
       </c>
       <c r="I70" s="9" t="n">
-        <v>194.565623767363</v>
+        <v>194.59500116141</v>
       </c>
       <c r="J70" s="10" t="n">
-        <v>193.657886291788</v>
+        <v>193.682024382568</v>
       </c>
       <c r="K70" s="11" t="n">
-        <v>200.496092094394</v>
+        <v>200.480184828816</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>200.496092094394</v>
+        <v>200.480184828816</v>
       </c>
       <c r="M70" s="13" t="n">
-        <v>198.211386970557</v>
+        <v>198.202892991185</v>
       </c>
       <c r="N70" s="14" t="n">
-        <v>198.211386970557</v>
+        <v>198.202892991185</v>
       </c>
       <c r="O70" s="15" t="n">
-        <v>0.067083411499982</v>
+        <v>0.0670461730120726</v>
       </c>
       <c r="P70" s="16" t="n">
-        <v>0.0972306326762828</v>
+        <v>0.0971317437005665</v>
       </c>
       <c r="Q70" s="17" t="n">
-        <v>0.0693846734342622</v>
+        <v>0.0693448519074813</v>
       </c>
       <c r="R70" s="18" t="n">
-        <v>0.998916833806072</v>
+        <v>0.998946250846569</v>
       </c>
       <c r="S70" s="19" t="n">
-        <v>1.01873796168409</v>
+        <v>1.01854051649961</v>
       </c>
     </row>
     <row r="71">
@@ -5605,46 +5605,46 @@
         <v>188.803</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>5.04276293917768</v>
+        <v>5.04667960219374</v>
       </c>
       <c r="G71" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H71" s="8" t="n">
-        <v>205.520728970787</v>
+        <v>205.516369098667</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>196.323630086296</v>
+        <v>196.350253818121</v>
       </c>
       <c r="J71" s="10" t="n">
-        <v>196.253816177865</v>
+        <v>196.284275394328</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>183.760237060822</v>
+        <v>183.756320397806</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>205.520728970787</v>
+        <v>205.516369098667</v>
       </c>
       <c r="M71" s="13" t="n">
-        <v>205.276069365527</v>
+        <v>205.276708073523</v>
       </c>
       <c r="N71" s="14" t="n">
-        <v>205.276069365527</v>
+        <v>205.276708073523</v>
       </c>
       <c r="O71" s="15" t="n">
-        <v>0.0350216808445754</v>
+        <v>0.0350676463518168</v>
       </c>
       <c r="P71" s="16" t="n">
-        <v>0.21309071583327</v>
+        <v>0.213020782631778</v>
       </c>
       <c r="Q71" s="17" t="n">
-        <v>0.0356421621529719</v>
+        <v>0.0356897670643594</v>
       </c>
       <c r="R71" s="18" t="n">
-        <v>0.998809562390688</v>
+        <v>0.998833859189926</v>
       </c>
       <c r="S71" s="19" t="n">
-        <v>1.04560041639051</v>
+        <v>1.04546189313139</v>
       </c>
     </row>
     <row r="72">
@@ -5664,46 +5664,46 @@
         <v>205.667</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>-3.89972742613922</v>
+        <v>-3.92690926794159</v>
       </c>
       <c r="G72" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H72" s="8" t="n">
-        <v>203.60679920899</v>
+        <v>203.625848129116</v>
       </c>
       <c r="I72" s="9" t="n">
-        <v>198.140061672609</v>
+        <v>198.162545415411</v>
       </c>
       <c r="J72" s="10" t="n">
-        <v>198.853219381775</v>
+        <v>198.890553434278</v>
       </c>
       <c r="K72" s="11" t="n">
-        <v>209.566727426139</v>
+        <v>209.593909267942</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>209.566727426139</v>
+        <v>209.593909267942</v>
       </c>
       <c r="M72" s="13" t="n">
-        <v>204.306678726549</v>
+        <v>204.32167814105</v>
       </c>
       <c r="N72" s="14" t="n">
-        <v>204.306678726549</v>
+        <v>204.32167814105</v>
       </c>
       <c r="O72" s="15" t="n">
-        <v>-0.00473356094002862</v>
+        <v>-0.00466325891549571</v>
       </c>
       <c r="P72" s="16" t="n">
-        <v>0.189336095354338</v>
+        <v>0.18937457220465</v>
       </c>
       <c r="Q72" s="17" t="n">
-        <v>-0.00472237529671005</v>
+        <v>-0.00465240280514601</v>
       </c>
       <c r="R72" s="18" t="n">
-        <v>1.00343740739641</v>
+        <v>1.00341719883958</v>
       </c>
       <c r="S72" s="19" t="n">
-        <v>1.03112251506275</v>
+        <v>1.03108121523534</v>
       </c>
     </row>
     <row r="73">
@@ -5723,46 +5723,46 @@
         <v>185.9</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>-6.67253108313201</v>
+        <v>-6.68252492965159</v>
       </c>
       <c r="G73" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H73" s="8" t="n">
-        <v>198.242131967803</v>
+        <v>198.244947822333</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>199.995751202879</v>
+        <v>200.012471630062</v>
       </c>
       <c r="J73" s="10" t="n">
-        <v>201.386560926806</v>
+        <v>201.430913144505</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>192.572531083132</v>
+        <v>192.582524929652</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>192.572531083132</v>
+        <v>192.582524929652</v>
       </c>
       <c r="M73" s="13" t="n">
-        <v>198.8851266663</v>
+        <v>198.885695431806</v>
       </c>
       <c r="N73" s="14" t="n">
-        <v>198.8851266663</v>
+        <v>198.885695431806</v>
       </c>
       <c r="O73" s="15" t="n">
-        <v>-0.0268947869534914</v>
+        <v>-0.0269653406669656</v>
       </c>
       <c r="P73" s="16" t="n">
-        <v>0.0730196154803495</v>
+        <v>0.0730287097146447</v>
       </c>
       <c r="Q73" s="17" t="n">
-        <v>-0.0265363427864502</v>
+        <v>-0.0266050218395891</v>
       </c>
       <c r="R73" s="18" t="n">
-        <v>1.00324348155518</v>
+        <v>1.00323210057311</v>
       </c>
       <c r="S73" s="19" t="n">
-        <v>0.994446759344142</v>
+        <v>0.994366470305211</v>
       </c>
     </row>
     <row r="74">
@@ -5782,46 +5782,46 @@
         <v>205.218</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>4.3892829272012</v>
+        <v>4.43417740001962</v>
       </c>
       <c r="G74" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H74" s="8" t="n">
-        <v>198.374685239273</v>
+        <v>198.340236013053</v>
       </c>
       <c r="I74" s="9" t="n">
-        <v>201.878673019777</v>
+        <v>201.887772741264</v>
       </c>
       <c r="J74" s="10" t="n">
-        <v>203.837873376466</v>
+        <v>203.888925946262</v>
       </c>
       <c r="K74" s="11" t="n">
-        <v>200.828717072799</v>
+        <v>200.78382259998</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>200.828717072799</v>
+        <v>200.78382259998</v>
       </c>
       <c r="M74" s="13" t="n">
-        <v>200.336341624337</v>
+        <v>200.311156847522</v>
       </c>
       <c r="N74" s="14" t="n">
-        <v>200.336341624337</v>
+        <v>200.311156847522</v>
       </c>
       <c r="O74" s="15" t="n">
-        <v>0.00727025706528449</v>
+        <v>0.00714167692557502</v>
       </c>
       <c r="P74" s="16" t="n">
-        <v>0.0107206487289064</v>
+        <v>0.0106368974969</v>
       </c>
       <c r="Q74" s="17" t="n">
-        <v>0.00729674954765169</v>
+        <v>0.00716723951725329</v>
       </c>
       <c r="R74" s="18" t="n">
-        <v>1.00988864271012</v>
+        <v>1.00993707012801</v>
       </c>
       <c r="S74" s="19" t="n">
-        <v>0.992360107324024</v>
+        <v>0.992190632090617</v>
       </c>
     </row>
     <row r="75">
@@ -5841,46 +5841,46 @@
         <v>213.262</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>6.14659873137969</v>
+        <v>6.1675427395262</v>
       </c>
       <c r="G75" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H75" s="8" t="n">
-        <v>207.624093675187</v>
+        <v>207.608500963445</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>203.7721619534</v>
+        <v>203.771545311519</v>
       </c>
       <c r="J75" s="10" t="n">
-        <v>206.147119145047</v>
+        <v>206.203921319731</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>207.11540126862</v>
+        <v>207.094457260474</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>207.11540126862</v>
+        <v>207.094457260474</v>
       </c>
       <c r="M75" s="13" t="n">
-        <v>208.173448888392</v>
+        <v>208.16578577556</v>
       </c>
       <c r="N75" s="14" t="n">
-        <v>208.173448888392</v>
+        <v>208.16578577556</v>
       </c>
       <c r="O75" s="15" t="n">
-        <v>0.0383739589136517</v>
+        <v>0.0384628674188018</v>
       </c>
       <c r="P75" s="16" t="n">
-        <v>0.014114550867133</v>
+        <v>0.0140740648520254</v>
       </c>
       <c r="Q75" s="17" t="n">
-        <v>0.0391197483218</v>
+        <v>0.0392121390123934</v>
       </c>
       <c r="R75" s="18" t="n">
-        <v>1.00264591263702</v>
+        <v>1.0026843063243</v>
       </c>
       <c r="S75" s="19" t="n">
-        <v>1.02159905893327</v>
+        <v>1.02156454404526</v>
       </c>
     </row>
     <row r="76">
@@ -5900,46 +5900,46 @@
         <v>215.168</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>-2.46627594352747</v>
+        <v>-2.52240598131162</v>
       </c>
       <c r="G76" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H76" s="8" t="n">
-        <v>219.409659297804</v>
+        <v>219.475958645006</v>
       </c>
       <c r="I76" s="9" t="n">
-        <v>205.658896611377</v>
+        <v>205.64619593449</v>
       </c>
       <c r="J76" s="10" t="n">
-        <v>208.23921486532</v>
+        <v>208.29970322836</v>
       </c>
       <c r="K76" s="11" t="n">
-        <v>217.634275943527</v>
+        <v>217.690405981312</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>217.634275943527</v>
+        <v>217.690405981312</v>
       </c>
       <c r="M76" s="13" t="n">
-        <v>218.51077010441</v>
+        <v>218.555532346682</v>
       </c>
       <c r="N76" s="14" t="n">
-        <v>218.51077010441</v>
+        <v>218.555532346682</v>
       </c>
       <c r="O76" s="15" t="n">
-        <v>0.0484636833209324</v>
+        <v>0.0487053256348076</v>
       </c>
       <c r="P76" s="16" t="n">
-        <v>0.0695233825266777</v>
+        <v>0.069663945280469</v>
       </c>
       <c r="Q76" s="17" t="n">
-        <v>0.0496572510626019</v>
+        <v>0.0499109233172654</v>
       </c>
       <c r="R76" s="18" t="n">
-        <v>0.995903146669702</v>
+        <v>0.995806254571087</v>
       </c>
       <c r="S76" s="19" t="n">
-        <v>1.06249121095558</v>
+        <v>1.0627744965256</v>
       </c>
     </row>
     <row r="77">
@@ -5959,46 +5959,46 @@
         <v>223.64</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>-8.01912726196603</v>
+        <v>-8.10686016363171</v>
       </c>
       <c r="G77" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H77" s="8" t="n">
-        <v>228.631094731733</v>
+        <v>228.650885181406</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>207.523645125912</v>
+        <v>207.496208023811</v>
       </c>
       <c r="J77" s="10" t="n">
-        <v>210.043918580676</v>
+        <v>210.104528315301</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>231.659127261966</v>
+        <v>231.746860163632</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>231.659127261966</v>
+        <v>231.746860163632</v>
       </c>
       <c r="M77" s="13" t="n">
-        <v>226.309310352972</v>
+        <v>226.326402690995</v>
       </c>
       <c r="N77" s="14" t="n">
-        <v>226.309310352972</v>
+        <v>226.326402690995</v>
       </c>
       <c r="O77" s="15" t="n">
-        <v>0.0350673890159134</v>
+        <v>0.0349380821662889</v>
       </c>
       <c r="P77" s="16" t="n">
-        <v>0.13788956543083</v>
+        <v>0.137972251848539</v>
       </c>
       <c r="Q77" s="17" t="n">
-        <v>0.0356895005442319</v>
+        <v>0.0355555874558537</v>
       </c>
       <c r="R77" s="18" t="n">
-        <v>0.98984484423921</v>
+        <v>0.989833923063248</v>
       </c>
       <c r="S77" s="19" t="n">
-        <v>1.09052301107983</v>
+        <v>1.09074958451782</v>
       </c>
     </row>
     <row r="78">
@@ -6018,46 +6018,46 @@
         <v>226.867</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>2.58228905557067</v>
+        <v>2.74551554459377</v>
       </c>
       <c r="G78" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H78" s="8" t="n">
-        <v>224.885742984366</v>
+        <v>224.802752603697</v>
       </c>
       <c r="I78" s="9" t="n">
-        <v>209.358660241288</v>
+        <v>209.313592624393</v>
       </c>
       <c r="J78" s="10" t="n">
-        <v>211.537963639896</v>
+        <v>211.593606737473</v>
       </c>
       <c r="K78" s="11" t="n">
-        <v>224.284710944429</v>
+        <v>224.121484455406</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>224.284710944429</v>
+        <v>224.121484455406</v>
       </c>
       <c r="M78" s="13" t="n">
-        <v>223.018312770875</v>
+        <v>222.95650082234</v>
       </c>
       <c r="N78" s="14" t="n">
-        <v>223.018312770875</v>
+        <v>222.95650082234</v>
       </c>
       <c r="O78" s="15" t="n">
-        <v>-0.0146488052952732</v>
+        <v>-0.0150015281712276</v>
       </c>
       <c r="P78" s="16" t="n">
-        <v>0.113219453657937</v>
+        <v>0.113050837163587</v>
       </c>
       <c r="Q78" s="17" t="n">
-        <v>-0.0145420335423426</v>
+        <v>-0.0148895658155092</v>
       </c>
       <c r="R78" s="18" t="n">
-        <v>0.991696093364082</v>
+        <v>0.991787236766574</v>
       </c>
       <c r="S78" s="19" t="n">
-        <v>1.06524522326349</v>
+        <v>1.06517927491899</v>
       </c>
     </row>
     <row r="79">
@@ -6077,46 +6077,46 @@
         <v>220.115</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>8.27029806732523</v>
+        <v>8.27882578508279</v>
       </c>
       <c r="G79" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H79" s="8" t="n">
-        <v>211.980512506984</v>
+        <v>211.971063178788</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>211.171279378125</v>
+        <v>211.105517438733</v>
       </c>
       <c r="J79" s="10" t="n">
-        <v>212.806159435168</v>
+        <v>212.850360311034</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>211.844701932675</v>
+        <v>211.836174214917</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>211.844701932675</v>
+        <v>211.836174214917</v>
       </c>
       <c r="M79" s="13" t="n">
-        <v>212.61535150144</v>
+        <v>212.607108583193</v>
       </c>
       <c r="N79" s="14" t="n">
-        <v>212.61535150144</v>
+        <v>212.607108583193</v>
       </c>
       <c r="O79" s="15" t="n">
-        <v>-0.0477692164569643</v>
+        <v>-0.0475307870855175</v>
       </c>
       <c r="P79" s="16" t="n">
-        <v>0.021337507913558</v>
+        <v>0.0213355080955595</v>
       </c>
       <c r="Q79" s="17" t="n">
-        <v>-0.0466462199457236</v>
+        <v>-0.0464188853026277</v>
       </c>
       <c r="R79" s="18" t="n">
-        <v>1.00299479884707</v>
+        <v>1.00300062374018</v>
       </c>
       <c r="S79" s="19" t="n">
-        <v>1.00683839264302</v>
+        <v>1.00711298862615</v>
       </c>
     </row>
     <row r="80">
@@ -6136,46 +6136,46 @@
         <v>200.998</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>-1.48929119598281</v>
+        <v>-1.636601447531</v>
       </c>
       <c r="G80" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H80" s="8" t="n">
-        <v>203.144101550873</v>
+        <v>203.211003879269</v>
       </c>
       <c r="I80" s="9" t="n">
-        <v>212.978168738732</v>
+        <v>212.888405101726</v>
       </c>
       <c r="J80" s="10" t="n">
-        <v>213.997049095202</v>
+        <v>214.020850240733</v>
       </c>
       <c r="K80" s="11" t="n">
-        <v>202.487291195983</v>
+        <v>202.634601447531</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>202.487291195983</v>
+        <v>202.634601447531</v>
       </c>
       <c r="M80" s="13" t="n">
-        <v>204.832585837396</v>
+        <v>204.882189011588</v>
       </c>
       <c r="N80" s="14" t="n">
-        <v>204.832585837396</v>
+        <v>204.882189011588</v>
       </c>
       <c r="O80" s="15" t="n">
-        <v>-0.0372916806374795</v>
+        <v>-0.0370107755765204</v>
       </c>
       <c r="P80" s="16" t="n">
-        <v>-0.0625973001718794</v>
+        <v>-0.0625623299867111</v>
       </c>
       <c r="Q80" s="17" t="n">
-        <v>-0.0366049093307907</v>
+        <v>-0.0363342487609364</v>
       </c>
       <c r="R80" s="18" t="n">
-        <v>1.00831175640165</v>
+        <v>1.00822389093315</v>
       </c>
       <c r="S80" s="19" t="n">
-        <v>0.961753906752159</v>
+        <v>0.962392427683823</v>
       </c>
     </row>
     <row r="81">
@@ -6195,46 +6195,46 @@
         <v>193.143</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>-9.36805902494365</v>
+        <v>-9.28037893637176</v>
       </c>
       <c r="G81" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H81" s="8" t="n">
-        <v>202.259540090632</v>
+        <v>202.259563751726</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>214.796415414515</v>
+        <v>214.67913490875</v>
       </c>
       <c r="J81" s="10" t="n">
-        <v>215.254368461196</v>
+        <v>215.246066800839</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>202.511059024944</v>
+        <v>202.423378936372</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>202.511059024944</v>
+        <v>202.423378936372</v>
       </c>
       <c r="M81" s="13" t="n">
-        <v>204.194715864022</v>
+        <v>204.185106654817</v>
       </c>
       <c r="N81" s="14" t="n">
-        <v>204.194715864022</v>
+        <v>204.185106654817</v>
       </c>
       <c r="O81" s="15" t="n">
-        <v>-0.0031189629045122</v>
+        <v>-0.00340815821213161</v>
       </c>
       <c r="P81" s="16" t="n">
-        <v>-0.0977184476169272</v>
+        <v>-0.0978290458953133</v>
       </c>
       <c r="Q81" s="17" t="n">
-        <v>-0.00311410399261369</v>
+        <v>-0.00340235703324865</v>
       </c>
       <c r="R81" s="18" t="n">
-        <v>1.00956778489916</v>
+        <v>1.00952015750145</v>
       </c>
       <c r="S81" s="19" t="n">
-        <v>0.95064303317151</v>
+        <v>0.951117614395112</v>
       </c>
     </row>
     <row r="82">
@@ -6254,46 +6254,46 @@
         <v>210.215</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>0.945545789780472</v>
+        <v>0.955932701007436</v>
       </c>
       <c r="G82" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H82" s="8" t="n">
-        <v>211.272081740901</v>
+        <v>211.181839463884</v>
       </c>
       <c r="I82" s="9" t="n">
-        <v>216.636549698416</v>
+        <v>216.488177527899</v>
       </c>
       <c r="J82" s="10" t="n">
-        <v>216.664304584852</v>
+        <v>216.610069021652</v>
       </c>
       <c r="K82" s="11" t="n">
-        <v>209.26945421022</v>
+        <v>209.259067298993</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>209.26945421022</v>
+        <v>209.259067298993</v>
       </c>
       <c r="M82" s="13" t="n">
-        <v>211.147835332834</v>
+        <v>211.098941596278</v>
       </c>
       <c r="N82" s="14" t="n">
-        <v>211.147835332834</v>
+        <v>211.098941596278</v>
       </c>
       <c r="O82" s="15" t="n">
-        <v>0.0334845013910547</v>
+        <v>0.0332999731048854</v>
       </c>
       <c r="P82" s="16" t="n">
-        <v>-0.0532264695690534</v>
+        <v>-0.0531832854495254</v>
       </c>
       <c r="Q82" s="17" t="n">
-        <v>0.0340514172435396</v>
+        <v>0.0338606231117031</v>
       </c>
       <c r="R82" s="18" t="n">
-        <v>0.999411912794899</v>
+        <v>0.999607457403459</v>
       </c>
       <c r="S82" s="19" t="n">
-        <v>0.974663950412696</v>
+        <v>0.975106095893271</v>
       </c>
     </row>
     <row r="83">
@@ -6313,46 +6313,46 @@
         <v>233.918</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>10.3766261140458</v>
+        <v>10.4144160566753</v>
       </c>
       <c r="G83" s="7" t="n">
-        <v>1</v>
+        <v>0.984271685033847</v>
       </c>
       <c r="H83" s="8" t="n">
-        <v>220.342980749499</v>
+        <v>220.367132729452</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>218.501423535632</v>
+        <v>218.318343779784</v>
       </c>
       <c r="J83" s="10" t="n">
-        <v>218.249327970691</v>
+        <v>218.132802494154</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>223.541373885954</v>
+        <v>223.503583943325</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>223.541373885954</v>
+        <v>223.454252850757</v>
       </c>
       <c r="M83" s="13" t="n">
-        <v>218.796009366214</v>
+        <v>218.800673410924</v>
       </c>
       <c r="N83" s="14" t="n">
-        <v>218.796009366214</v>
+        <v>218.800673410924</v>
       </c>
       <c r="O83" s="15" t="n">
-        <v>0.0355813021237278</v>
+        <v>0.035834207203032</v>
       </c>
       <c r="P83" s="16" t="n">
-        <v>0.0290696688697571</v>
+        <v>0.0291315039699513</v>
       </c>
       <c r="Q83" s="17" t="n">
-        <v>0.0362218917438779</v>
+        <v>0.0364839906652634</v>
       </c>
       <c r="R83" s="18" t="n">
-        <v>0.992979257256017</v>
+        <v>0.992891592774631</v>
       </c>
       <c r="S83" s="19" t="n">
-        <v>1.00134821012063</v>
+        <v>1.00220929502666</v>
       </c>
     </row>
     <row r="84">
@@ -6372,46 +6372,46 @@
         <v>217.826</v>
       </c>
       <c r="F84" s="6" t="n">
-        <v>-1.00583548272933</v>
+        <v>-1.2091206431897</v>
       </c>
       <c r="G84" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H84" s="8" t="n">
-        <v>218.969187944931</v>
+        <v>218.938463230753</v>
       </c>
       <c r="I84" s="9" t="n">
-        <v>220.389284436681</v>
+        <v>220.167926291124</v>
       </c>
       <c r="J84" s="10" t="n">
-        <v>219.994934871358</v>
+        <v>219.79745780071</v>
       </c>
       <c r="K84" s="11" t="n">
-        <v>218.831835482729</v>
+        <v>219.03512064319</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>218.831835482729</v>
+        <v>219.03512064319</v>
       </c>
       <c r="M84" s="13" t="n">
-        <v>218.352492428089</v>
+        <v>218.351341408016</v>
       </c>
       <c r="N84" s="14" t="n">
-        <v>218.352492428089</v>
+        <v>218.351341408016</v>
       </c>
       <c r="O84" s="15" t="n">
-        <v>-0.00202913695681196</v>
+        <v>-0.0020557249922941</v>
       </c>
       <c r="P84" s="16" t="n">
-        <v>0.0660046668620682</v>
+        <v>0.0657409629475745</v>
       </c>
       <c r="Q84" s="17" t="n">
-        <v>-0.00202707965017146</v>
+        <v>-0.00205361343684574</v>
       </c>
       <c r="R84" s="18" t="n">
-        <v>0.997183642490391</v>
+        <v>0.997318324911609</v>
       </c>
       <c r="S84" s="19" t="n">
-        <v>0.990758207624307</v>
+        <v>0.991749093913409</v>
       </c>
     </row>
     <row r="85">
@@ -6431,46 +6431,46 @@
         <v>201.979</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>-10.2259248609445</v>
+        <v>-9.90187149492958</v>
       </c>
       <c r="G85" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H85" s="8" t="n">
-        <v>213.872310312874</v>
+        <v>213.852430457019</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>222.30152988105</v>
+        <v>222.038427631807</v>
       </c>
       <c r="J85" s="10" t="n">
-        <v>221.91308176908</v>
+        <v>221.613832775471</v>
       </c>
       <c r="K85" s="11" t="n">
-        <v>212.204924860945</v>
+        <v>211.88087149493</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>212.204924860945</v>
+        <v>211.88087149493</v>
       </c>
       <c r="M85" s="13" t="n">
-        <v>215.523950840574</v>
+        <v>215.470969042693</v>
       </c>
       <c r="N85" s="14" t="n">
-        <v>215.523950840574</v>
+        <v>215.470969042693</v>
       </c>
       <c r="O85" s="15" t="n">
-        <v>-0.0130386505365838</v>
+        <v>-0.0132792372473067</v>
       </c>
       <c r="P85" s="16" t="n">
-        <v>0.0554825080982801</v>
+        <v>0.0552727011914516</v>
       </c>
       <c r="Q85" s="17" t="n">
-        <v>-0.0129540155739091</v>
+        <v>-0.0131914571568444</v>
       </c>
       <c r="R85" s="18" t="n">
-        <v>1.00772255429085</v>
+        <v>1.00756848347346</v>
       </c>
       <c r="S85" s="19" t="n">
-        <v>0.969511775091685</v>
+        <v>0.970421973082945</v>
       </c>
     </row>
     <row r="86">
@@ -6490,46 +6490,46 @@
         <v>218.523</v>
       </c>
       <c r="F86" s="6" t="n">
-        <v>-0.331118157677729</v>
+        <v>-0.564012537723683</v>
       </c>
       <c r="G86" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H86" s="8" t="n">
-        <v>219.40238240164</v>
+        <v>219.32657065522</v>
       </c>
       <c r="I86" s="9" t="n">
-        <v>224.23858394263</v>
+        <v>223.930642368192</v>
       </c>
       <c r="J86" s="10" t="n">
-        <v>224.009909649135</v>
+        <v>223.587913566797</v>
       </c>
       <c r="K86" s="11" t="n">
-        <v>218.854118157678</v>
+        <v>219.087012537724</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>218.854118157678</v>
+        <v>219.087012537724</v>
       </c>
       <c r="M86" s="13" t="n">
-        <v>219.910964880998</v>
+        <v>219.929841417526</v>
       </c>
       <c r="N86" s="14" t="n">
-        <v>219.910964880998</v>
+        <v>219.929841417526</v>
       </c>
       <c r="O86" s="15" t="n">
-        <v>0.0201507151911346</v>
+        <v>0.0204824067945471</v>
       </c>
       <c r="P86" s="16" t="n">
-        <v>0.0415023414014657</v>
+        <v>0.041832989566269</v>
       </c>
       <c r="Q86" s="17" t="n">
-        <v>0.0203551114542677</v>
+        <v>0.0206936108128302</v>
       </c>
       <c r="R86" s="18" t="n">
-        <v>1.00231803535491</v>
+        <v>1.00275055940784</v>
       </c>
       <c r="S86" s="19" t="n">
-        <v>0.980700827727582</v>
+        <v>0.982133749502279</v>
       </c>
     </row>
     <row r="87">
@@ -6549,46 +6549,46 @@
         <v>259.799</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>11.8847271582184</v>
+        <v>11.9574926978086</v>
       </c>
       <c r="G87" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H87" s="8" t="n">
-        <v>229.730698347692</v>
+        <v>229.664469099727</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>226.194560317173</v>
+        <v>225.839016594049</v>
       </c>
       <c r="J87" s="10" t="n">
-        <v>226.243018712264</v>
+        <v>225.677021516649</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>247.914272841782</v>
+        <v>247.841507302191</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>229.730698347692</v>
+        <v>229.664469099727</v>
       </c>
       <c r="M87" s="13" t="n">
-        <v>228.383850799914</v>
+        <v>228.24282301662</v>
       </c>
       <c r="N87" s="14" t="n">
-        <v>228.383850799914</v>
+        <v>228.24282301662</v>
       </c>
       <c r="O87" s="15" t="n">
-        <v>0.0378050101515877</v>
+        <v>0.0371014826164916</v>
       </c>
       <c r="P87" s="16" t="n">
-        <v>0.0438209154795484</v>
+        <v>0.0431541158374891</v>
       </c>
       <c r="Q87" s="17" t="n">
-        <v>0.0385287105783956</v>
+        <v>0.0377983339846633</v>
       </c>
       <c r="R87" s="18" t="n">
-        <v>0.994137276570065</v>
+        <v>0.99380989976952</v>
       </c>
       <c r="S87" s="19" t="n">
-        <v>1.00967879368836</v>
+        <v>1.0106438934194</v>
       </c>
     </row>
     <row r="88">
@@ -6608,46 +6608,46 @@
         <v>223.724</v>
       </c>
       <c r="F88" s="6" t="n">
-        <v>-0.780061531566807</v>
+        <v>-1.03381383789636</v>
       </c>
       <c r="G88" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H88" s="8" t="n">
-        <v>235.219888346593</v>
+        <v>234.555341329301</v>
       </c>
       <c r="I88" s="9" t="n">
-        <v>228.160207409318</v>
+        <v>227.754969134509</v>
       </c>
       <c r="J88" s="10" t="n">
-        <v>228.54423020175</v>
+        <v>227.81597346184</v>
       </c>
       <c r="K88" s="11" t="n">
-        <v>224.504061531567</v>
+        <v>224.757813837896</v>
       </c>
       <c r="L88" s="12" t="n">
-        <v>235.219888346593</v>
+        <v>234.555341329301</v>
       </c>
       <c r="M88" s="13" t="n">
-        <v>233.626423090786</v>
+        <v>233.108673898789</v>
       </c>
       <c r="N88" s="14" t="n">
-        <v>233.626423090786</v>
+        <v>233.108673898789</v>
       </c>
       <c r="O88" s="15" t="n">
-        <v>0.0226955876011309</v>
+        <v>0.0210946809514326</v>
       </c>
       <c r="P88" s="16" t="n">
-        <v>0.0699507960401533</v>
+        <v>0.0675852614213939</v>
       </c>
       <c r="Q88" s="17" t="n">
-        <v>0.0229550919318944</v>
+        <v>0.0213187464905098</v>
       </c>
       <c r="R88" s="18" t="n">
-        <v>0.99322563552339</v>
+        <v>0.993832298073823</v>
       </c>
       <c r="S88" s="19" t="n">
-        <v>1.02395779589936</v>
+        <v>1.02350642352448</v>
       </c>
     </row>
     <row r="89">
@@ -6667,80 +6667,106 @@
         <v>223.584</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>-10.751217322265</v>
+        <v>-10.0755438368281</v>
       </c>
       <c r="G89" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H89" s="8" t="n">
-        <v>233.381186116253</v>
+        <v>234.140713120558</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>230.128483709971</v>
+        <v>229.672309722515</v>
       </c>
       <c r="J89" s="10" t="n">
-        <v>230.862803759051</v>
+        <v>229.959523477099</v>
       </c>
       <c r="K89" s="11" t="n">
-        <v>234.335217322265</v>
+        <v>233.659543836828</v>
       </c>
       <c r="L89" s="12" t="n">
-        <v>234.335217322265</v>
+        <v>233.659543836828</v>
       </c>
       <c r="M89" s="13" t="n">
-        <v>234.630107663708</v>
+        <v>233.145087076604</v>
       </c>
       <c r="N89" s="14" t="n">
-        <v>234.630107663708</v>
+        <v>233.145087076604</v>
       </c>
       <c r="O89" s="15" t="n">
-        <v>0.00428690704392878</v>
+        <v>0.000156194677389179</v>
       </c>
       <c r="P89" s="16" t="n">
-        <v>0.0886498078223648</v>
+        <v>0.0820255188549726</v>
       </c>
       <c r="Q89" s="17" t="n">
-        <v>0.00429610897450527</v>
+        <v>0.000156206876412934</v>
       </c>
       <c r="R89" s="18" t="n">
-        <v>1.00535142342979</v>
+        <v>0.995747744889452</v>
       </c>
       <c r="S89" s="19" t="n">
-        <v>1.01956135060365</v>
+        <v>1.01512057486723</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
         <v>142</v>
       </c>
-      <c r="B90" s="2"/>
+      <c r="B90" s="2" t="n">
+        <v>229.117</v>
+      </c>
       <c r="C90" s="3" t="n">
-        <v>225.422383998404</v>
+        <v>229.117</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>253.554146895334</v>
+        <v>229.117</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>197.290621101474</v>
+        <v>229.117</v>
       </c>
       <c r="F90" s="6" t="n">
-        <v>-0.976659506990502</v>
-      </c>
-      <c r="G90" s="7"/>
-      <c r="H90" s="8"/>
-      <c r="I90" s="9"/>
-      <c r="J90" s="10"/>
-      <c r="K90" s="11"/>
-      <c r="L90" s="12"/>
-      <c r="M90" s="13"/>
+        <v>-1.58891930345777</v>
+      </c>
+      <c r="G90" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" s="8" t="n">
+        <v>228.785914689421</v>
+      </c>
+      <c r="I90" s="9" t="n">
+        <v>231.589098323633</v>
+      </c>
+      <c r="J90" s="10" t="n">
+        <v>232.096122476493</v>
+      </c>
+      <c r="K90" s="11" t="n">
+        <v>230.705919303458</v>
+      </c>
+      <c r="L90" s="12" t="n">
+        <v>230.705919303458</v>
+      </c>
+      <c r="M90" s="13" t="n">
+        <v>231.690460814581</v>
+      </c>
       <c r="N90" s="14" t="n">
-        <v>226.399043505395</v>
-      </c>
-      <c r="O90" s="15"/>
-      <c r="P90" s="16"/>
-      <c r="Q90" s="17"/>
-      <c r="R90" s="18"/>
-      <c r="S90" s="19"/>
+        <v>231.690460814581</v>
+      </c>
+      <c r="O90" s="15" t="n">
+        <v>-0.00625869091513379</v>
+      </c>
+      <c r="P90" s="16" t="n">
+        <v>0.0534744140279184</v>
+      </c>
+      <c r="Q90" s="17" t="n">
+        <v>-0.00623914610538023</v>
+      </c>
+      <c r="R90" s="18" t="n">
+        <v>1.01269547615771</v>
+      </c>
+      <c r="S90" s="19" t="n">
+        <v>1.00043768248023</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
@@ -6748,16 +6774,16 @@
       </c>
       <c r="B91" s="2"/>
       <c r="C91" s="3" t="n">
-        <v>231.746704784108</v>
+        <v>233.734375816777</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>263.708452825803</v>
+        <v>261.647083050523</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>199.784956742412</v>
+        <v>205.82166858303</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>12.6132209836113</v>
+        <v>12.7563660260726</v>
       </c>
       <c r="G91" s="7"/>
       <c r="H91" s="8"/>
@@ -6767,7 +6793,7 @@
       <c r="L91" s="12"/>
       <c r="M91" s="13"/>
       <c r="N91" s="14" t="n">
-        <v>219.133483800497</v>
+        <v>220.978009790704</v>
       </c>
       <c r="O91" s="15"/>
       <c r="P91" s="16"/>
@@ -6781,16 +6807,16 @@
       </c>
       <c r="B92" s="2"/>
       <c r="C92" s="3" t="n">
-        <v>224.549500035969</v>
+        <v>225.375059552419</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>256.907668581367</v>
+        <v>257.122346272341</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>192.19133149057</v>
+        <v>193.627772832496</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>-0.545925905853313</v>
+        <v>-0.691279054812694</v>
       </c>
       <c r="G92" s="7"/>
       <c r="H92" s="8"/>
@@ -6800,7 +6826,7 @@
       <c r="L92" s="12"/>
       <c r="M92" s="13"/>
       <c r="N92" s="14" t="n">
-        <v>225.095425941822</v>
+        <v>226.066338607232</v>
       </c>
       <c r="O92" s="15"/>
       <c r="P92" s="16"/>
@@ -6814,16 +6840,16 @@
       </c>
       <c r="B93" s="2"/>
       <c r="C93" s="3" t="n">
-        <v>220.300031029583</v>
+        <v>221.394547143606</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>253.253275979595</v>
+        <v>253.522630603489</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>187.346786079571</v>
+        <v>189.266463683724</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>-11.3553681956846</v>
+        <v>-10.5108904656908</v>
       </c>
       <c r="G93" s="7"/>
       <c r="H93" s="8"/>
@@ -6833,7 +6859,7 @@
       <c r="L93" s="12"/>
       <c r="M93" s="13"/>
       <c r="N93" s="14" t="n">
-        <v>231.655399225268</v>
+        <v>231.905437609297</v>
       </c>
       <c r="O93" s="15"/>
       <c r="P93" s="16"/>
@@ -6846,10 +6872,18 @@
         <v>146</v>
       </c>
       <c r="B94" s="2"/>
-      <c r="C94" s="3"/>
-      <c r="D94" s="4"/>
-      <c r="E94" s="5"/>
-      <c r="F94" s="6"/>
+      <c r="C94" s="3" t="n">
+        <v>222.728246039133</v>
+      </c>
+      <c r="D94" s="4" t="n">
+        <v>255.494276203319</v>
+      </c>
+      <c r="E94" s="5" t="n">
+        <v>189.962215874946</v>
+      </c>
+      <c r="F94" s="6" t="n">
+        <v>-1.8088111130645</v>
+      </c>
       <c r="G94" s="7"/>
       <c r="H94" s="8"/>
       <c r="I94" s="9"/>
@@ -6857,7 +6891,9 @@
       <c r="K94" s="11"/>
       <c r="L94" s="12"/>
       <c r="M94" s="13"/>
-      <c r="N94" s="14"/>
+      <c r="N94" s="14" t="n">
+        <v>224.537057152198</v>
+      </c>
       <c r="O94" s="15"/>
       <c r="P94" s="16"/>
       <c r="Q94" s="17"/>
@@ -7355,7 +7391,7 @@
         <v>183</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>-0.168159348791623</v>
+        <v>-0.178654210980329</v>
       </c>
     </row>
     <row r="6">
@@ -7363,7 +7399,7 @@
         <v>184</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>-0.136509896938198</v>
+        <v>-0.141017907017458</v>
       </c>
     </row>
     <row r="7">
@@ -7371,7 +7407,7 @@
         <v>185</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>-0.11340327541941</v>
+        <v>-0.114940843874714</v>
       </c>
     </row>
     <row r="8">
@@ -7379,7 +7415,7 @@
         <v>186</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.0301876153557199</v>
+        <v>0.0276281163229993</v>
       </c>
     </row>
     <row r="9">
@@ -7387,7 +7423,7 @@
         <v>187</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.19747373967353</v>
+        <v>0.193736058801247</v>
       </c>
     </row>
     <row r="10">
@@ -7395,7 +7431,7 @@
         <v>188</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.218167362850277</v>
+        <v>0.216312269352229</v>
       </c>
     </row>
     <row r="11">
@@ -7403,7 +7439,7 @@
         <v>189</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.0778593441887351</v>
+        <v>0.0870838791410162</v>
       </c>
     </row>
     <row r="12">
@@ -7411,7 +7447,7 @@
         <v>190</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>-0.128855970090904</v>
+        <v>-0.118182671987372</v>
       </c>
     </row>
     <row r="13">
@@ -7419,7 +7455,7 @@
         <v>191</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>-0.227429780760657</v>
+        <v>-0.242682477526942</v>
       </c>
     </row>
     <row r="14">
